--- a/research/traditional_assets/database/data/new_zealand/new_zealand_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_business_consumer_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="nzse_agl" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,121 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0165</v>
+        <v>-0.0354</v>
       </c>
       <c r="E2">
-        <v>-0.0625</v>
+        <v>-0.0781</v>
       </c>
       <c r="G2">
-        <v>-0.05704861111111112</v>
+        <v>0.04752650176678445</v>
       </c>
       <c r="H2">
-        <v>-0.06157407407407409</v>
+        <v>0.01124852767962308</v>
       </c>
       <c r="I2">
-        <v>-0.1359375</v>
+        <v>-0.001177856301531212</v>
       </c>
       <c r="J2">
-        <v>-0.1172289299242424</v>
+        <v>-0.0009917949332215355</v>
       </c>
       <c r="K2">
-        <v>-3.37</v>
+        <v>2.982</v>
       </c>
       <c r="L2">
-        <v>-0.01950231481481482</v>
+        <v>0.01756183745583039</v>
       </c>
       <c r="M2">
-        <v>2.536</v>
+        <v>2.43</v>
       </c>
       <c r="N2">
-        <v>0.02161977834612106</v>
+        <v>0.02809248554913295</v>
       </c>
       <c r="O2">
-        <v>-0.7525222551928783</v>
+        <v>0.8148893360160966</v>
       </c>
       <c r="P2">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="Q2">
-        <v>0.01687979539641944</v>
+        <v>0.02809248554913295</v>
       </c>
       <c r="R2">
-        <v>-0.5875370919881305</v>
+        <v>0.8148893360160966</v>
       </c>
       <c r="S2">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.2192429022082019</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>16.05</v>
+        <v>8.48</v>
       </c>
       <c r="V2">
-        <v>0.1368286445012788</v>
+        <v>0.09803468208092486</v>
       </c>
       <c r="W2">
-        <v>-0.1616211438672521</v>
+        <v>0.05552047954751498</v>
       </c>
       <c r="X2">
-        <v>0.06341050236159855</v>
+        <v>0.1056526371536118</v>
       </c>
       <c r="Y2">
-        <v>-0.2250316462288506</v>
+        <v>-0.05013215760609679</v>
       </c>
       <c r="Z2">
-        <v>10.17727781376995</v>
+        <v>7.184260630420985</v>
       </c>
       <c r="AA2">
-        <v>-1.054838164395705</v>
+        <v>-0.1015725336384102</v>
       </c>
       <c r="AB2">
-        <v>0.05501773155835694</v>
+        <v>0.09503483368727039</v>
       </c>
       <c r="AC2">
-        <v>-1.109855895954062</v>
+        <v>-0.1966073673256806</v>
       </c>
       <c r="AD2">
-        <v>19.065</v>
+        <v>13.32</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>19.065</v>
+        <v>13.32</v>
       </c>
       <c r="AG2">
-        <v>3.015000000000001</v>
+        <v>4.84</v>
       </c>
       <c r="AH2">
-        <v>0.1398086019139809</v>
+        <v>0.1334401923462232</v>
       </c>
       <c r="AI2">
-        <v>0.2595113319267678</v>
+        <v>0.2287873582961182</v>
       </c>
       <c r="AJ2">
-        <v>0.02505921954868471</v>
+        <v>0.05298883293190278</v>
       </c>
       <c r="AK2">
-        <v>0.05251240964904642</v>
+        <v>0.09730599115400081</v>
       </c>
       <c r="AL2">
-        <v>1.444</v>
+        <v>0.805</v>
       </c>
       <c r="AM2">
-        <v>1.174</v>
+        <v>0.793</v>
       </c>
       <c r="AN2">
-        <v>-0.9245877788554802</v>
+        <v>5.86784140969163</v>
       </c>
       <c r="AO2">
-        <v>-16.26731301939058</v>
+        <v>-0.2484472049689438</v>
       </c>
       <c r="AP2">
-        <v>-0.1462172647914646</v>
+        <v>2.13215859030837</v>
       </c>
       <c r="AQ2">
-        <v>-20.00851788756388</v>
+        <v>-0.2522068095838584</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +715,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Straker Translations Limited (ASX:STG)</t>
+          <t>Accordant Group Limited (NZSE:AGL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,113 +723,122 @@
           <t>Business &amp; Consumer Services</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.0354</v>
+      </c>
+      <c r="E3">
+        <v>-0.0781</v>
+      </c>
       <c r="G3">
-        <v>-0.02601449275362318</v>
+        <v>0.03597285067873303</v>
       </c>
       <c r="H3">
-        <v>-0.05434782608695652</v>
+        <v>0.03597285067873303</v>
       </c>
       <c r="I3">
-        <v>-0.1663043478260869</v>
+        <v>0.01862745098039216</v>
       </c>
       <c r="J3">
-        <v>-0.1663043478260869</v>
+        <v>0.01274243934862081</v>
       </c>
       <c r="K3">
-        <v>-6.24</v>
+        <v>2.02</v>
       </c>
       <c r="L3">
-        <v>-0.2260869565217391</v>
+        <v>0.01523378582202112</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>2.43</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.06787709497206705</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.202970297029703</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>2.43</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.06787709497206705</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.202970297029703</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>12.6</v>
+        <v>1.43</v>
       </c>
       <c r="V3">
-        <v>0.1655716162943495</v>
+        <v>0.03994413407821229</v>
       </c>
       <c r="W3">
-        <v>-0.4394366197183099</v>
+        <v>0.07680608365019011</v>
       </c>
       <c r="X3">
-        <v>0.05676055031279478</v>
+        <v>0.1125360222959113</v>
       </c>
       <c r="Y3">
-        <v>-0.4961971700311046</v>
+        <v>-0.03572993864572115</v>
       </c>
       <c r="Z3">
-        <v>6.053959201579295</v>
+        <v>8.752475247524751</v>
       </c>
       <c r="AA3">
-        <v>-1.006799736784383</v>
+        <v>0.111527884991889</v>
       </c>
       <c r="AB3">
-        <v>0.05653810754929008</v>
+        <v>0.09246732636577178</v>
       </c>
       <c r="AC3">
-        <v>-1.063337844333673</v>
+        <v>0.01906055862611723</v>
       </c>
       <c r="AD3">
-        <v>0.465</v>
+        <v>12.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.465</v>
+        <v>12.3</v>
       </c>
       <c r="AG3">
-        <v>-12.135</v>
+        <v>10.87</v>
       </c>
       <c r="AH3">
-        <v>0.006073271076862796</v>
+        <v>0.2557172557172558</v>
       </c>
       <c r="AI3">
-        <v>0.0162786626991073</v>
+        <v>0.3704819277108434</v>
       </c>
       <c r="AJ3">
-        <v>-0.189713124364887</v>
+        <v>0.2329119348617956</v>
       </c>
       <c r="AK3">
-        <v>-0.7601002192295646</v>
+        <v>0.3421466792571609</v>
       </c>
       <c r="AL3">
-        <v>0.752</v>
+        <v>0.678</v>
       </c>
       <c r="AM3">
-        <v>0.482</v>
+        <v>0.667</v>
       </c>
       <c r="AN3">
-        <v>-0.1400602409638554</v>
+        <v>3.245382585751979</v>
       </c>
       <c r="AO3">
-        <v>-6.103723404255319</v>
+        <v>3.64306784660767</v>
       </c>
       <c r="AP3">
-        <v>3.655120481927711</v>
+        <v>2.868073878627968</v>
       </c>
       <c r="AQ3">
-        <v>-9.522821576763485</v>
+        <v>3.703148425787107</v>
       </c>
     </row>
     <row r="4">
@@ -838,130 +849,8833 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Straker Translations Limited (ASX:STG)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Business &amp; Consumer Services</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0.08870967741935484</v>
+      </c>
+      <c r="H4">
+        <v>-0.07688172043010752</v>
+      </c>
+      <c r="I4">
+        <v>-0.07177419354838709</v>
+      </c>
+      <c r="J4">
+        <v>-0.07177419354838709</v>
+      </c>
+      <c r="K4">
+        <v>0.962</v>
+      </c>
+      <c r="L4">
+        <v>0.02586021505376344</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>7.05</v>
+      </c>
+      <c r="V4">
+        <v>0.1390532544378698</v>
+      </c>
+      <c r="W4">
+        <v>0.03423487544483986</v>
+      </c>
+      <c r="X4">
+        <v>0.09876925201131229</v>
+      </c>
+      <c r="Y4">
+        <v>-0.06453437656647243</v>
+      </c>
+      <c r="Z4">
+        <v>4.384207424867413</v>
+      </c>
+      <c r="AA4">
+        <v>-0.3146729522687094</v>
+      </c>
+      <c r="AB4">
+        <v>0.09760234100876901</v>
+      </c>
+      <c r="AC4">
+        <v>-0.4122752932774785</v>
+      </c>
+      <c r="AD4">
+        <v>1.02</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>1.02</v>
+      </c>
+      <c r="AG4">
+        <v>-6.029999999999999</v>
+      </c>
+      <c r="AH4">
+        <v>0.0197215777262181</v>
+      </c>
+      <c r="AI4">
+        <v>0.0407673860911271</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.134989926124916</v>
+      </c>
+      <c r="AK4">
+        <v>-0.335559265442404</v>
+      </c>
+      <c r="AL4">
+        <v>0.127</v>
+      </c>
+      <c r="AM4">
+        <v>0.126</v>
+      </c>
+      <c r="AN4">
+        <v>-0.6710526315789473</v>
+      </c>
+      <c r="AO4">
+        <v>-21.02362204724409</v>
+      </c>
+      <c r="AP4">
+        <v>3.967105263157894</v>
+      </c>
+      <c r="AQ4">
+        <v>-21.19047619047619</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>Accordant Group Limited (NZSE:AGL)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NZSE:AGL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Business &amp; Consumer Services</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.255717255717256</v>
+      </c>
+      <c r="F2">
+        <v>0.09</v>
+      </c>
+      <c r="G2">
+        <v>35.8</v>
+      </c>
+      <c r="H2">
+        <v>41.270937920245</v>
+      </c>
+      <c r="I2">
+        <v>46.67</v>
+      </c>
+      <c r="J2">
+        <v>44.169937920245</v>
+      </c>
+      <c r="K2">
+        <v>12.3</v>
+      </c>
+      <c r="L2">
+        <v>4.329</v>
+      </c>
+      <c r="M2">
+        <v>0.0924673263657718</v>
+      </c>
+      <c r="N2">
+        <v>0.0964953408348071</v>
+      </c>
+      <c r="O2">
+        <v>0.034056</v>
+      </c>
+      <c r="P2">
+        <v>0.0396</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.112536022295911</v>
+      </c>
+      <c r="T2">
+        <v>0.102122352565722</v>
+      </c>
+      <c r="U2">
+        <v>1.24675390953763</v>
+      </c>
+      <c r="V2">
+        <v>1.07067601647414</v>
+      </c>
+      <c r="W2">
+        <v>4.620004620004622</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>35.8</v>
+      </c>
+      <c r="AB2">
+        <v>0.0591424031092525</v>
+      </c>
+      <c r="AC2">
+        <v>0.0473</v>
+      </c>
+      <c r="AD2">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>3.79</v>
+      </c>
+      <c r="AH2">
+        <v>2.69</v>
+      </c>
+      <c r="AI2">
+        <v>0.2300000000000005</v>
+      </c>
+      <c r="AJ2">
+        <v>12.3</v>
+      </c>
+      <c r="AK2">
+        <v>12.3</v>
+      </c>
+      <c r="AL2">
+        <v>0.678</v>
+      </c>
+      <c r="AM2">
+        <v>12.3</v>
+      </c>
+      <c r="AN2">
+        <v>1.43</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09791298813582996</v>
+      </c>
+      <c r="C2">
+        <v>44.78259322868563</v>
+      </c>
+      <c r="D2">
+        <v>43.35259322868563</v>
+      </c>
+      <c r="E2">
+        <v>-12.3</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1.43</v>
+      </c>
+      <c r="H2">
+        <v>35.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>3.79</v>
+      </c>
+      <c r="K2">
+        <v>2.69</v>
+      </c>
+      <c r="L2">
+        <v>1.1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.1</v>
+      </c>
+      <c r="O2">
+        <v>0.3079999999999999</v>
+      </c>
+      <c r="P2">
+        <v>0.7920000000000001</v>
+      </c>
+      <c r="Q2">
+        <v>3.482</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09791298813582996</v>
+      </c>
+      <c r="T2">
+        <v>0.9995026415587442</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W2">
+        <v>0.03290400000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09768851176904964</v>
+      </c>
+      <c r="C3">
+        <v>44.42899350124557</v>
+      </c>
+      <c r="D3">
+        <v>43.47999350124557</v>
+      </c>
+      <c r="E3">
+        <v>-11.819</v>
+      </c>
+      <c r="F3">
+        <v>0.4809999999999999</v>
+      </c>
+      <c r="G3">
+        <v>1.43</v>
+      </c>
+      <c r="H3">
+        <v>35.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>3.79</v>
+      </c>
+      <c r="K3">
+        <v>2.69</v>
+      </c>
+      <c r="L3">
+        <v>1.1</v>
+      </c>
+      <c r="M3">
+        <v>0.0219817</v>
+      </c>
+      <c r="N3">
+        <v>1.0780183</v>
+      </c>
+      <c r="O3">
+        <v>0.3018451239999999</v>
+      </c>
+      <c r="P3">
+        <v>0.7761731760000001</v>
+      </c>
+      <c r="Q3">
+        <v>3.466173176</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09834290077681782</v>
+      </c>
+      <c r="T3">
+        <v>1.006771751679171</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W3">
+        <v>0.03290400000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>50.04162553396689</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09746403540226932</v>
+      </c>
+      <c r="C4">
+        <v>44.07614476314011</v>
+      </c>
       <c r="D4">
-        <v>-0.0165</v>
+        <v>43.60814476314012</v>
       </c>
       <c r="E4">
-        <v>-0.0625</v>
+        <v>-11.338</v>
+      </c>
+      <c r="F4">
+        <v>0.9619999999999999</v>
       </c>
       <c r="G4">
-        <v>-0.06294765840220387</v>
+        <v>1.43</v>
       </c>
       <c r="H4">
-        <v>-0.06294765840220387</v>
+        <v>35.8</v>
       </c>
       <c r="I4">
-        <v>-0.1301652892561984</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>-0.09433696468820436</v>
+        <v>3.79</v>
       </c>
       <c r="K4">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="L4">
-        <v>0.01976584022038568</v>
+        <v>1.1</v>
       </c>
       <c r="M4">
-        <v>2.536</v>
+        <v>0.0439634</v>
       </c>
       <c r="N4">
-        <v>0.06155339805825243</v>
+        <v>1.0560366</v>
       </c>
       <c r="O4">
-        <v>0.883623693379791</v>
+        <v>0.2956902479999999</v>
       </c>
       <c r="P4">
-        <v>1.98</v>
+        <v>0.7603463520000002</v>
       </c>
       <c r="Q4">
-        <v>0.04805825242718446</v>
+        <v>3.450346352</v>
       </c>
       <c r="R4">
-        <v>0.6898954703832753</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.556</v>
+        <v>0.09878158714517277</v>
       </c>
       <c r="T4">
-        <v>0.2192429022082019</v>
+        <v>1.01418921098573</v>
       </c>
       <c r="U4">
-        <v>3.45</v>
+        <v>0.0457</v>
       </c>
       <c r="V4">
-        <v>0.08373786407766991</v>
+        <v>0.2799999999999999</v>
       </c>
       <c r="W4">
-        <v>0.1161943319838057</v>
-      </c>
-      <c r="X4">
-        <v>0.07006045441040232</v>
+        <v>0.03290400000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y4">
-        <v>0.04613387757340336</v>
+        <v>25.02081276698345</v>
       </c>
       <c r="Z4">
-        <v>11.69082125603865</v>
-      </c>
-      <c r="AA4">
-        <v>-1.102876592007027</v>
-      </c>
-      <c r="AB4">
-        <v>0.0534973555674238</v>
-      </c>
-      <c r="AC4">
-        <v>-1.156373947574451</v>
-      </c>
-      <c r="AD4">
-        <v>18.6</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>18.6</v>
-      </c>
-      <c r="AG4">
-        <v>15.15</v>
-      </c>
-      <c r="AH4">
-        <v>0.3110367892976589</v>
-      </c>
-      <c r="AI4">
-        <v>0.4142538975501113</v>
-      </c>
-      <c r="AJ4">
-        <v>0.2688553682342502</v>
-      </c>
-      <c r="AK4">
-        <v>0.3655006031363088</v>
-      </c>
-      <c r="AL4">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="AM4">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="AN4">
-        <v>-1.07514450867052</v>
-      </c>
-      <c r="AO4">
-        <v>-27.3121387283237</v>
-      </c>
-      <c r="AP4">
-        <v>-0.8757225433526012</v>
-      </c>
-      <c r="AQ4">
-        <v>-27.3121387283237</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09723955903548899</v>
+      </c>
+      <c r="C5">
+        <v>43.72405367430985</v>
+      </c>
+      <c r="D5">
+        <v>43.73705367430985</v>
+      </c>
+      <c r="E5">
+        <v>-10.857</v>
+      </c>
+      <c r="F5">
+        <v>1.443</v>
+      </c>
+      <c r="G5">
+        <v>1.43</v>
+      </c>
+      <c r="H5">
+        <v>35.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>3.79</v>
+      </c>
+      <c r="K5">
+        <v>2.69</v>
+      </c>
+      <c r="L5">
+        <v>1.1</v>
+      </c>
+      <c r="M5">
+        <v>0.06594509999999999</v>
+      </c>
+      <c r="N5">
+        <v>1.0340549</v>
+      </c>
+      <c r="O5">
+        <v>0.289535372</v>
+      </c>
+      <c r="P5">
+        <v>0.7445195280000001</v>
+      </c>
+      <c r="Q5">
+        <v>3.434519528</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09922931859328762</v>
+      </c>
+      <c r="T5">
+        <v>1.021759607597578</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W5">
+        <v>0.03290400000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>16.68054184465564</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09706116266870868</v>
+      </c>
+      <c r="C6">
+        <v>43.34604525031945</v>
+      </c>
+      <c r="D6">
+        <v>43.84004525031945</v>
+      </c>
+      <c r="E6">
+        <v>-10.376</v>
+      </c>
+      <c r="F6">
+        <v>1.924</v>
+      </c>
+      <c r="G6">
+        <v>1.43</v>
+      </c>
+      <c r="H6">
+        <v>35.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3.79</v>
+      </c>
+      <c r="K6">
+        <v>2.69</v>
+      </c>
+      <c r="L6">
+        <v>1.1</v>
+      </c>
+      <c r="M6">
+        <v>0.09100519999999999</v>
+      </c>
+      <c r="N6">
+        <v>1.0089948</v>
+      </c>
+      <c r="O6">
+        <v>0.282518544</v>
+      </c>
+      <c r="P6">
+        <v>0.7264762560000002</v>
+      </c>
+      <c r="Q6">
+        <v>3.416476256</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09968637777990487</v>
+      </c>
+      <c r="T6">
+        <v>1.029487720805507</v>
+      </c>
+      <c r="U6">
+        <v>0.0473</v>
+      </c>
+      <c r="V6">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W6">
+        <v>0.034056</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>12.08722138954697</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09698500630192833</v>
+      </c>
+      <c r="C7">
+        <v>42.90915963012399</v>
+      </c>
+      <c r="D7">
+        <v>43.884159630124</v>
+      </c>
+      <c r="E7">
+        <v>-9.895000000000001</v>
+      </c>
+      <c r="F7">
+        <v>2.405</v>
+      </c>
+      <c r="G7">
+        <v>1.43</v>
+      </c>
+      <c r="H7">
+        <v>35.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3.79</v>
+      </c>
+      <c r="K7">
+        <v>2.69</v>
+      </c>
+      <c r="L7">
+        <v>1.1</v>
+      </c>
+      <c r="M7">
+        <v>0.1228955</v>
+      </c>
+      <c r="N7">
+        <v>0.9771045</v>
+      </c>
+      <c r="O7">
+        <v>0.2735892599999999</v>
+      </c>
+      <c r="P7">
+        <v>0.7035152400000001</v>
+      </c>
+      <c r="Q7">
+        <v>3.39351524</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1001530592651877</v>
+      </c>
+      <c r="T7">
+        <v>1.037378531133602</v>
+      </c>
+      <c r="U7">
+        <v>0.0511</v>
+      </c>
+      <c r="V7">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W7">
+        <v>0.03679200000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>8.950693882200731</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09688148993514803</v>
+      </c>
+      <c r="C8">
+        <v>42.48826512736373</v>
+      </c>
+      <c r="D8">
+        <v>43.94426512736373</v>
+      </c>
+      <c r="E8">
+        <v>-9.414000000000001</v>
+      </c>
+      <c r="F8">
+        <v>2.886</v>
+      </c>
+      <c r="G8">
+        <v>1.43</v>
+      </c>
+      <c r="H8">
+        <v>35.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>3.79</v>
+      </c>
+      <c r="K8">
+        <v>2.69</v>
+      </c>
+      <c r="L8">
+        <v>1.1</v>
+      </c>
+      <c r="M8">
+        <v>0.152958</v>
+      </c>
+      <c r="N8">
+        <v>0.9470420000000001</v>
+      </c>
+      <c r="O8">
+        <v>0.2651717599999999</v>
+      </c>
+      <c r="P8">
+        <v>0.6818702400000001</v>
+      </c>
+      <c r="Q8">
+        <v>3.37187024</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1006296701437745</v>
+      </c>
+      <c r="T8">
+        <v>1.045437231043146</v>
+      </c>
+      <c r="U8">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V8">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W8">
+        <v>0.03816000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>7.191516625478889</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09681037356836769</v>
+      </c>
+      <c r="C9">
+        <v>42.04865346630341</v>
+      </c>
+      <c r="D9">
+        <v>43.98565346630341</v>
+      </c>
+      <c r="E9">
+        <v>-8.933</v>
+      </c>
+      <c r="F9">
+        <v>3.367</v>
+      </c>
+      <c r="G9">
+        <v>1.43</v>
+      </c>
+      <c r="H9">
+        <v>35.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>3.79</v>
+      </c>
+      <c r="K9">
+        <v>2.69</v>
+      </c>
+      <c r="L9">
+        <v>1.1</v>
+      </c>
+      <c r="M9">
+        <v>0.185185</v>
+      </c>
+      <c r="N9">
+        <v>0.9148150000000002</v>
+      </c>
+      <c r="O9">
+        <v>0.2561482</v>
+      </c>
+      <c r="P9">
+        <v>0.6586668000000002</v>
+      </c>
+      <c r="Q9">
+        <v>3.3486668</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1011165307186749</v>
+      </c>
+      <c r="T9">
+        <v>1.053669236327089</v>
+      </c>
+      <c r="U9">
+        <v>0.055</v>
+      </c>
+      <c r="V9">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W9">
+        <v>0.0396</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>5.940005940005941</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09665285720158738</v>
+      </c>
+      <c r="C10">
+        <v>41.65960307497609</v>
+      </c>
+      <c r="D10">
+        <v>44.07760307497609</v>
+      </c>
+      <c r="E10">
+        <v>-8.452000000000002</v>
+      </c>
+      <c r="F10">
+        <v>3.847999999999999</v>
+      </c>
+      <c r="G10">
+        <v>1.43</v>
+      </c>
+      <c r="H10">
+        <v>35.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>3.79</v>
+      </c>
+      <c r="K10">
+        <v>2.69</v>
+      </c>
+      <c r="L10">
+        <v>1.1</v>
+      </c>
+      <c r="M10">
+        <v>0.21164</v>
+      </c>
+      <c r="N10">
+        <v>0.8883600000000001</v>
+      </c>
+      <c r="O10">
+        <v>0.2487408</v>
+      </c>
+      <c r="P10">
+        <v>0.6396192000000002</v>
+      </c>
+      <c r="Q10">
+        <v>3.3296192</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1016139752191167</v>
+      </c>
+      <c r="T10">
+        <v>1.06208019824764</v>
+      </c>
+      <c r="U10">
+        <v>0.055</v>
+      </c>
+      <c r="V10">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W10">
+        <v>0.0396</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>5.197505197505198</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09649534083480706</v>
+      </c>
+      <c r="C11">
+        <v>41.270937920245</v>
+      </c>
+      <c r="D11">
+        <v>44.169937920245</v>
+      </c>
+      <c r="E11">
+        <v>-7.971000000000001</v>
+      </c>
+      <c r="F11">
+        <v>4.329</v>
+      </c>
+      <c r="G11">
+        <v>1.43</v>
+      </c>
+      <c r="H11">
+        <v>35.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3.79</v>
+      </c>
+      <c r="K11">
+        <v>2.69</v>
+      </c>
+      <c r="L11">
+        <v>1.1</v>
+      </c>
+      <c r="M11">
+        <v>0.238095</v>
+      </c>
+      <c r="N11">
+        <v>0.8619050000000001</v>
+      </c>
+      <c r="O11">
+        <v>0.2413334</v>
+      </c>
+      <c r="P11">
+        <v>0.6205716000000001</v>
+      </c>
+      <c r="Q11">
+        <v>3.3105716</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.102122352565722</v>
+      </c>
+      <c r="T11">
+        <v>1.070676016474136</v>
+      </c>
+      <c r="U11">
+        <v>0.055</v>
+      </c>
+      <c r="V11">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W11">
+        <v>0.0396</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>4.620004620004622</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.09691382446802672</v>
+      </c>
+      <c r="C12">
+        <v>40.54547280630299</v>
+      </c>
+      <c r="D12">
+        <v>43.92547280630299</v>
+      </c>
+      <c r="E12">
+        <v>-7.490000000000001</v>
+      </c>
+      <c r="F12">
+        <v>4.81</v>
+      </c>
+      <c r="G12">
+        <v>1.43</v>
+      </c>
+      <c r="H12">
+        <v>35.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>3.79</v>
+      </c>
+      <c r="K12">
+        <v>2.69</v>
+      </c>
+      <c r="L12">
+        <v>1.1</v>
+      </c>
+      <c r="M12">
+        <v>0.30303</v>
+      </c>
+      <c r="N12">
+        <v>0.7969700000000002</v>
+      </c>
+      <c r="O12">
+        <v>0.2231516</v>
+      </c>
+      <c r="P12">
+        <v>0.5738184000000002</v>
+      </c>
+      <c r="Q12">
+        <v>3.2638184</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1026420271866964</v>
+      </c>
+      <c r="T12">
+        <v>1.079462852883444</v>
+      </c>
+      <c r="U12">
+        <v>0.063</v>
+      </c>
+      <c r="V12">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W12">
+        <v>0.04536</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>3.630003630003631</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.09906318810124641</v>
+      </c>
+      <c r="C13">
+        <v>38.85034400850842</v>
+      </c>
+      <c r="D13">
+        <v>42.71134400850842</v>
+      </c>
+      <c r="E13">
+        <v>-7.009000000000001</v>
+      </c>
+      <c r="F13">
+        <v>5.290999999999999</v>
+      </c>
+      <c r="G13">
+        <v>1.43</v>
+      </c>
+      <c r="H13">
+        <v>35.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>3.79</v>
+      </c>
+      <c r="K13">
+        <v>2.69</v>
+      </c>
+      <c r="L13">
+        <v>1.1</v>
+      </c>
+      <c r="M13">
+        <v>0.4835974</v>
+      </c>
+      <c r="N13">
+        <v>0.6164026</v>
+      </c>
+      <c r="O13">
+        <v>0.1725927279999999</v>
+      </c>
+      <c r="P13">
+        <v>0.4438098720000001</v>
+      </c>
+      <c r="Q13">
+        <v>3.133809872</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1031733798890409</v>
+      </c>
+      <c r="T13">
+        <v>1.088447146290713</v>
+      </c>
+      <c r="U13">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V13">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W13">
+        <v>0.06580800000000002</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>2.274619342453041</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09916775173446607</v>
+      </c>
+      <c r="C14">
+        <v>38.31198802560001</v>
+      </c>
+      <c r="D14">
+        <v>42.65398802560001</v>
+      </c>
+      <c r="E14">
+        <v>-6.528000000000001</v>
+      </c>
+      <c r="F14">
+        <v>5.771999999999999</v>
+      </c>
+      <c r="G14">
+        <v>1.43</v>
+      </c>
+      <c r="H14">
+        <v>35.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>3.79</v>
+      </c>
+      <c r="K14">
+        <v>2.69</v>
+      </c>
+      <c r="L14">
+        <v>1.1</v>
+      </c>
+      <c r="M14">
+        <v>0.5275607999999999</v>
+      </c>
+      <c r="N14">
+        <v>0.5724392000000001</v>
+      </c>
+      <c r="O14">
+        <v>0.160282976</v>
+      </c>
+      <c r="P14">
+        <v>0.4121562240000002</v>
+      </c>
+      <c r="Q14">
+        <v>3.102156224</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.103716808789166</v>
+      </c>
+      <c r="T14">
+        <v>1.097635628184512</v>
+      </c>
+      <c r="U14">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V14">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W14">
+        <v>0.06580800000000002</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>2.085067730581954</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1012472753676858</v>
+      </c>
+      <c r="C15">
+        <v>36.72147610918567</v>
+      </c>
+      <c r="D15">
+        <v>41.54447610918567</v>
+      </c>
+      <c r="E15">
+        <v>-6.047000000000001</v>
+      </c>
+      <c r="F15">
+        <v>6.252999999999999</v>
+      </c>
+      <c r="G15">
+        <v>1.43</v>
+      </c>
+      <c r="H15">
+        <v>35.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>3.79</v>
+      </c>
+      <c r="K15">
+        <v>2.69</v>
+      </c>
+      <c r="L15">
+        <v>1.1</v>
+      </c>
+      <c r="M15">
+        <v>0.7034624999999999</v>
+      </c>
+      <c r="N15">
+        <v>0.3965375000000002</v>
+      </c>
+      <c r="O15">
+        <v>0.1110305</v>
+      </c>
+      <c r="P15">
+        <v>0.2855070000000002</v>
+      </c>
+      <c r="Q15">
+        <v>2.975507</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1042727303076848</v>
+      </c>
+      <c r="T15">
+        <v>1.107035339547134</v>
+      </c>
+      <c r="U15">
+        <v>0.1125</v>
+      </c>
+      <c r="V15">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W15">
+        <v>0.08100000000000002</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>1.563693871386179</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1116763323443567</v>
+      </c>
+      <c r="C16">
+        <v>31.44629596313457</v>
+      </c>
+      <c r="D16">
+        <v>36.75029596313457</v>
+      </c>
+      <c r="E16">
+        <v>-5.566000000000001</v>
+      </c>
+      <c r="F16">
+        <v>6.734</v>
+      </c>
+      <c r="G16">
+        <v>1.43</v>
+      </c>
+      <c r="H16">
+        <v>35.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3.79</v>
+      </c>
+      <c r="K16">
+        <v>2.69</v>
+      </c>
+      <c r="L16">
+        <v>1.1</v>
+      </c>
+      <c r="M16">
+        <v>1.3239044</v>
+      </c>
+      <c r="N16">
+        <v>-0.2239043999999999</v>
+      </c>
+      <c r="O16">
+        <v>-0.06269323199999995</v>
+      </c>
+      <c r="P16">
+        <v>-0.161211168</v>
+      </c>
+      <c r="Q16">
+        <v>2.528788832</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.105297277613585</v>
+      </c>
+      <c r="T16">
+        <v>1.124358736163391</v>
+      </c>
+      <c r="U16">
+        <v>0.1966</v>
+      </c>
+      <c r="V16">
+        <v>0.232645197039907</v>
+      </c>
+      <c r="W16">
+        <v>0.1508619542619543</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.830875703713954</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1159892232025238</v>
+      </c>
+      <c r="C17">
+        <v>29.29135937811369</v>
+      </c>
+      <c r="D17">
+        <v>35.07635937811369</v>
+      </c>
+      <c r="E17">
+        <v>-5.085000000000002</v>
+      </c>
+      <c r="F17">
+        <v>7.214999999999999</v>
+      </c>
+      <c r="G17">
+        <v>1.43</v>
+      </c>
+      <c r="H17">
+        <v>35.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>3.79</v>
+      </c>
+      <c r="K17">
+        <v>2.69</v>
+      </c>
+      <c r="L17">
+        <v>1.1</v>
+      </c>
+      <c r="M17">
+        <v>1.542567</v>
+      </c>
+      <c r="N17">
+        <v>-0.4425669999999997</v>
+      </c>
+      <c r="O17">
+        <v>-0.1239187599999999</v>
+      </c>
+      <c r="P17">
+        <v>-0.3186482399999998</v>
+      </c>
+      <c r="Q17">
+        <v>2.37135176</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1062618230657061</v>
+      </c>
+      <c r="T17">
+        <v>1.140667600893479</v>
+      </c>
+      <c r="U17">
+        <v>0.2138</v>
+      </c>
+      <c r="V17">
+        <v>0.1996671781517431</v>
+      </c>
+      <c r="W17">
+        <v>0.1711111573111573</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.7130970648276543</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1177392232025238</v>
+      </c>
+      <c r="C18">
+        <v>28.17384397707283</v>
+      </c>
+      <c r="D18">
+        <v>34.43984397707283</v>
+      </c>
+      <c r="E18">
+        <v>-4.604000000000002</v>
+      </c>
+      <c r="F18">
+        <v>7.695999999999999</v>
+      </c>
+      <c r="G18">
+        <v>1.43</v>
+      </c>
+      <c r="H18">
+        <v>35.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>3.79</v>
+      </c>
+      <c r="K18">
+        <v>2.69</v>
+      </c>
+      <c r="L18">
+        <v>1.1</v>
+      </c>
+      <c r="M18">
+        <v>1.6454048</v>
+      </c>
+      <c r="N18">
+        <v>-0.5454047999999996</v>
+      </c>
+      <c r="O18">
+        <v>-0.1527133439999998</v>
+      </c>
+      <c r="P18">
+        <v>-0.3926914559999998</v>
+      </c>
+      <c r="Q18">
+        <v>2.297308544</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1070649400069645</v>
+      </c>
+      <c r="T18">
+        <v>1.154246977094592</v>
+      </c>
+      <c r="U18">
+        <v>0.2138</v>
+      </c>
+      <c r="V18">
+        <v>0.1871879795172592</v>
+      </c>
+      <c r="W18">
+        <v>0.17377920997921</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.668528498275926</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1194892232025238</v>
+      </c>
+      <c r="C19">
+        <v>27.0790179763263</v>
+      </c>
+      <c r="D19">
+        <v>33.8260179763263</v>
+      </c>
+      <c r="E19">
+        <v>-4.123000000000001</v>
+      </c>
+      <c r="F19">
+        <v>8.177</v>
+      </c>
+      <c r="G19">
+        <v>1.43</v>
+      </c>
+      <c r="H19">
+        <v>35.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>3.79</v>
+      </c>
+      <c r="K19">
+        <v>2.69</v>
+      </c>
+      <c r="L19">
+        <v>1.1</v>
+      </c>
+      <c r="M19">
+        <v>1.7482426</v>
+      </c>
+      <c r="N19">
+        <v>-0.6482425999999997</v>
+      </c>
+      <c r="O19">
+        <v>-0.1815079279999998</v>
+      </c>
+      <c r="P19">
+        <v>-0.4667346719999999</v>
+      </c>
+      <c r="Q19">
+        <v>2.223265328</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1078874091636749</v>
+      </c>
+      <c r="T19">
+        <v>1.168153567180069</v>
+      </c>
+      <c r="U19">
+        <v>0.2138</v>
+      </c>
+      <c r="V19">
+        <v>0.1761769218985969</v>
+      </c>
+      <c r="W19">
+        <v>0.17613337409808</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.6292032924949891</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1212392232025238</v>
+      </c>
+      <c r="C20">
+        <v>26.00568943130584</v>
+      </c>
+      <c r="D20">
+        <v>33.23368943130584</v>
+      </c>
+      <c r="E20">
+        <v>-3.642000000000001</v>
+      </c>
+      <c r="F20">
+        <v>8.657999999999999</v>
+      </c>
+      <c r="G20">
+        <v>1.43</v>
+      </c>
+      <c r="H20">
+        <v>35.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>3.79</v>
+      </c>
+      <c r="K20">
+        <v>2.69</v>
+      </c>
+      <c r="L20">
+        <v>1.1</v>
+      </c>
+      <c r="M20">
+        <v>1.8510804</v>
+      </c>
+      <c r="N20">
+        <v>-0.7510803999999998</v>
+      </c>
+      <c r="O20">
+        <v>-0.2103025119999999</v>
+      </c>
+      <c r="P20">
+        <v>-0.5407778879999999</v>
+      </c>
+      <c r="Q20">
+        <v>2.149222112</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1087299385437197</v>
+      </c>
+      <c r="T20">
+        <v>1.182399342389582</v>
+      </c>
+      <c r="U20">
+        <v>0.2138</v>
+      </c>
+      <c r="V20">
+        <v>0.1663893151264526</v>
+      </c>
+      <c r="W20">
+        <v>0.1782259644259644</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.5942475540230452</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1229892232025238</v>
+      </c>
+      <c r="C21">
+        <v>24.95274844935604</v>
+      </c>
+      <c r="D21">
+        <v>32.66174844935604</v>
+      </c>
+      <c r="E21">
+        <v>-3.161000000000001</v>
+      </c>
+      <c r="F21">
+        <v>9.138999999999999</v>
+      </c>
+      <c r="G21">
+        <v>1.43</v>
+      </c>
+      <c r="H21">
+        <v>35.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3.79</v>
+      </c>
+      <c r="K21">
+        <v>2.69</v>
+      </c>
+      <c r="L21">
+        <v>1.1</v>
+      </c>
+      <c r="M21">
+        <v>1.9539182</v>
+      </c>
+      <c r="N21">
+        <v>-0.8539181999999996</v>
+      </c>
+      <c r="O21">
+        <v>-0.2390970959999998</v>
+      </c>
+      <c r="P21">
+        <v>-0.6148211039999998</v>
+      </c>
+      <c r="Q21">
+        <v>2.075178896</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1095932711183335</v>
+      </c>
+      <c r="T21">
+        <v>1.196996865135132</v>
+      </c>
+      <c r="U21">
+        <v>0.2138</v>
+      </c>
+      <c r="V21">
+        <v>0.1576319827513762</v>
+      </c>
+      <c r="W21">
+        <v>0.1800982820877558</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.5629713669692008</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1247392232025238</v>
+      </c>
+      <c r="C22">
+        <v>23.91916024875272</v>
+      </c>
+      <c r="D22">
+        <v>32.10916024875272</v>
+      </c>
+      <c r="E22">
+        <v>-2.680000000000001</v>
+      </c>
+      <c r="F22">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="G22">
+        <v>1.43</v>
+      </c>
+      <c r="H22">
+        <v>35.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>3.79</v>
+      </c>
+      <c r="K22">
+        <v>2.69</v>
+      </c>
+      <c r="L22">
+        <v>1.1</v>
+      </c>
+      <c r="M22">
+        <v>2.056756</v>
+      </c>
+      <c r="N22">
+        <v>-0.9567559999999995</v>
+      </c>
+      <c r="O22">
+        <v>-0.2678916799999998</v>
+      </c>
+      <c r="P22">
+        <v>-0.6888643199999998</v>
+      </c>
+      <c r="Q22">
+        <v>2.00113568</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1104781870073127</v>
+      </c>
+      <c r="T22">
+        <v>1.211959325949321</v>
+      </c>
+      <c r="U22">
+        <v>0.2138</v>
+      </c>
+      <c r="V22">
+        <v>0.1497503836138074</v>
+      </c>
+      <c r="W22">
+        <v>0.181783367983368</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.5348227986207408</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1264892232025238</v>
+      </c>
+      <c r="C23">
+        <v>22.9039589105856</v>
+      </c>
+      <c r="D23">
+        <v>31.5749589105856</v>
+      </c>
+      <c r="E23">
+        <v>-2.199000000000002</v>
+      </c>
+      <c r="F23">
+        <v>10.101</v>
+      </c>
+      <c r="G23">
+        <v>1.43</v>
+      </c>
+      <c r="H23">
+        <v>35.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3.79</v>
+      </c>
+      <c r="K23">
+        <v>2.69</v>
+      </c>
+      <c r="L23">
+        <v>1.1</v>
+      </c>
+      <c r="M23">
+        <v>2.1595938</v>
+      </c>
+      <c r="N23">
+        <v>-1.0595938</v>
+      </c>
+      <c r="O23">
+        <v>-0.2966862639999998</v>
+      </c>
+      <c r="P23">
+        <v>-0.7629075359999997</v>
+      </c>
+      <c r="Q23">
+        <v>1.927092464</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1113855058301901</v>
+      </c>
+      <c r="T23">
+        <v>1.227300583239819</v>
+      </c>
+      <c r="U23">
+        <v>0.2138</v>
+      </c>
+      <c r="V23">
+        <v>0.1426194129655308</v>
+      </c>
+      <c r="W23">
+        <v>0.1833079695079695</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.5093550463054674</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1339245706198165</v>
+      </c>
+      <c r="C24">
+        <v>20.33837430636366</v>
+      </c>
+      <c r="D24">
+        <v>29.49037430636366</v>
+      </c>
+      <c r="E24">
+        <v>-1.718000000000002</v>
+      </c>
+      <c r="F24">
+        <v>10.582</v>
+      </c>
+      <c r="G24">
+        <v>1.43</v>
+      </c>
+      <c r="H24">
+        <v>35.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>3.79</v>
+      </c>
+      <c r="K24">
+        <v>2.69</v>
+      </c>
+      <c r="L24">
+        <v>1.1</v>
+      </c>
+      <c r="M24">
+        <v>2.5269816</v>
+      </c>
+      <c r="N24">
+        <v>-1.4269816</v>
+      </c>
+      <c r="O24">
+        <v>-0.3995548479999999</v>
+      </c>
+      <c r="P24">
+        <v>-1.027426752</v>
+      </c>
+      <c r="Q24">
+        <v>1.662573248</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1125537141322344</v>
+      </c>
+      <c r="T24">
+        <v>1.247053049163234</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.1218845439950967</v>
+      </c>
+      <c r="W24">
+        <v>0.2096939708939709</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.4353019428396313</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1359245706198164</v>
+      </c>
+      <c r="C25">
+        <v>19.34280838223255</v>
+      </c>
+      <c r="D25">
+        <v>28.97580838223255</v>
+      </c>
+      <c r="E25">
+        <v>-1.237000000000002</v>
+      </c>
+      <c r="F25">
+        <v>11.063</v>
+      </c>
+      <c r="G25">
+        <v>1.43</v>
+      </c>
+      <c r="H25">
+        <v>35.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>3.79</v>
+      </c>
+      <c r="K25">
+        <v>2.69</v>
+      </c>
+      <c r="L25">
+        <v>1.1</v>
+      </c>
+      <c r="M25">
+        <v>2.6418444</v>
+      </c>
+      <c r="N25">
+        <v>-1.5418444</v>
+      </c>
+      <c r="O25">
+        <v>-0.4317164319999998</v>
+      </c>
+      <c r="P25">
+        <v>-1.110127968</v>
+      </c>
+      <c r="Q25">
+        <v>1.579872032</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1135115545755102</v>
+      </c>
+      <c r="T25">
+        <v>1.263248543308211</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.1165852159953099</v>
+      </c>
+      <c r="W25">
+        <v>0.21095945042032</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.4163757714118214</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1379245706198164</v>
+      </c>
+      <c r="C26">
+        <v>18.3648914244545</v>
+      </c>
+      <c r="D26">
+        <v>28.4788914244545</v>
+      </c>
+      <c r="E26">
+        <v>-0.756000000000002</v>
+      </c>
+      <c r="F26">
+        <v>11.544</v>
+      </c>
+      <c r="G26">
+        <v>1.43</v>
+      </c>
+      <c r="H26">
+        <v>35.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>3.79</v>
+      </c>
+      <c r="K26">
+        <v>2.69</v>
+      </c>
+      <c r="L26">
+        <v>1.1</v>
+      </c>
+      <c r="M26">
+        <v>2.7567072</v>
+      </c>
+      <c r="N26">
+        <v>-1.6567072</v>
+      </c>
+      <c r="O26">
+        <v>-0.4638780159999997</v>
+      </c>
+      <c r="P26">
+        <v>-1.192829184</v>
+      </c>
+      <c r="Q26">
+        <v>1.497170816</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1144946013462406</v>
+      </c>
+      <c r="T26">
+        <v>1.279870234667529</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.111727498662172</v>
+      </c>
+      <c r="W26">
+        <v>0.2121194733194733</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.3990267809363287</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1399245706198164</v>
+      </c>
+      <c r="C27">
+        <v>17.40373073608002</v>
+      </c>
+      <c r="D27">
+        <v>27.99873073608002</v>
+      </c>
+      <c r="E27">
+        <v>-0.2750000000000021</v>
+      </c>
+      <c r="F27">
+        <v>12.025</v>
+      </c>
+      <c r="G27">
+        <v>1.43</v>
+      </c>
+      <c r="H27">
+        <v>35.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>3.79</v>
+      </c>
+      <c r="K27">
+        <v>2.69</v>
+      </c>
+      <c r="L27">
+        <v>1.1</v>
+      </c>
+      <c r="M27">
+        <v>2.87157</v>
+      </c>
+      <c r="N27">
+        <v>-1.77157</v>
+      </c>
+      <c r="O27">
+        <v>-0.4960395999999997</v>
+      </c>
+      <c r="P27">
+        <v>-1.2755304</v>
+      </c>
+      <c r="Q27">
+        <v>1.4144696</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1155038626975238</v>
+      </c>
+      <c r="T27">
+        <v>1.296935171129763</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.1072583987156851</v>
+      </c>
+      <c r="W27">
+        <v>0.2131866943866944</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.3830657096988755</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1419245706198164</v>
+      </c>
+      <c r="C28">
+        <v>16.45849282623863</v>
+      </c>
+      <c r="D28">
+        <v>27.53449282623863</v>
+      </c>
+      <c r="E28">
+        <v>0.2059999999999977</v>
+      </c>
+      <c r="F28">
+        <v>12.506</v>
+      </c>
+      <c r="G28">
+        <v>1.43</v>
+      </c>
+      <c r="H28">
+        <v>35.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>3.79</v>
+      </c>
+      <c r="K28">
+        <v>2.69</v>
+      </c>
+      <c r="L28">
+        <v>1.1</v>
+      </c>
+      <c r="M28">
+        <v>2.9864328</v>
+      </c>
+      <c r="N28">
+        <v>-1.8864328</v>
+      </c>
+      <c r="O28">
+        <v>-0.5282011839999997</v>
+      </c>
+      <c r="P28">
+        <v>-1.358231616</v>
+      </c>
+      <c r="Q28">
+        <v>1.331768384</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1165404013826255</v>
+      </c>
+      <c r="T28">
+        <v>1.314461322090976</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.1031330756881588</v>
+      </c>
+      <c r="W28">
+        <v>0.2141718215256677</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.3683324131719957</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1439245706198165</v>
+      </c>
+      <c r="C29">
+        <v>15.52839858181139</v>
+      </c>
+      <c r="D29">
+        <v>27.08539858181139</v>
+      </c>
+      <c r="E29">
+        <v>0.6869999999999994</v>
+      </c>
+      <c r="F29">
+        <v>12.987</v>
+      </c>
+      <c r="G29">
+        <v>1.43</v>
+      </c>
+      <c r="H29">
+        <v>35.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>3.79</v>
+      </c>
+      <c r="K29">
+        <v>2.69</v>
+      </c>
+      <c r="L29">
+        <v>1.1</v>
+      </c>
+      <c r="M29">
+        <v>3.1012956</v>
+      </c>
+      <c r="N29">
+        <v>-2.0012956</v>
+      </c>
+      <c r="O29">
+        <v>-0.5603627679999998</v>
+      </c>
+      <c r="P29">
+        <v>-1.440932832</v>
+      </c>
+      <c r="Q29">
+        <v>1.249067168</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1176053383878669</v>
+      </c>
+      <c r="T29">
+        <v>1.332467641571674</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.09931333214415287</v>
+      </c>
+      <c r="W29">
+        <v>0.2150839762839763</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.3546904719434033</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1459245706198165</v>
+      </c>
+      <c r="C30">
+        <v>14.6127189040277</v>
+      </c>
+      <c r="D30">
+        <v>26.6507189040277</v>
+      </c>
+      <c r="E30">
+        <v>1.167999999999999</v>
+      </c>
+      <c r="F30">
+        <v>13.468</v>
+      </c>
+      <c r="G30">
+        <v>1.43</v>
+      </c>
+      <c r="H30">
+        <v>35.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>3.79</v>
+      </c>
+      <c r="K30">
+        <v>2.69</v>
+      </c>
+      <c r="L30">
+        <v>1.1</v>
+      </c>
+      <c r="M30">
+        <v>3.2161584</v>
+      </c>
+      <c r="N30">
+        <v>-2.1161584</v>
+      </c>
+      <c r="O30">
+        <v>-0.5925243519999999</v>
+      </c>
+      <c r="P30">
+        <v>-1.523634048</v>
+      </c>
+      <c r="Q30">
+        <v>1.166365952</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1186998569765873</v>
+      </c>
+      <c r="T30">
+        <v>1.350974136593503</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.09576642742471886</v>
+      </c>
+      <c r="W30">
+        <v>0.2159309771309771</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.3420229550882817</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1479245706198165</v>
+      </c>
+      <c r="C31">
+        <v>13.71077075858166</v>
+      </c>
+      <c r="D31">
+        <v>26.22977075858166</v>
+      </c>
+      <c r="E31">
+        <v>1.648999999999997</v>
+      </c>
+      <c r="F31">
+        <v>13.949</v>
+      </c>
+      <c r="G31">
+        <v>1.43</v>
+      </c>
+      <c r="H31">
+        <v>35.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>3.79</v>
+      </c>
+      <c r="K31">
+        <v>2.69</v>
+      </c>
+      <c r="L31">
+        <v>1.1</v>
+      </c>
+      <c r="M31">
+        <v>3.3310212</v>
+      </c>
+      <c r="N31">
+        <v>-2.2310212</v>
+      </c>
+      <c r="O31">
+        <v>-0.6246859359999998</v>
+      </c>
+      <c r="P31">
+        <v>-1.606335264</v>
+      </c>
+      <c r="Q31">
+        <v>1.083664736</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1198252070748491</v>
+      </c>
+      <c r="T31">
+        <v>1.370001941334257</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.09246413682386649</v>
+      </c>
+      <c r="W31">
+        <v>0.2167195641264607</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.3302290600852376</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1499245706198165</v>
+      </c>
+      <c r="C32">
+        <v>12.82191359425847</v>
+      </c>
+      <c r="D32">
+        <v>25.82191359425847</v>
+      </c>
+      <c r="E32">
+        <v>2.129999999999997</v>
+      </c>
+      <c r="F32">
+        <v>14.43</v>
+      </c>
+      <c r="G32">
+        <v>1.43</v>
+      </c>
+      <c r="H32">
+        <v>35.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>3.79</v>
+      </c>
+      <c r="K32">
+        <v>2.69</v>
+      </c>
+      <c r="L32">
+        <v>1.1</v>
+      </c>
+      <c r="M32">
+        <v>3.445884</v>
+      </c>
+      <c r="N32">
+        <v>-2.345883999999999</v>
+      </c>
+      <c r="O32">
+        <v>-0.6568475199999997</v>
+      </c>
+      <c r="P32">
+        <v>-1.68903648</v>
+      </c>
+      <c r="Q32">
+        <v>1.00096352</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1209827100330612</v>
+      </c>
+      <c r="T32">
+        <v>1.389573397639032</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.08938199892973761</v>
+      </c>
+      <c r="W32">
+        <v>0.2174555786555787</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.319221424749063</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1519245706198165</v>
+      </c>
+      <c r="C33">
+        <v>11.94554609057408</v>
+      </c>
+      <c r="D33">
+        <v>25.42654609057408</v>
+      </c>
+      <c r="E33">
+        <v>2.610999999999997</v>
+      </c>
+      <c r="F33">
+        <v>14.911</v>
+      </c>
+      <c r="G33">
+        <v>1.43</v>
+      </c>
+      <c r="H33">
+        <v>35.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>3.79</v>
+      </c>
+      <c r="K33">
+        <v>2.69</v>
+      </c>
+      <c r="L33">
+        <v>1.1</v>
+      </c>
+      <c r="M33">
+        <v>3.5607468</v>
+      </c>
+      <c r="N33">
+        <v>-2.460746799999999</v>
+      </c>
+      <c r="O33">
+        <v>-0.6890091039999996</v>
+      </c>
+      <c r="P33">
+        <v>-1.771737696</v>
+      </c>
+      <c r="Q33">
+        <v>0.9182623040000002</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1221737638016563</v>
+      </c>
+      <c r="T33">
+        <v>1.409712142532351</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.08649870864168156</v>
+      </c>
+      <c r="W33">
+        <v>0.2181441083763665</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.3089239594345771</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1539245706198165</v>
+      </c>
+      <c r="C34">
+        <v>11.08110319969646</v>
+      </c>
+      <c r="D34">
+        <v>25.04310319969646</v>
+      </c>
+      <c r="E34">
+        <v>3.091999999999997</v>
+      </c>
+      <c r="F34">
+        <v>15.392</v>
+      </c>
+      <c r="G34">
+        <v>1.43</v>
+      </c>
+      <c r="H34">
+        <v>35.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>3.79</v>
+      </c>
+      <c r="K34">
+        <v>2.69</v>
+      </c>
+      <c r="L34">
+        <v>1.1</v>
+      </c>
+      <c r="M34">
+        <v>3.6756096</v>
+      </c>
+      <c r="N34">
+        <v>-2.575609599999999</v>
+      </c>
+      <c r="O34">
+        <v>-0.7211706879999996</v>
+      </c>
+      <c r="P34">
+        <v>-1.854438912</v>
+      </c>
+      <c r="Q34">
+        <v>0.835561088</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1233998485634454</v>
+      </c>
+      <c r="T34">
+        <v>1.430443203451945</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.08379562399662902</v>
+      </c>
+      <c r="W34">
+        <v>0.218789604989605</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.2992700857022466</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1559245706198165</v>
+      </c>
+      <c r="C35">
+        <v>10.22805345204492</v>
+      </c>
+      <c r="D35">
+        <v>24.67105345204492</v>
+      </c>
+      <c r="E35">
+        <v>3.572999999999999</v>
+      </c>
+      <c r="F35">
+        <v>15.873</v>
+      </c>
+      <c r="G35">
+        <v>1.43</v>
+      </c>
+      <c r="H35">
+        <v>35.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>3.79</v>
+      </c>
+      <c r="K35">
+        <v>2.69</v>
+      </c>
+      <c r="L35">
+        <v>1.1</v>
+      </c>
+      <c r="M35">
+        <v>3.7904724</v>
+      </c>
+      <c r="N35">
+        <v>-2.6904724</v>
+      </c>
+      <c r="O35">
+        <v>-0.7533322719999997</v>
+      </c>
+      <c r="P35">
+        <v>-1.937140128</v>
+      </c>
+      <c r="Q35">
+        <v>0.7528598719999997</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1246625328703625</v>
+      </c>
+      <c r="T35">
+        <v>1.451793102010929</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.08125636266339781</v>
+      </c>
+      <c r="W35">
+        <v>0.2193959805959806</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.2902012952264209</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1579245706198165</v>
+      </c>
+      <c r="C36">
+        <v>9.385896498547655</v>
+      </c>
+      <c r="D36">
+        <v>24.30989649854765</v>
+      </c>
+      <c r="E36">
+        <v>4.053999999999998</v>
+      </c>
+      <c r="F36">
+        <v>16.354</v>
+      </c>
+      <c r="G36">
+        <v>1.43</v>
+      </c>
+      <c r="H36">
+        <v>35.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>3.79</v>
+      </c>
+      <c r="K36">
+        <v>2.69</v>
+      </c>
+      <c r="L36">
+        <v>1.1</v>
+      </c>
+      <c r="M36">
+        <v>3.9053352</v>
+      </c>
+      <c r="N36">
+        <v>-2.8053352</v>
+      </c>
+      <c r="O36">
+        <v>-0.7854938559999998</v>
+      </c>
+      <c r="P36">
+        <v>-2.019841344</v>
+      </c>
+      <c r="Q36">
+        <v>0.6701586559999995</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1259634803380952</v>
+      </c>
+      <c r="T36">
+        <v>1.473789967192912</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.07886646964388612</v>
+      </c>
+      <c r="W36">
+        <v>0.21996668704904</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.281665963013879</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1599245706198165</v>
+      </c>
+      <c r="C37">
+        <v>8.554160865656627</v>
+      </c>
+      <c r="D37">
+        <v>23.95916086565663</v>
+      </c>
+      <c r="E37">
+        <v>4.535</v>
+      </c>
+      <c r="F37">
+        <v>16.835</v>
+      </c>
+      <c r="G37">
+        <v>1.43</v>
+      </c>
+      <c r="H37">
+        <v>35.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>3.79</v>
+      </c>
+      <c r="K37">
+        <v>2.69</v>
+      </c>
+      <c r="L37">
+        <v>1.1</v>
+      </c>
+      <c r="M37">
+        <v>4.020198000000001</v>
+      </c>
+      <c r="N37">
+        <v>-2.920198000000001</v>
+      </c>
+      <c r="O37">
+        <v>-0.8176554399999999</v>
+      </c>
+      <c r="P37">
+        <v>-2.102542560000001</v>
+      </c>
+      <c r="Q37">
+        <v>0.5874574399999992</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1273044569586813</v>
+      </c>
+      <c r="T37">
+        <v>1.49646365899588</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.07661314193977507</v>
+      </c>
+      <c r="W37">
+        <v>0.2205047817047817</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.2736183640706253</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1619245706198165</v>
+      </c>
+      <c r="C38">
+        <v>7.732401901938058</v>
+      </c>
+      <c r="D38">
+        <v>23.61840190193806</v>
+      </c>
+      <c r="E38">
+        <v>5.015999999999998</v>
+      </c>
+      <c r="F38">
+        <v>17.316</v>
+      </c>
+      <c r="G38">
+        <v>1.43</v>
+      </c>
+      <c r="H38">
+        <v>35.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>3.79</v>
+      </c>
+      <c r="K38">
+        <v>2.69</v>
+      </c>
+      <c r="L38">
+        <v>1.1</v>
+      </c>
+      <c r="M38">
+        <v>4.1350608</v>
+      </c>
+      <c r="N38">
+        <v>-3.0350608</v>
+      </c>
+      <c r="O38">
+        <v>-0.8498170239999997</v>
+      </c>
+      <c r="P38">
+        <v>-2.185243776</v>
+      </c>
+      <c r="Q38">
+        <v>0.5047562239999999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1286873390986607</v>
+      </c>
+      <c r="T38">
+        <v>1.519845903667691</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.07448499910811468</v>
+      </c>
+      <c r="W38">
+        <v>0.2210129822129822</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.2660178539575525</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1639245706198165</v>
+      </c>
+      <c r="C39">
+        <v>6.920199897433335</v>
+      </c>
+      <c r="D39">
+        <v>23.28719989743333</v>
+      </c>
+      <c r="E39">
+        <v>5.496999999999996</v>
+      </c>
+      <c r="F39">
+        <v>17.797</v>
+      </c>
+      <c r="G39">
+        <v>1.43</v>
+      </c>
+      <c r="H39">
+        <v>35.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>3.79</v>
+      </c>
+      <c r="K39">
+        <v>2.69</v>
+      </c>
+      <c r="L39">
+        <v>1.1</v>
+      </c>
+      <c r="M39">
+        <v>4.2499236</v>
+      </c>
+      <c r="N39">
+        <v>-3.1499236</v>
+      </c>
+      <c r="O39">
+        <v>-0.8819786079999996</v>
+      </c>
+      <c r="P39">
+        <v>-2.267944992</v>
+      </c>
+      <c r="Q39">
+        <v>0.4220550079999996</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1301141222589569</v>
+      </c>
+      <c r="T39">
+        <v>1.543970441821146</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.07247189102411157</v>
+      </c>
+      <c r="W39">
+        <v>0.2214937124234422</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.25882818222897</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1659245706198165</v>
+      </c>
+      <c r="C40">
+        <v>6.11715835906546</v>
+      </c>
+      <c r="D40">
+        <v>22.96515835906546</v>
+      </c>
+      <c r="E40">
+        <v>5.977999999999998</v>
+      </c>
+      <c r="F40">
+        <v>18.278</v>
+      </c>
+      <c r="G40">
+        <v>1.43</v>
+      </c>
+      <c r="H40">
+        <v>35.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>3.79</v>
+      </c>
+      <c r="K40">
+        <v>2.69</v>
+      </c>
+      <c r="L40">
+        <v>1.1</v>
+      </c>
+      <c r="M40">
+        <v>4.3647864</v>
+      </c>
+      <c r="N40">
+        <v>-3.2647864</v>
+      </c>
+      <c r="O40">
+        <v>-0.9141401919999996</v>
+      </c>
+      <c r="P40">
+        <v>-2.350646208</v>
+      </c>
+      <c r="Q40">
+        <v>0.3393537919999998</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1315869306824885</v>
+      </c>
+      <c r="T40">
+        <v>1.568873190882778</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.07056473599716127</v>
+      </c>
+      <c r="W40">
+        <v>0.2219491410438779</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.252016914275576</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1679245706198165</v>
+      </c>
+      <c r="C41">
+        <v>5.322902427191242</v>
+      </c>
+      <c r="D41">
+        <v>22.65190242719124</v>
+      </c>
+      <c r="E41">
+        <v>6.458999999999996</v>
+      </c>
+      <c r="F41">
+        <v>18.759</v>
+      </c>
+      <c r="G41">
+        <v>1.43</v>
+      </c>
+      <c r="H41">
+        <v>35.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>3.79</v>
+      </c>
+      <c r="K41">
+        <v>2.69</v>
+      </c>
+      <c r="L41">
+        <v>1.1</v>
+      </c>
+      <c r="M41">
+        <v>4.4796492</v>
+      </c>
+      <c r="N41">
+        <v>-3.3796492</v>
+      </c>
+      <c r="O41">
+        <v>-0.9463017759999997</v>
+      </c>
+      <c r="P41">
+        <v>-2.433347424</v>
+      </c>
+      <c r="Q41">
+        <v>0.256652576</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1331080279067916</v>
+      </c>
+      <c r="T41">
+        <v>1.5945924235202</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.06875538379210586</v>
+      </c>
+      <c r="W41">
+        <v>0.2223812143504451</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.2455549421146638</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1699245706198165</v>
+      </c>
+      <c r="C42">
+        <v>4.537077420003556</v>
+      </c>
+      <c r="D42">
+        <v>22.34707742000355</v>
+      </c>
+      <c r="E42">
+        <v>6.939999999999998</v>
+      </c>
+      <c r="F42">
+        <v>19.24</v>
+      </c>
+      <c r="G42">
+        <v>1.43</v>
+      </c>
+      <c r="H42">
+        <v>35.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>3.79</v>
+      </c>
+      <c r="K42">
+        <v>2.69</v>
+      </c>
+      <c r="L42">
+        <v>1.1</v>
+      </c>
+      <c r="M42">
+        <v>4.594512</v>
+      </c>
+      <c r="N42">
+        <v>-3.494512</v>
+      </c>
+      <c r="O42">
+        <v>-0.9784633599999997</v>
+      </c>
+      <c r="P42">
+        <v>-2.51604864</v>
+      </c>
+      <c r="Q42">
+        <v>0.1739513599999998</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1346798283719048</v>
+      </c>
+      <c r="T42">
+        <v>1.621168963912204</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.0670364991973032</v>
+      </c>
+      <c r="W42">
+        <v>0.222791683991684</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.2394160685617972</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1719245706198165</v>
+      </c>
+      <c r="C43">
+        <v>3.759347493900272</v>
+      </c>
+      <c r="D43">
+        <v>22.05034749390027</v>
+      </c>
+      <c r="E43">
+        <v>7.420999999999999</v>
+      </c>
+      <c r="F43">
+        <v>19.721</v>
+      </c>
+      <c r="G43">
+        <v>1.43</v>
+      </c>
+      <c r="H43">
+        <v>35.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>3.79</v>
+      </c>
+      <c r="K43">
+        <v>2.69</v>
+      </c>
+      <c r="L43">
+        <v>1.1</v>
+      </c>
+      <c r="M43">
+        <v>4.7093748</v>
+      </c>
+      <c r="N43">
+        <v>-3.6093748</v>
+      </c>
+      <c r="O43">
+        <v>-1.010624944</v>
+      </c>
+      <c r="P43">
+        <v>-2.598749856</v>
+      </c>
+      <c r="Q43">
+        <v>0.09125014399999953</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1363049102087167</v>
+      </c>
+      <c r="T43">
+        <v>1.648646403978512</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.06540146263151532</v>
+      </c>
+      <c r="W43">
+        <v>0.2231821307235941</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.2335766522554119</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1739245706198164</v>
+      </c>
+      <c r="C44">
+        <v>2.989394409182321</v>
+      </c>
+      <c r="D44">
+        <v>21.76139440918232</v>
+      </c>
+      <c r="E44">
+        <v>7.901999999999997</v>
+      </c>
+      <c r="F44">
+        <v>20.202</v>
+      </c>
+      <c r="G44">
+        <v>1.43</v>
+      </c>
+      <c r="H44">
+        <v>35.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>3.79</v>
+      </c>
+      <c r="K44">
+        <v>2.69</v>
+      </c>
+      <c r="L44">
+        <v>1.1</v>
+      </c>
+      <c r="M44">
+        <v>4.8242376</v>
+      </c>
+      <c r="N44">
+        <v>-3.7242376</v>
+      </c>
+      <c r="O44">
+        <v>-1.042786528</v>
+      </c>
+      <c r="P44">
+        <v>-2.681451072</v>
+      </c>
+      <c r="Q44">
+        <v>0.008548927999999734</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1379860293502463</v>
+      </c>
+      <c r="T44">
+        <v>1.677071341978142</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.06384428494981258</v>
+      </c>
+      <c r="W44">
+        <v>0.2235539847539848</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.2280153033921878</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1759245706198165</v>
+      </c>
+      <c r="C45">
+        <v>2.226916391543945</v>
+      </c>
+      <c r="D45">
+        <v>21.47991639154394</v>
+      </c>
+      <c r="E45">
+        <v>8.382999999999996</v>
+      </c>
+      <c r="F45">
+        <v>20.683</v>
+      </c>
+      <c r="G45">
+        <v>1.43</v>
+      </c>
+      <c r="H45">
+        <v>35.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>3.79</v>
+      </c>
+      <c r="K45">
+        <v>2.69</v>
+      </c>
+      <c r="L45">
+        <v>1.1</v>
+      </c>
+      <c r="M45">
+        <v>4.939100399999999</v>
+      </c>
+      <c r="N45">
+        <v>-3.839100399999999</v>
+      </c>
+      <c r="O45">
+        <v>-1.074948112</v>
+      </c>
+      <c r="P45">
+        <v>-2.764152288</v>
+      </c>
+      <c r="Q45">
+        <v>-0.07415228799999962</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1397261351283208</v>
+      </c>
+      <c r="T45">
+        <v>1.706493646223372</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.06235953413702625</v>
+      </c>
+      <c r="W45">
+        <v>0.2239085432480782</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.2227126219179509</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1779245706198165</v>
+      </c>
+      <c r="C46">
+        <v>1.471627080792715</v>
+      </c>
+      <c r="D46">
+        <v>21.20562708079271</v>
+      </c>
+      <c r="E46">
+        <v>8.863999999999997</v>
+      </c>
+      <c r="F46">
+        <v>21.164</v>
+      </c>
+      <c r="G46">
+        <v>1.43</v>
+      </c>
+      <c r="H46">
+        <v>35.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>3.79</v>
+      </c>
+      <c r="K46">
+        <v>2.69</v>
+      </c>
+      <c r="L46">
+        <v>1.1</v>
+      </c>
+      <c r="M46">
+        <v>5.0539632</v>
+      </c>
+      <c r="N46">
+        <v>-3.9539632</v>
+      </c>
+      <c r="O46">
+        <v>-1.107109696</v>
+      </c>
+      <c r="P46">
+        <v>-2.846853504</v>
+      </c>
+      <c r="Q46">
+        <v>-0.1568535040000003</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1415283875413265</v>
+      </c>
+      <c r="T46">
+        <v>1.73696674704879</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.06094227199754836</v>
+      </c>
+      <c r="W46">
+        <v>0.2242469854469855</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.2176509714198157</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1799245706198165</v>
+      </c>
+      <c r="C47">
+        <v>0.7232545591002975</v>
+      </c>
+      <c r="D47">
+        <v>20.9382545591003</v>
+      </c>
+      <c r="E47">
+        <v>9.344999999999999</v>
+      </c>
+      <c r="F47">
+        <v>21.645</v>
+      </c>
+      <c r="G47">
+        <v>1.43</v>
+      </c>
+      <c r="H47">
+        <v>35.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>3.79</v>
+      </c>
+      <c r="K47">
+        <v>2.69</v>
+      </c>
+      <c r="L47">
+        <v>1.1</v>
+      </c>
+      <c r="M47">
+        <v>5.168826</v>
+      </c>
+      <c r="N47">
+        <v>-4.068826</v>
+      </c>
+      <c r="O47">
+        <v>-1.13927128</v>
+      </c>
+      <c r="P47">
+        <v>-2.92955472</v>
+      </c>
+      <c r="Q47">
+        <v>-0.2395547200000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1433961764057143</v>
+      </c>
+      <c r="T47">
+        <v>1.768547960631495</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.05958799928649174</v>
+      </c>
+      <c r="W47">
+        <v>0.2245703857703858</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.212814283166042</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1819245706198165</v>
+      </c>
+      <c r="C48">
+        <v>-0.01845954814796613</v>
+      </c>
+      <c r="D48">
+        <v>20.67754045185203</v>
+      </c>
+      <c r="E48">
+        <v>9.825999999999997</v>
+      </c>
+      <c r="F48">
+        <v>22.126</v>
+      </c>
+      <c r="G48">
+        <v>1.43</v>
+      </c>
+      <c r="H48">
+        <v>35.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>3.79</v>
+      </c>
+      <c r="K48">
+        <v>2.69</v>
+      </c>
+      <c r="L48">
+        <v>1.1</v>
+      </c>
+      <c r="M48">
+        <v>5.283688799999999</v>
+      </c>
+      <c r="N48">
+        <v>-4.183688799999999</v>
+      </c>
+      <c r="O48">
+        <v>-1.171432863999999</v>
+      </c>
+      <c r="P48">
+        <v>-3.012255935999999</v>
+      </c>
+      <c r="Q48">
+        <v>-0.3222559359999995</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1453331426354497</v>
+      </c>
+      <c r="T48">
+        <v>1.801298848791337</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.05829260799765496</v>
+      </c>
+      <c r="W48">
+        <v>0.22487972521016</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.2081878857059107</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1839245706198165</v>
+      </c>
+      <c r="C49">
+        <v>-0.7537609051546532</v>
+      </c>
+      <c r="D49">
+        <v>20.42323909484535</v>
+      </c>
+      <c r="E49">
+        <v>10.307</v>
+      </c>
+      <c r="F49">
+        <v>22.607</v>
+      </c>
+      <c r="G49">
+        <v>1.43</v>
+      </c>
+      <c r="H49">
+        <v>35.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>3.79</v>
+      </c>
+      <c r="K49">
+        <v>2.69</v>
+      </c>
+      <c r="L49">
+        <v>1.1</v>
+      </c>
+      <c r="M49">
+        <v>5.3985516</v>
+      </c>
+      <c r="N49">
+        <v>-4.2985516</v>
+      </c>
+      <c r="O49">
+        <v>-1.203594448</v>
+      </c>
+      <c r="P49">
+        <v>-3.094957152</v>
+      </c>
+      <c r="Q49">
+        <v>-0.4049571520000002</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1473432019304582</v>
+      </c>
+      <c r="T49">
+        <v>1.83528561952325</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.0570523397423857</v>
+      </c>
+      <c r="W49">
+        <v>0.2251759012695183</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.2037583562228062</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1859245706198164</v>
+      </c>
+      <c r="C50">
+        <v>-1.482883237805424</v>
+      </c>
+      <c r="D50">
+        <v>20.17511676219457</v>
+      </c>
+      <c r="E50">
+        <v>10.788</v>
+      </c>
+      <c r="F50">
+        <v>23.088</v>
+      </c>
+      <c r="G50">
+        <v>1.43</v>
+      </c>
+      <c r="H50">
+        <v>35.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>3.79</v>
+      </c>
+      <c r="K50">
+        <v>2.69</v>
+      </c>
+      <c r="L50">
+        <v>1.1</v>
+      </c>
+      <c r="M50">
+        <v>5.513414399999999</v>
+      </c>
+      <c r="N50">
+        <v>-4.413414399999999</v>
+      </c>
+      <c r="O50">
+        <v>-1.235756031999999</v>
+      </c>
+      <c r="P50">
+        <v>-3.177658367999999</v>
+      </c>
+      <c r="Q50">
+        <v>-0.4876583679999995</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1494305711983517</v>
+      </c>
+      <c r="T50">
+        <v>1.87057957374485</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.05586374933108601</v>
+      </c>
+      <c r="W50">
+        <v>0.2254597366597366</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.1995133904681644</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1879245706198165</v>
+      </c>
+      <c r="C51">
+        <v>-2.20604905015869</v>
+      </c>
+      <c r="D51">
+        <v>19.93295094984131</v>
+      </c>
+      <c r="E51">
+        <v>11.26899999999999</v>
+      </c>
+      <c r="F51">
+        <v>23.569</v>
+      </c>
+      <c r="G51">
+        <v>1.43</v>
+      </c>
+      <c r="H51">
+        <v>35.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>3.79</v>
+      </c>
+      <c r="K51">
+        <v>2.69</v>
+      </c>
+      <c r="L51">
+        <v>1.1</v>
+      </c>
+      <c r="M51">
+        <v>5.628277199999999</v>
+      </c>
+      <c r="N51">
+        <v>-4.5282772</v>
+      </c>
+      <c r="O51">
+        <v>-1.267917616</v>
+      </c>
+      <c r="P51">
+        <v>-3.260359584</v>
+      </c>
+      <c r="Q51">
+        <v>-0.5703595840000002</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1515997980845938</v>
+      </c>
+      <c r="T51">
+        <v>1.907257604602592</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.05472367281412507</v>
+      </c>
+      <c r="W51">
+        <v>0.225731986931987</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1954416886218753</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1899245706198165</v>
+      </c>
+      <c r="C52">
+        <v>-2.923470289946177</v>
+      </c>
+      <c r="D52">
+        <v>19.69652971005382</v>
+      </c>
+      <c r="E52">
+        <v>11.75</v>
+      </c>
+      <c r="F52">
+        <v>24.05</v>
+      </c>
+      <c r="G52">
+        <v>1.43</v>
+      </c>
+      <c r="H52">
+        <v>35.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>3.79</v>
+      </c>
+      <c r="K52">
+        <v>2.69</v>
+      </c>
+      <c r="L52">
+        <v>1.1</v>
+      </c>
+      <c r="M52">
+        <v>5.743139999999999</v>
+      </c>
+      <c r="N52">
+        <v>-4.643139999999999</v>
+      </c>
+      <c r="O52">
+        <v>-1.300079199999999</v>
+      </c>
+      <c r="P52">
+        <v>-3.3430608</v>
+      </c>
+      <c r="Q52">
+        <v>-0.6530608</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1538557940462857</v>
+      </c>
+      <c r="T52">
+        <v>1.945402756694644</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.05362919935784257</v>
+      </c>
+      <c r="W52">
+        <v>0.2259933471933472</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1915328548494378</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1919245706198165</v>
+      </c>
+      <c r="C53">
+        <v>-3.635348967268445</v>
+      </c>
+      <c r="D53">
+        <v>19.46565103273155</v>
+      </c>
+      <c r="E53">
+        <v>12.231</v>
+      </c>
+      <c r="F53">
+        <v>24.531</v>
+      </c>
+      <c r="G53">
+        <v>1.43</v>
+      </c>
+      <c r="H53">
+        <v>35.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>3.79</v>
+      </c>
+      <c r="K53">
+        <v>2.69</v>
+      </c>
+      <c r="L53">
+        <v>1.1</v>
+      </c>
+      <c r="M53">
+        <v>5.8580028</v>
+      </c>
+      <c r="N53">
+        <v>-4.7580028</v>
+      </c>
+      <c r="O53">
+        <v>-1.332240783999999</v>
+      </c>
+      <c r="P53">
+        <v>-3.425762016</v>
+      </c>
+      <c r="Q53">
+        <v>-0.7357620160000002</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1562038714758018</v>
+      </c>
+      <c r="T53">
+        <v>1.985104853770045</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.05257764642925741</v>
+      </c>
+      <c r="W53">
+        <v>0.2262444580326933</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1877773086759195</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1939245706198165</v>
+      </c>
+      <c r="C54">
+        <v>-4.341877730281148</v>
+      </c>
+      <c r="D54">
+        <v>19.24012226971885</v>
+      </c>
+      <c r="E54">
+        <v>12.712</v>
+      </c>
+      <c r="F54">
+        <v>25.012</v>
+      </c>
+      <c r="G54">
+        <v>1.43</v>
+      </c>
+      <c r="H54">
+        <v>35.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>3.79</v>
+      </c>
+      <c r="K54">
+        <v>2.69</v>
+      </c>
+      <c r="L54">
+        <v>1.1</v>
+      </c>
+      <c r="M54">
+        <v>5.9728656</v>
+      </c>
+      <c r="N54">
+        <v>-4.872865599999999</v>
+      </c>
+      <c r="O54">
+        <v>-1.364402367999999</v>
+      </c>
+      <c r="P54">
+        <v>-3.508463232</v>
+      </c>
+      <c r="Q54">
+        <v>-0.8184632319999996</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.158649785464881</v>
+      </c>
+      <c r="T54">
+        <v>2.026461204890254</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.05156653784407939</v>
+      </c>
+      <c r="W54">
+        <v>0.2264859107628339</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1841662065859979</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1959245706198164</v>
+      </c>
+      <c r="C55">
+        <v>-5.043240401320322</v>
+      </c>
+      <c r="D55">
+        <v>19.01975959867968</v>
+      </c>
+      <c r="E55">
+        <v>13.193</v>
+      </c>
+      <c r="F55">
+        <v>25.493</v>
+      </c>
+      <c r="G55">
+        <v>1.43</v>
+      </c>
+      <c r="H55">
+        <v>35.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>3.79</v>
+      </c>
+      <c r="K55">
+        <v>2.69</v>
+      </c>
+      <c r="L55">
+        <v>1.1</v>
+      </c>
+      <c r="M55">
+        <v>6.0877284</v>
+      </c>
+      <c r="N55">
+        <v>-4.9877284</v>
+      </c>
+      <c r="O55">
+        <v>-1.396563951999999</v>
+      </c>
+      <c r="P55">
+        <v>-3.591164448000001</v>
+      </c>
+      <c r="Q55">
+        <v>-0.9011644480000007</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.161199780900304</v>
+      </c>
+      <c r="T55">
+        <v>2.069577400738984</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.05059358429985148</v>
+      </c>
+      <c r="W55">
+        <v>0.2267182520691955</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1806913724994695</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1979245706198165</v>
+      </c>
+      <c r="C56">
+        <v>-5.739612476602478</v>
+      </c>
+      <c r="D56">
+        <v>18.80438752339752</v>
+      </c>
+      <c r="E56">
+        <v>13.674</v>
+      </c>
+      <c r="F56">
+        <v>25.974</v>
+      </c>
+      <c r="G56">
+        <v>1.43</v>
+      </c>
+      <c r="H56">
+        <v>35.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>3.79</v>
+      </c>
+      <c r="K56">
+        <v>2.69</v>
+      </c>
+      <c r="L56">
+        <v>1.1</v>
+      </c>
+      <c r="M56">
+        <v>6.202591200000001</v>
+      </c>
+      <c r="N56">
+        <v>-5.102591200000001</v>
+      </c>
+      <c r="O56">
+        <v>-1.428725536</v>
+      </c>
+      <c r="P56">
+        <v>-3.673865664000001</v>
+      </c>
+      <c r="Q56">
+        <v>-0.983865664000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1638606457024845</v>
+      </c>
+      <c r="T56">
+        <v>2.114568213798527</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.04965666607207644</v>
+      </c>
+      <c r="W56">
+        <v>0.2269419881419882</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1773452359717016</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1999245706198165</v>
+      </c>
+      <c r="C57">
+        <v>-6.431161592354368</v>
+      </c>
+      <c r="D57">
+        <v>18.59383840764563</v>
+      </c>
+      <c r="E57">
+        <v>14.155</v>
+      </c>
+      <c r="F57">
+        <v>26.455</v>
+      </c>
+      <c r="G57">
+        <v>1.43</v>
+      </c>
+      <c r="H57">
+        <v>35.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>3.79</v>
+      </c>
+      <c r="K57">
+        <v>2.69</v>
+      </c>
+      <c r="L57">
+        <v>1.1</v>
+      </c>
+      <c r="M57">
+        <v>6.317454</v>
+      </c>
+      <c r="N57">
+        <v>-5.217454</v>
+      </c>
+      <c r="O57">
+        <v>-1.46088712</v>
+      </c>
+      <c r="P57">
+        <v>-3.75656688</v>
+      </c>
+      <c r="Q57">
+        <v>-1.06656688</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1666397711625397</v>
+      </c>
+      <c r="T57">
+        <v>2.161558618549605</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.04875381759803869</v>
+      </c>
+      <c r="W57">
+        <v>0.2271575883575884</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1741207771358525</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2019245706198165</v>
+      </c>
+      <c r="C58">
+        <v>-7.118047959974604</v>
+      </c>
+      <c r="D58">
+        <v>18.3879520400254</v>
+      </c>
+      <c r="E58">
+        <v>14.636</v>
+      </c>
+      <c r="F58">
+        <v>26.936</v>
+      </c>
+      <c r="G58">
+        <v>1.43</v>
+      </c>
+      <c r="H58">
+        <v>35.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>3.79</v>
+      </c>
+      <c r="K58">
+        <v>2.69</v>
+      </c>
+      <c r="L58">
+        <v>1.1</v>
+      </c>
+      <c r="M58">
+        <v>6.432316800000001</v>
+      </c>
+      <c r="N58">
+        <v>-5.332316800000001</v>
+      </c>
+      <c r="O58">
+        <v>-1.493048704</v>
+      </c>
+      <c r="P58">
+        <v>-3.839268096000001</v>
+      </c>
+      <c r="Q58">
+        <v>-1.149268096000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1695452205071429</v>
+      </c>
+      <c r="T58">
+        <v>2.210684950789369</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.04788321371235943</v>
+      </c>
+      <c r="W58">
+        <v>0.2273654885654886</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1710114775441408</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2039245706198165</v>
+      </c>
+      <c r="C59">
+        <v>-7.800424772600962</v>
+      </c>
+      <c r="D59">
+        <v>18.18657522739904</v>
+      </c>
+      <c r="E59">
+        <v>15.117</v>
+      </c>
+      <c r="F59">
+        <v>27.417</v>
+      </c>
+      <c r="G59">
+        <v>1.43</v>
+      </c>
+      <c r="H59">
+        <v>35.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>3.79</v>
+      </c>
+      <c r="K59">
+        <v>2.69</v>
+      </c>
+      <c r="L59">
+        <v>1.1</v>
+      </c>
+      <c r="M59">
+        <v>6.5471796</v>
+      </c>
+      <c r="N59">
+        <v>-5.4471796</v>
+      </c>
+      <c r="O59">
+        <v>-1.525210288</v>
+      </c>
+      <c r="P59">
+        <v>-3.921969312000001</v>
+      </c>
+      <c r="Q59">
+        <v>-1.231969312000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1725858070305648</v>
+      </c>
+      <c r="T59">
+        <v>2.262096228714703</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.04704315733144085</v>
+      </c>
+      <c r="W59">
+        <v>0.2275660940292519</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1680112761837173</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2059245706198164</v>
+      </c>
+      <c r="C60">
+        <v>-8.478438585251901</v>
+      </c>
+      <c r="D60">
+        <v>17.9895614147481</v>
+      </c>
+      <c r="E60">
+        <v>15.598</v>
+      </c>
+      <c r="F60">
+        <v>27.898</v>
+      </c>
+      <c r="G60">
+        <v>1.43</v>
+      </c>
+      <c r="H60">
+        <v>35.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>3.79</v>
+      </c>
+      <c r="K60">
+        <v>2.69</v>
+      </c>
+      <c r="L60">
+        <v>1.1</v>
+      </c>
+      <c r="M60">
+        <v>6.6620424</v>
+      </c>
+      <c r="N60">
+        <v>-5.562042399999999</v>
+      </c>
+      <c r="O60">
+        <v>-1.557371871999999</v>
+      </c>
+      <c r="P60">
+        <v>-4.004670528</v>
+      </c>
+      <c r="Q60">
+        <v>-1.314670528</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1757711833884354</v>
+      </c>
+      <c r="T60">
+        <v>2.315955662731719</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.04623206841193325</v>
+      </c>
+      <c r="W60">
+        <v>0.2277597820632303</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1651145300426189</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2079245706198165</v>
+      </c>
+      <c r="C61">
+        <v>-9.152229670524566</v>
+      </c>
+      <c r="D61">
+        <v>17.79677032947543</v>
+      </c>
+      <c r="E61">
+        <v>16.07899999999999</v>
+      </c>
+      <c r="F61">
+        <v>28.37899999999999</v>
+      </c>
+      <c r="G61">
+        <v>1.43</v>
+      </c>
+      <c r="H61">
+        <v>35.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>3.79</v>
+      </c>
+      <c r="K61">
+        <v>2.69</v>
+      </c>
+      <c r="L61">
+        <v>1.1</v>
+      </c>
+      <c r="M61">
+        <v>6.776905199999999</v>
+      </c>
+      <c r="N61">
+        <v>-5.676905199999998</v>
+      </c>
+      <c r="O61">
+        <v>-1.589533455999999</v>
+      </c>
+      <c r="P61">
+        <v>-4.087371743999999</v>
+      </c>
+      <c r="Q61">
+        <v>-1.397371744</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.179111943958885</v>
+      </c>
+      <c r="T61">
+        <v>2.372442386212981</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.04544847403206998</v>
+      </c>
+      <c r="W61">
+        <v>0.2279469044011417</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1623159786859643</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2099245706198165</v>
+      </c>
+      <c r="C62">
+        <v>-9.821932351663541</v>
+      </c>
+      <c r="D62">
+        <v>17.60806764833645</v>
+      </c>
+      <c r="E62">
+        <v>16.56</v>
+      </c>
+      <c r="F62">
+        <v>28.86</v>
+      </c>
+      <c r="G62">
+        <v>1.43</v>
+      </c>
+      <c r="H62">
+        <v>35.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>3.79</v>
+      </c>
+      <c r="K62">
+        <v>2.69</v>
+      </c>
+      <c r="L62">
+        <v>1.1</v>
+      </c>
+      <c r="M62">
+        <v>6.891767999999999</v>
+      </c>
+      <c r="N62">
+        <v>-5.791767999999999</v>
+      </c>
+      <c r="O62">
+        <v>-1.621695039999999</v>
+      </c>
+      <c r="P62">
+        <v>-4.17007296</v>
+      </c>
+      <c r="Q62">
+        <v>-1.48007296</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1826197425578572</v>
+      </c>
+      <c r="T62">
+        <v>2.431753445868305</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.04469099946486881</v>
+      </c>
+      <c r="W62">
+        <v>0.2281277893277893</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1596107123745314</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2119245706198165</v>
+      </c>
+      <c r="C63">
+        <v>-10.48767531466244</v>
+      </c>
+      <c r="D63">
+        <v>17.42332468533755</v>
+      </c>
+      <c r="E63">
+        <v>17.041</v>
+      </c>
+      <c r="F63">
+        <v>29.341</v>
+      </c>
+      <c r="G63">
+        <v>1.43</v>
+      </c>
+      <c r="H63">
+        <v>35.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>3.79</v>
+      </c>
+      <c r="K63">
+        <v>2.69</v>
+      </c>
+      <c r="L63">
+        <v>1.1</v>
+      </c>
+      <c r="M63">
+        <v>7.0066308</v>
+      </c>
+      <c r="N63">
+        <v>-5.9066308</v>
+      </c>
+      <c r="O63">
+        <v>-1.653856624</v>
+      </c>
+      <c r="P63">
+        <v>-4.252774176000001</v>
+      </c>
+      <c r="Q63">
+        <v>-1.562774176000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1863074282644689</v>
+      </c>
+      <c r="T63">
+        <v>2.494106098326467</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.04395836012937915</v>
+      </c>
+      <c r="W63">
+        <v>0.2283027436011043</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1569941433192112</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2139245706198165</v>
+      </c>
+      <c r="C64">
+        <v>-11.14958190092208</v>
+      </c>
+      <c r="D64">
+        <v>17.24241809907791</v>
+      </c>
+      <c r="E64">
+        <v>17.52199999999999</v>
+      </c>
+      <c r="F64">
+        <v>29.822</v>
+      </c>
+      <c r="G64">
+        <v>1.43</v>
+      </c>
+      <c r="H64">
+        <v>35.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>3.79</v>
+      </c>
+      <c r="K64">
+        <v>2.69</v>
+      </c>
+      <c r="L64">
+        <v>1.1</v>
+      </c>
+      <c r="M64">
+        <v>7.121493599999999</v>
+      </c>
+      <c r="N64">
+        <v>-6.021493599999999</v>
+      </c>
+      <c r="O64">
+        <v>-1.686018207999999</v>
+      </c>
+      <c r="P64">
+        <v>-4.335475392</v>
+      </c>
+      <c r="Q64">
+        <v>-1.645475392</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1901892026924812</v>
+      </c>
+      <c r="T64">
+        <v>2.559740469335058</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.04324935432084078</v>
+      </c>
+      <c r="W64">
+        <v>0.2284720541881832</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1544619797172885</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2159245706198165</v>
+      </c>
+      <c r="C65">
+        <v>-11.80777038186407</v>
+      </c>
+      <c r="D65">
+        <v>17.06522961813593</v>
+      </c>
+      <c r="E65">
+        <v>18.003</v>
+      </c>
+      <c r="F65">
+        <v>30.303</v>
+      </c>
+      <c r="G65">
+        <v>1.43</v>
+      </c>
+      <c r="H65">
+        <v>35.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>3.79</v>
+      </c>
+      <c r="K65">
+        <v>2.69</v>
+      </c>
+      <c r="L65">
+        <v>1.1</v>
+      </c>
+      <c r="M65">
+        <v>7.2363564</v>
+      </c>
+      <c r="N65">
+        <v>-6.1363564</v>
+      </c>
+      <c r="O65">
+        <v>-1.718179791999999</v>
+      </c>
+      <c r="P65">
+        <v>-4.418176608000001</v>
+      </c>
+      <c r="Q65">
+        <v>-1.728176608000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1942808027652509</v>
+      </c>
+      <c r="T65">
+        <v>2.628922644181952</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.04256285663320838</v>
+      </c>
+      <c r="W65">
+        <v>0.2286359898359898</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1520102022614584</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2179245706198165</v>
+      </c>
+      <c r="C66">
+        <v>-12.46235421678442</v>
+      </c>
+      <c r="D66">
+        <v>16.89164578321557</v>
+      </c>
+      <c r="E66">
+        <v>18.48399999999999</v>
+      </c>
+      <c r="F66">
+        <v>30.784</v>
+      </c>
+      <c r="G66">
+        <v>1.43</v>
+      </c>
+      <c r="H66">
+        <v>35.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>3.79</v>
+      </c>
+      <c r="K66">
+        <v>2.69</v>
+      </c>
+      <c r="L66">
+        <v>1.1</v>
+      </c>
+      <c r="M66">
+        <v>7.351219199999999</v>
+      </c>
+      <c r="N66">
+        <v>-6.2512192</v>
+      </c>
+      <c r="O66">
+        <v>-1.750341375999999</v>
+      </c>
+      <c r="P66">
+        <v>-4.500877824</v>
+      </c>
+      <c r="Q66">
+        <v>-1.810877824</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1985997139531746</v>
+      </c>
+      <c r="T66">
+        <v>2.701948273187006</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.04189781199831451</v>
+      </c>
+      <c r="W66">
+        <v>0.2287948024948025</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1496350428511232</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2199245706198165</v>
+      </c>
+      <c r="C67">
+        <v>-13.11344229512876</v>
+      </c>
+      <c r="D67">
+        <v>16.72155770487124</v>
+      </c>
+      <c r="E67">
+        <v>18.965</v>
+      </c>
+      <c r="F67">
+        <v>31.265</v>
+      </c>
+      <c r="G67">
+        <v>1.43</v>
+      </c>
+      <c r="H67">
+        <v>35.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>3.79</v>
+      </c>
+      <c r="K67">
+        <v>2.69</v>
+      </c>
+      <c r="L67">
+        <v>1.1</v>
+      </c>
+      <c r="M67">
+        <v>7.466082</v>
+      </c>
+      <c r="N67">
+        <v>-6.366082</v>
+      </c>
+      <c r="O67">
+        <v>-1.78250296</v>
+      </c>
+      <c r="P67">
+        <v>-4.583579040000001</v>
+      </c>
+      <c r="Q67">
+        <v>-1.893579040000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2031654200661225</v>
+      </c>
+      <c r="T67">
+        <v>2.779146795278063</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.04125323027526351</v>
+      </c>
+      <c r="W67">
+        <v>0.2289487286102671</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1473329652687982</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2219245706198165</v>
+      </c>
+      <c r="C68">
+        <v>-13.761139164276</v>
+      </c>
+      <c r="D68">
+        <v>16.554860835724</v>
+      </c>
+      <c r="E68">
+        <v>19.446</v>
+      </c>
+      <c r="F68">
+        <v>31.746</v>
+      </c>
+      <c r="G68">
+        <v>1.43</v>
+      </c>
+      <c r="H68">
+        <v>35.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>3.79</v>
+      </c>
+      <c r="K68">
+        <v>2.69</v>
+      </c>
+      <c r="L68">
+        <v>1.1</v>
+      </c>
+      <c r="M68">
+        <v>7.5809448</v>
+      </c>
+      <c r="N68">
+        <v>-6.4809448</v>
+      </c>
+      <c r="O68">
+        <v>-1.814664543999999</v>
+      </c>
+      <c r="P68">
+        <v>-4.666280256</v>
+      </c>
+      <c r="Q68">
+        <v>-1.976280256</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2079996971268908</v>
+      </c>
+      <c r="T68">
+        <v>2.860886406903889</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.0406281813316989</v>
+      </c>
+      <c r="W68">
+        <v>0.2290979902979903</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1451006476132105</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2239245706198165</v>
+      </c>
+      <c r="C69">
+        <v>-14.40554524383196</v>
+      </c>
+      <c r="D69">
+        <v>16.39145475616804</v>
+      </c>
+      <c r="E69">
+        <v>19.927</v>
+      </c>
+      <c r="F69">
+        <v>32.227</v>
+      </c>
+      <c r="G69">
+        <v>1.43</v>
+      </c>
+      <c r="H69">
+        <v>35.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>3.79</v>
+      </c>
+      <c r="K69">
+        <v>2.69</v>
+      </c>
+      <c r="L69">
+        <v>1.1</v>
+      </c>
+      <c r="M69">
+        <v>7.695807599999999</v>
+      </c>
+      <c r="N69">
+        <v>-6.595807599999999</v>
+      </c>
+      <c r="O69">
+        <v>-1.846826127999999</v>
+      </c>
+      <c r="P69">
+        <v>-4.748981472</v>
+      </c>
+      <c r="Q69">
+        <v>-2.058981472</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2131269606761905</v>
+      </c>
+      <c r="T69">
+        <v>2.947579934385825</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.04002179056555415</v>
+      </c>
+      <c r="W69">
+        <v>0.2292427964129457</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1429349663055507</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2259245706198165</v>
+      </c>
+      <c r="C70">
+        <v>-15.04675702735578</v>
+      </c>
+      <c r="D70">
+        <v>16.23124297264422</v>
+      </c>
+      <c r="E70">
+        <v>20.408</v>
+      </c>
+      <c r="F70">
+        <v>32.708</v>
+      </c>
+      <c r="G70">
+        <v>1.43</v>
+      </c>
+      <c r="H70">
+        <v>35.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>3.79</v>
+      </c>
+      <c r="K70">
+        <v>2.69</v>
+      </c>
+      <c r="L70">
+        <v>1.1</v>
+      </c>
+      <c r="M70">
+        <v>7.8106704</v>
+      </c>
+      <c r="N70">
+        <v>-6.7106704</v>
+      </c>
+      <c r="O70">
+        <v>-1.878987711999999</v>
+      </c>
+      <c r="P70">
+        <v>-4.831682688000001</v>
+      </c>
+      <c r="Q70">
+        <v>-2.141682688000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2185746781973215</v>
+      </c>
+      <c r="T70">
+        <v>3.039691807335382</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.03943323482194306</v>
+      </c>
+      <c r="W70">
+        <v>0.22938334352452</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1408329815069396</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2279245706198165</v>
+      </c>
+      <c r="C71">
+        <v>-15.68486727237068</v>
+      </c>
+      <c r="D71">
+        <v>16.07413272762932</v>
+      </c>
+      <c r="E71">
+        <v>20.889</v>
+      </c>
+      <c r="F71">
+        <v>33.189</v>
+      </c>
+      <c r="G71">
+        <v>1.43</v>
+      </c>
+      <c r="H71">
+        <v>35.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>3.79</v>
+      </c>
+      <c r="K71">
+        <v>2.69</v>
+      </c>
+      <c r="L71">
+        <v>1.1</v>
+      </c>
+      <c r="M71">
+        <v>7.9255332</v>
+      </c>
+      <c r="N71">
+        <v>-6.825533200000001</v>
+      </c>
+      <c r="O71">
+        <v>-1.911149296</v>
+      </c>
+      <c r="P71">
+        <v>-4.914383904000001</v>
+      </c>
+      <c r="Q71">
+        <v>-2.224383904000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.224373861364977</v>
+      </c>
+      <c r="T71">
+        <v>3.137746381765556</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.03886173866510331</v>
+      </c>
+      <c r="W71">
+        <v>0.2295198168067733</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1387919238039403</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2299245706198165</v>
+      </c>
+      <c r="C72">
+        <v>-16.31996517944523</v>
+      </c>
+      <c r="D72">
+        <v>15.92003482055477</v>
+      </c>
+      <c r="E72">
+        <v>21.37</v>
+      </c>
+      <c r="F72">
+        <v>33.67</v>
+      </c>
+      <c r="G72">
+        <v>1.43</v>
+      </c>
+      <c r="H72">
+        <v>35.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>3.79</v>
+      </c>
+      <c r="K72">
+        <v>2.69</v>
+      </c>
+      <c r="L72">
+        <v>1.1</v>
+      </c>
+      <c r="M72">
+        <v>8.040396000000001</v>
+      </c>
+      <c r="N72">
+        <v>-6.940396000000002</v>
+      </c>
+      <c r="O72">
+        <v>-1.94331088</v>
+      </c>
+      <c r="P72">
+        <v>-4.997085120000001</v>
+      </c>
+      <c r="Q72">
+        <v>-2.307085120000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2305596567438096</v>
+      </c>
+      <c r="T72">
+        <v>3.242337927824408</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.03830657096988754</v>
+      </c>
+      <c r="W72">
+        <v>0.2296523908523909</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1368091820353127</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2319245706198165</v>
+      </c>
+      <c r="C73">
+        <v>-16.95213656107172</v>
+      </c>
+      <c r="D73">
+        <v>15.76886343892828</v>
+      </c>
+      <c r="E73">
+        <v>21.851</v>
+      </c>
+      <c r="F73">
+        <v>34.151</v>
+      </c>
+      <c r="G73">
+        <v>1.43</v>
+      </c>
+      <c r="H73">
+        <v>35.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>3.79</v>
+      </c>
+      <c r="K73">
+        <v>2.69</v>
+      </c>
+      <c r="L73">
+        <v>1.1</v>
+      </c>
+      <c r="M73">
+        <v>8.1552588</v>
+      </c>
+      <c r="N73">
+        <v>-7.055258800000001</v>
+      </c>
+      <c r="O73">
+        <v>-1.975472464</v>
+      </c>
+      <c r="P73">
+        <v>-5.079786336000002</v>
+      </c>
+      <c r="Q73">
+        <v>-2.389786336000002</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2371720587004926</v>
+      </c>
+      <c r="T73">
+        <v>3.354142683956283</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.03776704180129758</v>
+      </c>
+      <c r="W73">
+        <v>0.2297812304178502</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1348822921474914</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2339245706198165</v>
+      </c>
+      <c r="C74">
+        <v>-17.58146400101327</v>
+      </c>
+      <c r="D74">
+        <v>15.62053599898673</v>
+      </c>
+      <c r="E74">
+        <v>22.332</v>
+      </c>
+      <c r="F74">
+        <v>34.632</v>
+      </c>
+      <c r="G74">
+        <v>1.43</v>
+      </c>
+      <c r="H74">
+        <v>35.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>3.79</v>
+      </c>
+      <c r="K74">
+        <v>2.69</v>
+      </c>
+      <c r="L74">
+        <v>1.1</v>
+      </c>
+      <c r="M74">
+        <v>8.2701216</v>
+      </c>
+      <c r="N74">
+        <v>-7.1701216</v>
+      </c>
+      <c r="O74">
+        <v>-2.007634047999999</v>
+      </c>
+      <c r="P74">
+        <v>-5.162487552</v>
+      </c>
+      <c r="Q74">
+        <v>-2.472487552</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2442567750826531</v>
+      </c>
+      <c r="T74">
+        <v>3.473933494097579</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.03724249955405734</v>
+      </c>
+      <c r="W74">
+        <v>0.2299064911064911</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1330089269787762</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2359245706198164</v>
+      </c>
+      <c r="C75">
+        <v>-18.20802700474152</v>
+      </c>
+      <c r="D75">
+        <v>15.47497299525847</v>
+      </c>
+      <c r="E75">
+        <v>22.81299999999999</v>
+      </c>
+      <c r="F75">
+        <v>35.11299999999999</v>
+      </c>
+      <c r="G75">
+        <v>1.43</v>
+      </c>
+      <c r="H75">
+        <v>35.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>3.79</v>
+      </c>
+      <c r="K75">
+        <v>2.69</v>
+      </c>
+      <c r="L75">
+        <v>1.1</v>
+      </c>
+      <c r="M75">
+        <v>8.384984399999999</v>
+      </c>
+      <c r="N75">
+        <v>-7.284984399999999</v>
+      </c>
+      <c r="O75">
+        <v>-2.039795631999999</v>
+      </c>
+      <c r="P75">
+        <v>-5.245188768</v>
+      </c>
+      <c r="Q75">
+        <v>-2.555188768</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2518662852708994</v>
+      </c>
+      <c r="T75">
+        <v>3.602597697582674</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.03673232832728943</v>
+      </c>
+      <c r="W75">
+        <v>0.2300283199954433</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1311868868831765</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2379245706198165</v>
+      </c>
+      <c r="C76">
+        <v>-18.83190214154079</v>
+      </c>
+      <c r="D76">
+        <v>15.3320978584592</v>
+      </c>
+      <c r="E76">
+        <v>23.29399999999999</v>
+      </c>
+      <c r="F76">
+        <v>35.59399999999999</v>
+      </c>
+      <c r="G76">
+        <v>1.43</v>
+      </c>
+      <c r="H76">
+        <v>35.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>3.79</v>
+      </c>
+      <c r="K76">
+        <v>2.69</v>
+      </c>
+      <c r="L76">
+        <v>1.1</v>
+      </c>
+      <c r="M76">
+        <v>8.4998472</v>
+      </c>
+      <c r="N76">
+        <v>-7.3998472</v>
+      </c>
+      <c r="O76">
+        <v>-2.071957215999999</v>
+      </c>
+      <c r="P76">
+        <v>-5.327889984</v>
+      </c>
+      <c r="Q76">
+        <v>-2.637889984000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2600611423967033</v>
+      </c>
+      <c r="T76">
+        <v>3.741159147489701</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.03623594551205579</v>
+      </c>
+      <c r="W76">
+        <v>0.2301468562117211</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.129414091114485</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2399245706198165</v>
+      </c>
+      <c r="C77">
+        <v>-19.45316317881203</v>
+      </c>
+      <c r="D77">
+        <v>15.19183682118797</v>
+      </c>
+      <c r="E77">
+        <v>23.775</v>
+      </c>
+      <c r="F77">
+        <v>36.075</v>
+      </c>
+      <c r="G77">
+        <v>1.43</v>
+      </c>
+      <c r="H77">
+        <v>35.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>3.79</v>
+      </c>
+      <c r="K77">
+        <v>2.69</v>
+      </c>
+      <c r="L77">
+        <v>1.1</v>
+      </c>
+      <c r="M77">
+        <v>8.614709999999999</v>
+      </c>
+      <c r="N77">
+        <v>-7.514709999999999</v>
+      </c>
+      <c r="O77">
+        <v>-2.104118799999999</v>
+      </c>
+      <c r="P77">
+        <v>-5.4105912</v>
+      </c>
+      <c r="Q77">
+        <v>-2.7205912</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2689115880925714</v>
+      </c>
+      <c r="T77">
+        <v>3.890805513389289</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.03575279957189505</v>
+      </c>
+      <c r="W77">
+        <v>0.2302622314622315</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1276885698996252</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2419245706198165</v>
+      </c>
+      <c r="C78">
+        <v>-20.07188120907199</v>
+      </c>
+      <c r="D78">
+        <v>15.054118790928</v>
+      </c>
+      <c r="E78">
+        <v>24.256</v>
+      </c>
+      <c r="F78">
+        <v>36.556</v>
+      </c>
+      <c r="G78">
+        <v>1.43</v>
+      </c>
+      <c r="H78">
+        <v>35.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>3.79</v>
+      </c>
+      <c r="K78">
+        <v>2.69</v>
+      </c>
+      <c r="L78">
+        <v>1.1</v>
+      </c>
+      <c r="M78">
+        <v>8.7295728</v>
+      </c>
+      <c r="N78">
+        <v>-7.6295728</v>
+      </c>
+      <c r="O78">
+        <v>-2.136280384</v>
+      </c>
+      <c r="P78">
+        <v>-5.493292416000001</v>
+      </c>
+      <c r="Q78">
+        <v>-2.803292416000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2784995709297619</v>
+      </c>
+      <c r="T78">
+        <v>4.052922409780509</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.03528236799858064</v>
+      </c>
+      <c r="W78">
+        <v>0.230374570521939</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.126008457137788</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2439245706198165</v>
+      </c>
+      <c r="C79">
+        <v>-20.68812477010666</v>
+      </c>
+      <c r="D79">
+        <v>14.91887522989334</v>
+      </c>
+      <c r="E79">
+        <v>24.737</v>
+      </c>
+      <c r="F79">
+        <v>37.037</v>
+      </c>
+      <c r="G79">
+        <v>1.43</v>
+      </c>
+      <c r="H79">
+        <v>35.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>3.79</v>
+      </c>
+      <c r="K79">
+        <v>2.69</v>
+      </c>
+      <c r="L79">
+        <v>1.1</v>
+      </c>
+      <c r="M79">
+        <v>8.844435600000001</v>
+      </c>
+      <c r="N79">
+        <v>-7.744435600000001</v>
+      </c>
+      <c r="O79">
+        <v>-2.168441968</v>
+      </c>
+      <c r="P79">
+        <v>-5.575993632000001</v>
+      </c>
+      <c r="Q79">
+        <v>-2.885993632000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.288921291404969</v>
+      </c>
+      <c r="T79">
+        <v>4.229136427597053</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.03482415542717049</v>
+      </c>
+      <c r="W79">
+        <v>0.2304839916839917</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.124371983668466</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2459245706198165</v>
+      </c>
+      <c r="C80">
+        <v>-21.30195995870573</v>
+      </c>
+      <c r="D80">
+        <v>14.78604004129426</v>
+      </c>
+      <c r="E80">
+        <v>25.21799999999999</v>
+      </c>
+      <c r="F80">
+        <v>37.51799999999999</v>
+      </c>
+      <c r="G80">
+        <v>1.43</v>
+      </c>
+      <c r="H80">
+        <v>35.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>3.79</v>
+      </c>
+      <c r="K80">
+        <v>2.69</v>
+      </c>
+      <c r="L80">
+        <v>1.1</v>
+      </c>
+      <c r="M80">
+        <v>8.9592984</v>
+      </c>
+      <c r="N80">
+        <v>-7.8592984</v>
+      </c>
+      <c r="O80">
+        <v>-2.200603552</v>
+      </c>
+      <c r="P80">
+        <v>-5.658694848000001</v>
+      </c>
+      <c r="Q80">
+        <v>-2.968694848000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3002904410142858</v>
+      </c>
+      <c r="T80">
+        <v>4.421369901578737</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.03437769189605293</v>
+      </c>
+      <c r="W80">
+        <v>0.2305906071752226</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1227774710573318</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2479245706198165</v>
+      </c>
+      <c r="C81">
+        <v>-21.91345053837472</v>
+      </c>
+      <c r="D81">
+        <v>14.65554946162528</v>
+      </c>
+      <c r="E81">
+        <v>25.69899999999999</v>
+      </c>
+      <c r="F81">
+        <v>37.999</v>
+      </c>
+      <c r="G81">
+        <v>1.43</v>
+      </c>
+      <c r="H81">
+        <v>35.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>3.79</v>
+      </c>
+      <c r="K81">
+        <v>2.69</v>
+      </c>
+      <c r="L81">
+        <v>1.1</v>
+      </c>
+      <c r="M81">
+        <v>9.074161199999999</v>
+      </c>
+      <c r="N81">
+        <v>-7.974161199999999</v>
+      </c>
+      <c r="O81">
+        <v>-2.232765135999999</v>
+      </c>
+      <c r="P81">
+        <v>-5.741396064</v>
+      </c>
+      <c r="Q81">
+        <v>-3.051396064</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3127423667768708</v>
+      </c>
+      <c r="T81">
+        <v>4.63191132546344</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.03394253123914086</v>
+      </c>
+      <c r="W81">
+        <v>0.2306945235400932</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1212233258540745</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2499245706198165</v>
+      </c>
+      <c r="C82">
+        <v>-22.52265804139338</v>
+      </c>
+      <c r="D82">
+        <v>14.52734195860662</v>
+      </c>
+      <c r="E82">
+        <v>26.18</v>
+      </c>
+      <c r="F82">
+        <v>38.48</v>
+      </c>
+      <c r="G82">
+        <v>1.43</v>
+      </c>
+      <c r="H82">
+        <v>35.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>3.79</v>
+      </c>
+      <c r="K82">
+        <v>2.69</v>
+      </c>
+      <c r="L82">
+        <v>1.1</v>
+      </c>
+      <c r="M82">
+        <v>9.189024</v>
+      </c>
+      <c r="N82">
+        <v>-8.089024</v>
+      </c>
+      <c r="O82">
+        <v>-2.264926719999999</v>
+      </c>
+      <c r="P82">
+        <v>-5.824097280000001</v>
+      </c>
+      <c r="Q82">
+        <v>-3.134097280000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3264394851157144</v>
+      </c>
+      <c r="T82">
+        <v>4.863506891736612</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.0335182495986516</v>
+      </c>
+      <c r="W82">
+        <v>0.230795841995842</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1197080342808986</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2519245706198164</v>
+      </c>
+      <c r="C83">
+        <v>-23.12964186556374</v>
+      </c>
+      <c r="D83">
+        <v>14.40135813443626</v>
+      </c>
+      <c r="E83">
+        <v>26.661</v>
+      </c>
+      <c r="F83">
+        <v>38.961</v>
+      </c>
+      <c r="G83">
+        <v>1.43</v>
+      </c>
+      <c r="H83">
+        <v>35.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>3.79</v>
+      </c>
+      <c r="K83">
+        <v>2.69</v>
+      </c>
+      <c r="L83">
+        <v>1.1</v>
+      </c>
+      <c r="M83">
+        <v>9.303886800000001</v>
+      </c>
+      <c r="N83">
+        <v>-8.203886800000001</v>
+      </c>
+      <c r="O83">
+        <v>-2.297088303999999</v>
+      </c>
+      <c r="P83">
+        <v>-5.906798496000002</v>
+      </c>
+      <c r="Q83">
+        <v>-3.216798496000002</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3415784053849624</v>
+      </c>
+      <c r="T83">
+        <v>5.119480938670117</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.03310444404805096</v>
+      </c>
+      <c r="W83">
+        <v>0.2308946587613254</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1182301573144677</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2539245706198165</v>
+      </c>
+      <c r="C84">
+        <v>-23.73445936596735</v>
+      </c>
+      <c r="D84">
+        <v>14.27754063403265</v>
+      </c>
+      <c r="E84">
+        <v>27.142</v>
+      </c>
+      <c r="F84">
+        <v>39.442</v>
+      </c>
+      <c r="G84">
+        <v>1.43</v>
+      </c>
+      <c r="H84">
+        <v>35.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>3.79</v>
+      </c>
+      <c r="K84">
+        <v>2.69</v>
+      </c>
+      <c r="L84">
+        <v>1.1</v>
+      </c>
+      <c r="M84">
+        <v>9.4187496</v>
+      </c>
+      <c r="N84">
+        <v>-8.3187496</v>
+      </c>
+      <c r="O84">
+        <v>-2.329249887999999</v>
+      </c>
+      <c r="P84">
+        <v>-5.989499712000001</v>
+      </c>
+      <c r="Q84">
+        <v>-3.299499712000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3583994279063493</v>
+      </c>
+      <c r="T84">
+        <v>5.403896546374013</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.03270073131575766</v>
+      </c>
+      <c r="W84">
+        <v>0.2309910653617971</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.116788326127706</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2559245706198164</v>
+      </c>
+      <c r="C85">
+        <v>-24.33716594202944</v>
+      </c>
+      <c r="D85">
+        <v>14.15583405797056</v>
+      </c>
+      <c r="E85">
+        <v>27.623</v>
+      </c>
+      <c r="F85">
+        <v>39.923</v>
+      </c>
+      <c r="G85">
+        <v>1.43</v>
+      </c>
+      <c r="H85">
+        <v>35.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>3.79</v>
+      </c>
+      <c r="K85">
+        <v>2.69</v>
+      </c>
+      <c r="L85">
+        <v>1.1</v>
+      </c>
+      <c r="M85">
+        <v>9.533612400000001</v>
+      </c>
+      <c r="N85">
+        <v>-8.433612400000001</v>
+      </c>
+      <c r="O85">
+        <v>-2.361411471999999</v>
+      </c>
+      <c r="P85">
+        <v>-6.072200928000002</v>
+      </c>
+      <c r="Q85">
+        <v>-3.382200928000002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3771993942537817</v>
+      </c>
+      <c r="T85">
+        <v>5.72177281380778</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.03230674660110997</v>
+      </c>
+      <c r="W85">
+        <v>0.2310851489116549</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.115381237861107</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2579245706198165</v>
+      </c>
+      <c r="C86">
+        <v>-24.93781512016779</v>
+      </c>
+      <c r="D86">
+        <v>14.0361848798322</v>
+      </c>
+      <c r="E86">
+        <v>28.104</v>
+      </c>
+      <c r="F86">
+        <v>40.404</v>
+      </c>
+      <c r="G86">
+        <v>1.43</v>
+      </c>
+      <c r="H86">
+        <v>35.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>3.79</v>
+      </c>
+      <c r="K86">
+        <v>2.69</v>
+      </c>
+      <c r="L86">
+        <v>1.1</v>
+      </c>
+      <c r="M86">
+        <v>9.6484752</v>
+      </c>
+      <c r="N86">
+        <v>-8.5484752</v>
+      </c>
+      <c r="O86">
+        <v>-2.393573055999999</v>
+      </c>
+      <c r="P86">
+        <v>-6.154902144000001</v>
+      </c>
+      <c r="Q86">
+        <v>-3.464902144000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3983493563946429</v>
+      </c>
+      <c r="T86">
+        <v>6.079383614670763</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.03192214247490629</v>
+      </c>
+      <c r="W86">
+        <v>0.2311769923769924</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1140076516960938</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2599245706198164</v>
+      </c>
+      <c r="C87">
+        <v>-25.53645863228525</v>
+      </c>
+      <c r="D87">
+        <v>13.91854136771474</v>
+      </c>
+      <c r="E87">
+        <v>28.58499999999999</v>
+      </c>
+      <c r="F87">
+        <v>40.88499999999999</v>
+      </c>
+      <c r="G87">
+        <v>1.43</v>
+      </c>
+      <c r="H87">
+        <v>35.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>3.79</v>
+      </c>
+      <c r="K87">
+        <v>2.69</v>
+      </c>
+      <c r="L87">
+        <v>1.1</v>
+      </c>
+      <c r="M87">
+        <v>9.763337999999999</v>
+      </c>
+      <c r="N87">
+        <v>-8.663338</v>
+      </c>
+      <c r="O87">
+        <v>-2.425734639999999</v>
+      </c>
+      <c r="P87">
+        <v>-6.23760336</v>
+      </c>
+      <c r="Q87">
+        <v>-3.547603360000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.422319313487619</v>
+      </c>
+      <c r="T87">
+        <v>6.484675855648814</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.03154658785755445</v>
+      </c>
+      <c r="W87">
+        <v>0.231266674819616</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1126663852055516</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2619245706198164</v>
+      </c>
+      <c r="C88">
+        <v>-26.13314649034785</v>
+      </c>
+      <c r="D88">
+        <v>13.80285350965214</v>
+      </c>
+      <c r="E88">
+        <v>29.06599999999999</v>
+      </c>
+      <c r="F88">
+        <v>41.36599999999999</v>
+      </c>
+      <c r="G88">
+        <v>1.43</v>
+      </c>
+      <c r="H88">
+        <v>35.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>3.79</v>
+      </c>
+      <c r="K88">
+        <v>2.69</v>
+      </c>
+      <c r="L88">
+        <v>1.1</v>
+      </c>
+      <c r="M88">
+        <v>9.878200799999998</v>
+      </c>
+      <c r="N88">
+        <v>-8.778200799999999</v>
+      </c>
+      <c r="O88">
+        <v>-2.457896223999999</v>
+      </c>
+      <c r="P88">
+        <v>-6.320304576</v>
+      </c>
+      <c r="Q88">
+        <v>-3.630304576</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4497135501653061</v>
+      </c>
+      <c r="T88">
+        <v>6.947866988195158</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.03117976706851312</v>
+      </c>
+      <c r="W88">
+        <v>0.2313542716240391</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1113563109589755</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2639245706198164</v>
+      </c>
+      <c r="C89">
+        <v>-26.72792705727421</v>
+      </c>
+      <c r="D89">
+        <v>13.68907294272578</v>
+      </c>
+      <c r="E89">
+        <v>29.54699999999999</v>
+      </c>
+      <c r="F89">
+        <v>41.84699999999999</v>
+      </c>
+      <c r="G89">
+        <v>1.43</v>
+      </c>
+      <c r="H89">
+        <v>35.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>3.79</v>
+      </c>
+      <c r="K89">
+        <v>2.69</v>
+      </c>
+      <c r="L89">
+        <v>1.1</v>
+      </c>
+      <c r="M89">
+        <v>9.993063599999999</v>
+      </c>
+      <c r="N89">
+        <v>-8.8930636</v>
+      </c>
+      <c r="O89">
+        <v>-2.490057807999999</v>
+      </c>
+      <c r="P89">
+        <v>-6.403005792</v>
+      </c>
+      <c r="Q89">
+        <v>-3.713005792</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4813222847934066</v>
+      </c>
+      <c r="T89">
+        <v>7.482318294979401</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.03082137894128883</v>
+      </c>
+      <c r="W89">
+        <v>0.2314398547088203</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1100763533617458</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2659245706198164</v>
+      </c>
+      <c r="C90">
+        <v>-27.32084711434757</v>
+      </c>
+      <c r="D90">
+        <v>13.57715288565243</v>
+      </c>
+      <c r="E90">
+        <v>30.028</v>
+      </c>
+      <c r="F90">
+        <v>42.328</v>
+      </c>
+      <c r="G90">
+        <v>1.43</v>
+      </c>
+      <c r="H90">
+        <v>35.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>3.79</v>
+      </c>
+      <c r="K90">
+        <v>2.69</v>
+      </c>
+      <c r="L90">
+        <v>1.1</v>
+      </c>
+      <c r="M90">
+        <v>10.1079264</v>
+      </c>
+      <c r="N90">
+        <v>-9.007926400000001</v>
+      </c>
+      <c r="O90">
+        <v>-2.522219391999999</v>
+      </c>
+      <c r="P90">
+        <v>-6.485707008000001</v>
+      </c>
+      <c r="Q90">
+        <v>-3.795707008000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5181991418595238</v>
+      </c>
+      <c r="T90">
+        <v>8.105844819561018</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.03047113599877418</v>
+      </c>
+      <c r="W90">
+        <v>0.2315234927234927</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1088254857099078</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2679245706198164</v>
+      </c>
+      <c r="C91">
+        <v>-27.91195192534762</v>
+      </c>
+      <c r="D91">
+        <v>13.46704807465238</v>
+      </c>
+      <c r="E91">
+        <v>30.509</v>
+      </c>
+      <c r="F91">
+        <v>42.809</v>
+      </c>
+      <c r="G91">
+        <v>1.43</v>
+      </c>
+      <c r="H91">
+        <v>35.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>3.79</v>
+      </c>
+      <c r="K91">
+        <v>2.69</v>
+      </c>
+      <c r="L91">
+        <v>1.1</v>
+      </c>
+      <c r="M91">
+        <v>10.2227892</v>
+      </c>
+      <c r="N91">
+        <v>-9.1227892</v>
+      </c>
+      <c r="O91">
+        <v>-2.554380975999999</v>
+      </c>
+      <c r="P91">
+        <v>-6.568408224000001</v>
+      </c>
+      <c r="Q91">
+        <v>-3.878408224000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5617808820285715</v>
+      </c>
+      <c r="T91">
+        <v>8.842739803157475</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.03012876368418122</v>
+      </c>
+      <c r="W91">
+        <v>0.2316052512322175</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1076027274435043</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2699245706198165</v>
+      </c>
+      <c r="C92">
+        <v>-28.50128529758702</v>
+      </c>
+      <c r="D92">
+        <v>13.35871470241298</v>
+      </c>
+      <c r="E92">
+        <v>30.99</v>
+      </c>
+      <c r="F92">
+        <v>43.29</v>
+      </c>
+      <c r="G92">
+        <v>1.43</v>
+      </c>
+      <c r="H92">
+        <v>35.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>3.79</v>
+      </c>
+      <c r="K92">
+        <v>2.69</v>
+      </c>
+      <c r="L92">
+        <v>1.1</v>
+      </c>
+      <c r="M92">
+        <v>10.337652</v>
+      </c>
+      <c r="N92">
+        <v>-9.237652000000001</v>
+      </c>
+      <c r="O92">
+        <v>-2.586542559999999</v>
+      </c>
+      <c r="P92">
+        <v>-6.651109440000001</v>
+      </c>
+      <c r="Q92">
+        <v>-3.961109440000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6140789702314287</v>
+      </c>
+      <c r="T92">
+        <v>9.727013783473224</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.02979399964324587</v>
+      </c>
+      <c r="W92">
+        <v>0.2316851928851929</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1064071415830209</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2719245706198165</v>
+      </c>
+      <c r="C93">
+        <v>-29.08888964002543</v>
+      </c>
+      <c r="D93">
+        <v>13.25211035997456</v>
+      </c>
+      <c r="E93">
+        <v>31.47099999999999</v>
+      </c>
+      <c r="F93">
+        <v>43.77099999999999</v>
+      </c>
+      <c r="G93">
+        <v>1.43</v>
+      </c>
+      <c r="H93">
+        <v>35.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>3.79</v>
+      </c>
+      <c r="K93">
+        <v>2.69</v>
+      </c>
+      <c r="L93">
+        <v>1.1</v>
+      </c>
+      <c r="M93">
+        <v>10.4525148</v>
+      </c>
+      <c r="N93">
+        <v>-9.3525148</v>
+      </c>
+      <c r="O93">
+        <v>-2.618704143999999</v>
+      </c>
+      <c r="P93">
+        <v>-6.733810656000001</v>
+      </c>
+      <c r="Q93">
+        <v>-4.043810656000002</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6779988558126986</v>
+      </c>
+      <c r="T93">
+        <v>10.80779309274803</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.02946659305375965</v>
+      </c>
+      <c r="W93">
+        <v>0.2317633775787622</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1052378323348558</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2739245706198165</v>
+      </c>
+      <c r="C94">
+        <v>-29.67480601862298</v>
+      </c>
+      <c r="D94">
+        <v>13.14719398137702</v>
+      </c>
+      <c r="E94">
+        <v>31.95199999999999</v>
+      </c>
+      <c r="F94">
+        <v>44.252</v>
+      </c>
+      <c r="G94">
+        <v>1.43</v>
+      </c>
+      <c r="H94">
+        <v>35.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>3.79</v>
+      </c>
+      <c r="K94">
+        <v>2.69</v>
+      </c>
+      <c r="L94">
+        <v>1.1</v>
+      </c>
+      <c r="M94">
+        <v>10.5673776</v>
+      </c>
+      <c r="N94">
+        <v>-9.467377599999999</v>
+      </c>
+      <c r="O94">
+        <v>-2.650865727999999</v>
+      </c>
+      <c r="P94">
+        <v>-6.816511872</v>
+      </c>
+      <c r="Q94">
+        <v>-4.126511872</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7578987127892862</v>
+      </c>
+      <c r="T94">
+        <v>12.15876722934154</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02914630399882748</v>
+      </c>
+      <c r="W94">
+        <v>0.23183986260508</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1040939428529553</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2759245706198165</v>
+      </c>
+      <c r="C95">
+        <v>-30.25907420908503</v>
+      </c>
+      <c r="D95">
+        <v>13.04392579091497</v>
+      </c>
+      <c r="E95">
+        <v>32.43299999999999</v>
+      </c>
+      <c r="F95">
+        <v>44.733</v>
+      </c>
+      <c r="G95">
+        <v>1.43</v>
+      </c>
+      <c r="H95">
+        <v>35.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>3.79</v>
+      </c>
+      <c r="K95">
+        <v>2.69</v>
+      </c>
+      <c r="L95">
+        <v>1.1</v>
+      </c>
+      <c r="M95">
+        <v>10.6822404</v>
+      </c>
+      <c r="N95">
+        <v>-9.5822404</v>
+      </c>
+      <c r="O95">
+        <v>-2.683027311999999</v>
+      </c>
+      <c r="P95">
+        <v>-6.899213088000001</v>
+      </c>
+      <c r="Q95">
+        <v>-4.209213088</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.860627100330613</v>
+      </c>
+      <c r="T95">
+        <v>13.89573397639033</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.02883290288056052</v>
+      </c>
+      <c r="W95">
+        <v>0.2319147027921222</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.102974653144859</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2779245706198165</v>
+      </c>
+      <c r="C96">
+        <v>-30.84173274714055</v>
+      </c>
+      <c r="D96">
+        <v>12.94226725285945</v>
+      </c>
+      <c r="E96">
+        <v>32.914</v>
+      </c>
+      <c r="F96">
+        <v>45.214</v>
+      </c>
+      <c r="G96">
+        <v>1.43</v>
+      </c>
+      <c r="H96">
+        <v>35.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>3.79</v>
+      </c>
+      <c r="K96">
+        <v>2.69</v>
+      </c>
+      <c r="L96">
+        <v>1.1</v>
+      </c>
+      <c r="M96">
+        <v>10.7971032</v>
+      </c>
+      <c r="N96">
+        <v>-9.697103200000001</v>
+      </c>
+      <c r="O96">
+        <v>-2.715188895999999</v>
+      </c>
+      <c r="P96">
+        <v>-6.981914304000002</v>
+      </c>
+      <c r="Q96">
+        <v>-4.291914304000002</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9975982837190485</v>
+      </c>
+      <c r="T96">
+        <v>16.21168963912205</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02852616987119285</v>
+      </c>
+      <c r="W96">
+        <v>0.2319879506347592</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.101879178111403</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2799245706198165</v>
+      </c>
+      <c r="C97">
+        <v>-31.42281897648753</v>
+      </c>
+      <c r="D97">
+        <v>12.84218102351247</v>
+      </c>
+      <c r="E97">
+        <v>33.395</v>
+      </c>
+      <c r="F97">
+        <v>45.695</v>
+      </c>
+      <c r="G97">
+        <v>1.43</v>
+      </c>
+      <c r="H97">
+        <v>35.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>3.79</v>
+      </c>
+      <c r="K97">
+        <v>2.69</v>
+      </c>
+      <c r="L97">
+        <v>1.1</v>
+      </c>
+      <c r="M97">
+        <v>10.911966</v>
+      </c>
+      <c r="N97">
+        <v>-9.811966000000002</v>
+      </c>
+      <c r="O97">
+        <v>-2.74735048</v>
+      </c>
+      <c r="P97">
+        <v>-7.064615520000002</v>
+      </c>
+      <c r="Q97">
+        <v>-4.374615520000003</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.189357940462859</v>
+      </c>
+      <c r="T97">
+        <v>19.45402756694647</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.0282258943988645</v>
+      </c>
+      <c r="W97">
+        <v>0.2320596564175512</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1008067657102304</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2819245706198165</v>
+      </c>
+      <c r="C98">
+        <v>-32.00236909453088</v>
+      </c>
+      <c r="D98">
+        <v>12.74363090546911</v>
+      </c>
+      <c r="E98">
+        <v>33.87599999999999</v>
+      </c>
+      <c r="F98">
+        <v>46.17599999999999</v>
+      </c>
+      <c r="G98">
+        <v>1.43</v>
+      </c>
+      <c r="H98">
+        <v>35.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>3.79</v>
+      </c>
+      <c r="K98">
+        <v>2.69</v>
+      </c>
+      <c r="L98">
+        <v>1.1</v>
+      </c>
+      <c r="M98">
+        <v>11.0268288</v>
+      </c>
+      <c r="N98">
+        <v>-9.926828799999999</v>
+      </c>
+      <c r="O98">
+        <v>-2.779512063999999</v>
+      </c>
+      <c r="P98">
+        <v>-7.147316736000001</v>
+      </c>
+      <c r="Q98">
+        <v>-4.457316736000001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.47699742557857</v>
+      </c>
+      <c r="T98">
+        <v>24.31753445868303</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.02793187466554301</v>
+      </c>
+      <c r="W98">
+        <v>0.2321298683298683</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.09975669523408215</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2839245706198165</v>
+      </c>
+      <c r="C99">
+        <v>-32.58041819603043</v>
+      </c>
+      <c r="D99">
+        <v>12.64658180396957</v>
+      </c>
+      <c r="E99">
+        <v>34.357</v>
+      </c>
+      <c r="F99">
+        <v>46.657</v>
+      </c>
+      <c r="G99">
+        <v>1.43</v>
+      </c>
+      <c r="H99">
+        <v>35.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>3.79</v>
+      </c>
+      <c r="K99">
+        <v>2.69</v>
+      </c>
+      <c r="L99">
+        <v>1.1</v>
+      </c>
+      <c r="M99">
+        <v>11.1416916</v>
+      </c>
+      <c r="N99">
+        <v>-10.0416916</v>
+      </c>
+      <c r="O99">
+        <v>-2.811673647999999</v>
+      </c>
+      <c r="P99">
+        <v>-7.230017952000001</v>
+      </c>
+      <c r="Q99">
+        <v>-4.540017952000001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.956396567438093</v>
+      </c>
+      <c r="T99">
+        <v>32.42337927824404</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.02764391719476421</v>
+      </c>
+      <c r="W99">
+        <v>0.2321986325738903</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.0987282756955864</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2859245706198165</v>
+      </c>
+      <c r="C100">
+        <v>-33.15700031476943</v>
+      </c>
+      <c r="D100">
+        <v>12.55099968523057</v>
+      </c>
+      <c r="E100">
+        <v>34.83799999999999</v>
+      </c>
+      <c r="F100">
+        <v>47.13799999999999</v>
+      </c>
+      <c r="G100">
+        <v>1.43</v>
+      </c>
+      <c r="H100">
+        <v>35.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>3.79</v>
+      </c>
+      <c r="K100">
+        <v>2.69</v>
+      </c>
+      <c r="L100">
+        <v>1.1</v>
+      </c>
+      <c r="M100">
+        <v>11.2565544</v>
+      </c>
+      <c r="N100">
+        <v>-10.1565544</v>
+      </c>
+      <c r="O100">
+        <v>-2.843835231999999</v>
+      </c>
+      <c r="P100">
+        <v>-7.312719168</v>
+      </c>
+      <c r="Q100">
+        <v>-4.622719168</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.915194851157141</v>
+      </c>
+      <c r="T100">
+        <v>48.63506891736607</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.02736183640706253</v>
+      </c>
+      <c r="W100">
+        <v>0.2322659934659935</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.09772084431093764</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2879245706198165</v>
+      </c>
+      <c r="C101">
+        <v>-33.73214846334794</v>
+      </c>
+      <c r="D101">
+        <v>12.45685153665206</v>
+      </c>
+      <c r="E101">
+        <v>35.31899999999999</v>
+      </c>
+      <c r="F101">
+        <v>47.61899999999999</v>
+      </c>
+      <c r="G101">
+        <v>1.43</v>
+      </c>
+      <c r="H101">
+        <v>35.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>3.79</v>
+      </c>
+      <c r="K101">
+        <v>2.69</v>
+      </c>
+      <c r="L101">
+        <v>1.1</v>
+      </c>
+      <c r="M101">
+        <v>11.3714172</v>
+      </c>
+      <c r="N101">
+        <v>-10.2714172</v>
+      </c>
+      <c r="O101">
+        <v>-2.875996815999998</v>
+      </c>
+      <c r="P101">
+        <v>-7.395420383999999</v>
+      </c>
+      <c r="Q101">
+        <v>-4.705420384</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.791589702314281</v>
+      </c>
+      <c r="T101">
+        <v>97.27013783473214</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.02708545422113261</v>
+      </c>
+      <c r="W101">
+        <v>0.2323319935319935</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.0967337650754736</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/new_zealand/new_zealand_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_business_consumer_services.xlsx
@@ -1403,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1540,22 +1540,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08708711407311603</v>
+        <v>0.08688647015371131</v>
       </c>
       <c r="C2">
-        <v>16.37435995042393</v>
+        <v>16.24309598450483</v>
       </c>
       <c r="D2">
-        <v>8.814359950423926</v>
+        <v>8.846995984504829</v>
       </c>
       <c r="E2">
-        <v>-0.09</v>
+        <v>0.07390000000000002</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1639</v>
       </c>
       <c r="G2">
         <v>7.56</v>
@@ -1576,45 +1576,45 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.008490020000000001</v>
       </c>
       <c r="N2">
-        <v>0.09200000000000003</v>
+        <v>0.08350998000000003</v>
       </c>
       <c r="O2">
-        <v>0.02576000000000001</v>
+        <v>0.02338279440000001</v>
       </c>
       <c r="P2">
-        <v>0.06624000000000002</v>
+        <v>0.06012718560000001</v>
       </c>
       <c r="Q2">
-        <v>0.52424</v>
+        <v>0.5181271856</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08708711407311603</v>
+        <v>0.08738738399364779</v>
       </c>
       <c r="T2">
-        <v>0.9535130270927493</v>
+        <v>0.9604476672897876</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V2">
         <v>0.28</v>
       </c>
       <c r="W2">
-        <v>0.036216</v>
+        <v>0.037296</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>10.8362524469907</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08688647015371131</v>
+        <v>0.08673622623430659</v>
       </c>
       <c r="C3">
-        <v>16.24309598450483</v>
+        <v>16.10379281216959</v>
       </c>
       <c r="D3">
-        <v>8.846995984504829</v>
+        <v>8.871592812169592</v>
       </c>
       <c r="E3">
-        <v>0.07390000000000002</v>
+        <v>0.2378</v>
       </c>
       <c r="F3">
-        <v>0.1639</v>
+        <v>0.3278</v>
       </c>
       <c r="G3">
         <v>7.56</v>
@@ -1658,45 +1658,45 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M3">
-        <v>0.008490020000000001</v>
+        <v>0.01812734</v>
       </c>
       <c r="N3">
-        <v>0.08350998000000003</v>
+        <v>0.07387266000000002</v>
       </c>
       <c r="O3">
-        <v>0.02338279440000001</v>
+        <v>0.02068434480000001</v>
       </c>
       <c r="P3">
-        <v>0.06012718560000001</v>
+        <v>0.05318831520000002</v>
       </c>
       <c r="Q3">
-        <v>0.5181271856</v>
+        <v>0.5111883152000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08738738399364779</v>
+        <v>0.08769378187174141</v>
       </c>
       <c r="T3">
-        <v>0.9604476672897876</v>
+        <v>0.9675238307561529</v>
       </c>
       <c r="U3">
-        <v>0.0518</v>
+        <v>0.0553</v>
       </c>
       <c r="V3">
         <v>0.28</v>
       </c>
       <c r="W3">
-        <v>0.037296</v>
+        <v>0.039816</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y3">
-        <v>10.8362524469907</v>
+        <v>5.075206842261468</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1704,22 +1704,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08673622623430659</v>
+        <v>0.08691934231490187</v>
       </c>
       <c r="C4">
-        <v>16.10379281216959</v>
+        <v>15.90993257059033</v>
       </c>
       <c r="D4">
-        <v>8.871592812169592</v>
+        <v>8.841632570590326</v>
       </c>
       <c r="E4">
-        <v>0.2378</v>
+        <v>0.4017000000000001</v>
       </c>
       <c r="F4">
-        <v>0.3278</v>
+        <v>0.4917</v>
       </c>
       <c r="G4">
         <v>7.56</v>
@@ -1740,45 +1740,45 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M4">
-        <v>0.01812734</v>
+        <v>0.03535323000000001</v>
       </c>
       <c r="N4">
-        <v>0.07387266000000002</v>
+        <v>0.05664677000000002</v>
       </c>
       <c r="O4">
-        <v>0.02068434480000001</v>
+        <v>0.01586109560000001</v>
       </c>
       <c r="P4">
-        <v>0.05318831520000002</v>
+        <v>0.04078567440000001</v>
       </c>
       <c r="Q4">
-        <v>0.5111883152000001</v>
+        <v>0.4987856744</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08769378187174141</v>
+        <v>0.08800649723185759</v>
       </c>
       <c r="T4">
-        <v>0.9675238307561529</v>
+        <v>0.9747458945001756</v>
       </c>
       <c r="U4">
-        <v>0.0553</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V4">
         <v>0.28</v>
       </c>
       <c r="W4">
-        <v>0.039816</v>
+        <v>0.051768</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y4">
-        <v>5.075206842261468</v>
+        <v>2.602308190793317</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08691934231490187</v>
+        <v>0.08738469839549712</v>
       </c>
       <c r="C5">
-        <v>15.90993257059033</v>
+        <v>15.67079690813823</v>
       </c>
       <c r="D5">
-        <v>8.841632570590326</v>
+        <v>8.766396908138228</v>
       </c>
       <c r="E5">
-        <v>0.4017000000000001</v>
+        <v>0.5656000000000001</v>
       </c>
       <c r="F5">
-        <v>0.4917</v>
+        <v>0.6556000000000001</v>
       </c>
       <c r="G5">
         <v>7.56</v>
@@ -1822,45 +1822,45 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M5">
-        <v>0.03535323000000001</v>
+        <v>0.059004</v>
       </c>
       <c r="N5">
-        <v>0.05664677000000002</v>
+        <v>0.03299600000000003</v>
       </c>
       <c r="O5">
-        <v>0.01586109560000001</v>
+        <v>0.009238880000000008</v>
       </c>
       <c r="P5">
-        <v>0.04078567440000001</v>
+        <v>0.02375712000000002</v>
       </c>
       <c r="Q5">
-        <v>0.4987856744</v>
+        <v>0.48175712</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08800649723185759</v>
+        <v>0.08832572749530951</v>
       </c>
       <c r="T5">
-        <v>0.9747458945001756</v>
+        <v>0.9821184179055318</v>
       </c>
       <c r="U5">
-        <v>0.07190000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V5">
         <v>0.28</v>
       </c>
       <c r="W5">
-        <v>0.051768</v>
+        <v>0.0648</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y5">
-        <v>2.602308190793317</v>
+        <v>1.559216324316996</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1868,22 +1868,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08738469839549712</v>
+        <v>0.09294226392565115</v>
       </c>
       <c r="C6">
-        <v>15.67079690813823</v>
+        <v>14.69821307406755</v>
       </c>
       <c r="D6">
-        <v>8.766396908138228</v>
+        <v>7.957713074067547</v>
       </c>
       <c r="E6">
-        <v>0.5656000000000001</v>
+        <v>0.7295000000000001</v>
       </c>
       <c r="F6">
-        <v>0.6556000000000001</v>
+        <v>0.8195000000000001</v>
       </c>
       <c r="G6">
         <v>7.56</v>
@@ -1904,45 +1904,45 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M6">
-        <v>0.059004</v>
+        <v>0.1645556</v>
       </c>
       <c r="N6">
-        <v>0.03299600000000003</v>
+        <v>-0.0725556</v>
       </c>
       <c r="O6">
-        <v>0.009238880000000008</v>
+        <v>-0.020315568</v>
       </c>
       <c r="P6">
-        <v>0.02375712000000002</v>
+        <v>-0.05224003199999999</v>
       </c>
       <c r="Q6">
-        <v>0.48175712</v>
+        <v>0.405759968</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08832572749530951</v>
+        <v>0.08891995155848703</v>
       </c>
       <c r="T6">
-        <v>0.9821184179055318</v>
+        <v>0.9958418373784536</v>
       </c>
       <c r="U6">
-        <v>0.09</v>
+        <v>0.2008</v>
       </c>
       <c r="V6">
-        <v>0.28</v>
+        <v>0.156542834154535</v>
       </c>
       <c r="W6">
-        <v>0.0648</v>
+        <v>0.1693661989017693</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y6">
-        <v>1.559216324316996</v>
+        <v>0.5590815505519108</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09294226392565115</v>
+        <v>0.09664023086050852</v>
       </c>
       <c r="C7">
-        <v>14.69821307406755</v>
+        <v>14.07410640456178</v>
       </c>
       <c r="D7">
-        <v>7.957713074067547</v>
+        <v>7.497506404561781</v>
       </c>
       <c r="E7">
-        <v>0.7295000000000001</v>
+        <v>0.8934000000000002</v>
       </c>
       <c r="F7">
-        <v>0.8195000000000001</v>
+        <v>0.9834000000000002</v>
       </c>
       <c r="G7">
         <v>7.56</v>
@@ -1986,45 +1986,45 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M7">
-        <v>0.1645556</v>
+        <v>0.23188572</v>
       </c>
       <c r="N7">
-        <v>-0.0725556</v>
+        <v>-0.13988572</v>
       </c>
       <c r="O7">
-        <v>-0.020315568</v>
+        <v>-0.03916800160000001</v>
       </c>
       <c r="P7">
-        <v>-0.05224003199999999</v>
+        <v>-0.1007177184</v>
       </c>
       <c r="Q7">
-        <v>0.405759968</v>
+        <v>0.3572822816</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08891995155848703</v>
+        <v>0.08942970310151069</v>
       </c>
       <c r="T7">
-        <v>0.9958418373784536</v>
+        <v>1.00761439033512</v>
       </c>
       <c r="U7">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>0.156542834154535</v>
+        <v>0.111089203768132</v>
       </c>
       <c r="W7">
-        <v>0.1693661989017693</v>
+        <v>0.2096051657514745</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y7">
-        <v>0.5590815505519108</v>
+        <v>0.3967471563147571</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2032,22 +2032,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09664023086050852</v>
+        <v>0.09854023086050853</v>
       </c>
       <c r="C8">
-        <v>14.07410640456178</v>
+        <v>13.69385704788618</v>
       </c>
       <c r="D8">
-        <v>7.497506404561781</v>
+        <v>7.28115704788618</v>
       </c>
       <c r="E8">
-        <v>0.8934000000000001</v>
+        <v>1.0573</v>
       </c>
       <c r="F8">
-        <v>0.9834000000000001</v>
+        <v>1.1473</v>
       </c>
       <c r="G8">
         <v>7.56</v>
@@ -2068,37 +2068,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M8">
-        <v>0.23188572</v>
+        <v>0.27053334</v>
       </c>
       <c r="N8">
-        <v>-0.13988572</v>
+        <v>-0.17853334</v>
       </c>
       <c r="O8">
-        <v>-0.0391680016</v>
+        <v>-0.0499893352</v>
       </c>
       <c r="P8">
-        <v>-0.1007177184</v>
+        <v>-0.1285440048</v>
       </c>
       <c r="Q8">
-        <v>0.3572822816</v>
+        <v>0.3294559952</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08942970310151069</v>
+        <v>0.08989883969400006</v>
       </c>
       <c r="T8">
-        <v>1.00761439033512</v>
+        <v>1.018448953672057</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>0.111089203768132</v>
+        <v>0.09521931751554173</v>
       </c>
       <c r="W8">
-        <v>0.2096051657514745</v>
+        <v>0.2133472849298353</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>0.3967471563147572</v>
+        <v>0.3400689911269348</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2114,22 +2114,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09854023086050852</v>
+        <v>0.1004402308605085</v>
       </c>
       <c r="C9">
-        <v>13.69385704788618</v>
+        <v>13.32574352718749</v>
       </c>
       <c r="D9">
-        <v>7.281157047886182</v>
+        <v>7.076943527187488</v>
       </c>
       <c r="E9">
-        <v>1.0573</v>
+        <v>1.2212</v>
       </c>
       <c r="F9">
-        <v>1.1473</v>
+        <v>1.3112</v>
       </c>
       <c r="G9">
         <v>7.56</v>
@@ -2150,37 +2150,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M9">
-        <v>0.2705333400000001</v>
+        <v>0.3091809600000001</v>
       </c>
       <c r="N9">
-        <v>-0.17853334</v>
+        <v>-0.21718096</v>
       </c>
       <c r="O9">
-        <v>-0.04998933520000002</v>
+        <v>-0.06081066880000002</v>
       </c>
       <c r="P9">
-        <v>-0.1285440048</v>
+        <v>-0.1563702912</v>
       </c>
       <c r="Q9">
-        <v>0.3294559952</v>
+        <v>0.3016297088</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08989883969400006</v>
+        <v>0.09037817490806527</v>
       </c>
       <c r="T9">
-        <v>1.018448953672057</v>
+        <v>1.029519050994579</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>0.09521931751554172</v>
+        <v>0.08331690282609902</v>
       </c>
       <c r="W9">
-        <v>0.2133472849298353</v>
+        <v>0.2161538743136059</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>0.3400689911269347</v>
+        <v>0.2975603672360678</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2196,22 +2196,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1004402308605085</v>
+        <v>0.1023402308605085</v>
       </c>
       <c r="C10">
-        <v>13.32574352718749</v>
+        <v>12.96877258430884</v>
       </c>
       <c r="D10">
-        <v>7.076943527187488</v>
+        <v>6.883872584308835</v>
       </c>
       <c r="E10">
-        <v>1.2212</v>
+        <v>1.3851</v>
       </c>
       <c r="F10">
-        <v>1.3112</v>
+        <v>1.4751</v>
       </c>
       <c r="G10">
         <v>7.56</v>
@@ -2232,37 +2232,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M10">
-        <v>0.3091809600000001</v>
+        <v>0.3478285800000001</v>
       </c>
       <c r="N10">
-        <v>-0.21718096</v>
+        <v>-0.25582858</v>
       </c>
       <c r="O10">
-        <v>-0.06081066880000002</v>
+        <v>-0.07163200240000002</v>
       </c>
       <c r="P10">
-        <v>-0.1563702912</v>
+        <v>-0.1841965776</v>
       </c>
       <c r="Q10">
-        <v>0.3016297088</v>
+        <v>0.2738034224</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09037817490806527</v>
+        <v>0.09086804496200006</v>
       </c>
       <c r="T10">
-        <v>1.029519050994579</v>
+        <v>1.040832447159355</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>0.08331690282609902</v>
+        <v>0.07405946917875468</v>
       </c>
       <c r="W10">
-        <v>0.2161538743136059</v>
+        <v>0.2183367771676497</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.2975603672360678</v>
+        <v>0.2644981042098381</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2278,22 +2278,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1023402308605085</v>
+        <v>0.1042402308605085</v>
       </c>
       <c r="C11">
-        <v>12.96877258430884</v>
+        <v>12.62205647355949</v>
       </c>
       <c r="D11">
-        <v>6.883872584308835</v>
+        <v>6.701056473559485</v>
       </c>
       <c r="E11">
-        <v>1.3851</v>
+        <v>1.549</v>
       </c>
       <c r="F11">
-        <v>1.4751</v>
+        <v>1.639</v>
       </c>
       <c r="G11">
         <v>7.56</v>
@@ -2314,37 +2314,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M11">
-        <v>0.3478285800000001</v>
+        <v>0.3864762</v>
       </c>
       <c r="N11">
-        <v>-0.25582858</v>
+        <v>-0.2944762</v>
       </c>
       <c r="O11">
-        <v>-0.07163200240000002</v>
+        <v>-0.082453336</v>
       </c>
       <c r="P11">
-        <v>-0.1841965776</v>
+        <v>-0.212022864</v>
       </c>
       <c r="Q11">
-        <v>0.2738034224</v>
+        <v>0.245977136</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09086804496200006</v>
+        <v>0.09136880101713338</v>
       </c>
       <c r="T11">
-        <v>1.040832447159355</v>
+        <v>1.052397252127792</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.07405946917875468</v>
+        <v>0.06665352226087921</v>
       </c>
       <c r="W11">
-        <v>0.2183367771676497</v>
+        <v>0.2200830994508847</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.2644981042098381</v>
+        <v>0.2380482937888544</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1042402308605085</v>
+        <v>0.1061402308605085</v>
       </c>
       <c r="C12">
-        <v>12.62205647355949</v>
+        <v>12.28479931361206</v>
       </c>
       <c r="D12">
-        <v>6.701056473559485</v>
+        <v>6.527699313612055</v>
       </c>
       <c r="E12">
-        <v>1.549</v>
+        <v>1.7129</v>
       </c>
       <c r="F12">
-        <v>1.639</v>
+        <v>1.8029</v>
       </c>
       <c r="G12">
         <v>7.56</v>
@@ -2396,37 +2396,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M12">
-        <v>0.3864762</v>
+        <v>0.42512382</v>
       </c>
       <c r="N12">
-        <v>-0.2944762</v>
+        <v>-0.33312382</v>
       </c>
       <c r="O12">
-        <v>-0.08245333600000002</v>
+        <v>-0.09327466960000001</v>
       </c>
       <c r="P12">
-        <v>-0.212022864</v>
+        <v>-0.2398491504</v>
       </c>
       <c r="Q12">
-        <v>0.245977136</v>
+        <v>0.2181508496</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09136880101713338</v>
+        <v>0.0918808100173259</v>
       </c>
       <c r="T12">
-        <v>1.052397252127792</v>
+        <v>1.064221940353947</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.06665352226087921</v>
+        <v>0.06059411114625383</v>
       </c>
       <c r="W12">
-        <v>0.2200830994508847</v>
+        <v>0.2215119085917134</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.2380482937888543</v>
+        <v>0.2164075398080494</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2442,22 +2442,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1061402308605085</v>
+        <v>0.1080402308605085</v>
       </c>
       <c r="C13">
-        <v>12.28479931361206</v>
+        <v>11.95628550444543</v>
       </c>
       <c r="D13">
-        <v>6.527699313612055</v>
+        <v>6.363085504445425</v>
       </c>
       <c r="E13">
-        <v>1.7129</v>
+        <v>1.8768</v>
       </c>
       <c r="F13">
-        <v>1.8029</v>
+        <v>1.9668</v>
       </c>
       <c r="G13">
         <v>7.56</v>
@@ -2478,37 +2478,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M13">
-        <v>0.42512382</v>
+        <v>0.46377144</v>
       </c>
       <c r="N13">
-        <v>-0.33312382</v>
+        <v>-0.37177144</v>
       </c>
       <c r="O13">
-        <v>-0.09327466960000001</v>
+        <v>-0.1040960032</v>
       </c>
       <c r="P13">
-        <v>-0.2398491504</v>
+        <v>-0.2676754368</v>
       </c>
       <c r="Q13">
-        <v>0.2181508496</v>
+        <v>0.1903245632</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0918808100173259</v>
+        <v>0.09240445558570459</v>
       </c>
       <c r="T13">
-        <v>1.064221940353947</v>
+        <v>1.076315371494333</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.06059411114625383</v>
+        <v>0.05554460188406601</v>
       </c>
       <c r="W13">
-        <v>0.2215119085917134</v>
+        <v>0.2227025828757372</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.2164075398080494</v>
+        <v>0.1983735781573785</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1080402308605085</v>
+        <v>0.1099402308605085</v>
       </c>
       <c r="C14">
-        <v>11.95628550444543</v>
+        <v>11.63586985376935</v>
       </c>
       <c r="D14">
-        <v>6.363085504445425</v>
+        <v>6.206569853769351</v>
       </c>
       <c r="E14">
-        <v>1.8768</v>
+        <v>2.0407</v>
       </c>
       <c r="F14">
-        <v>1.9668</v>
+        <v>2.1307</v>
       </c>
       <c r="G14">
         <v>7.56</v>
@@ -2560,37 +2560,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M14">
-        <v>0.46377144</v>
+        <v>0.50241906</v>
       </c>
       <c r="N14">
-        <v>-0.37177144</v>
+        <v>-0.41041906</v>
       </c>
       <c r="O14">
-        <v>-0.1040960032</v>
+        <v>-0.1149173368</v>
       </c>
       <c r="P14">
-        <v>-0.2676754368</v>
+        <v>-0.2955017232</v>
       </c>
       <c r="Q14">
-        <v>0.1903245632</v>
+        <v>0.1624982768</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09240445558570459</v>
+        <v>0.09294013898324144</v>
       </c>
       <c r="T14">
-        <v>1.076315371494333</v>
+        <v>1.088686812545992</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.05554460188406601</v>
+        <v>0.05127194020067632</v>
       </c>
       <c r="W14">
-        <v>0.2227025828757372</v>
+        <v>0.2237100765006805</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.1983735781573785</v>
+        <v>0.1831140721452725</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2606,22 +2606,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1099402308605085</v>
+        <v>0.1118402308605085</v>
       </c>
       <c r="C15">
-        <v>11.63586985376935</v>
+        <v>11.32296912565485</v>
       </c>
       <c r="D15">
-        <v>6.206569853769351</v>
+        <v>6.057569125654854</v>
       </c>
       <c r="E15">
-        <v>2.0407</v>
+        <v>2.204600000000001</v>
       </c>
       <c r="F15">
-        <v>2.1307</v>
+        <v>2.2946</v>
       </c>
       <c r="G15">
         <v>7.56</v>
@@ -2642,37 +2642,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M15">
-        <v>0.50241906</v>
+        <v>0.5410666800000001</v>
       </c>
       <c r="N15">
-        <v>-0.41041906</v>
+        <v>-0.4490666800000001</v>
       </c>
       <c r="O15">
-        <v>-0.1149173368</v>
+        <v>-0.1257386704</v>
       </c>
       <c r="P15">
-        <v>-0.2955017232</v>
+        <v>-0.3233280096000001</v>
       </c>
       <c r="Q15">
-        <v>0.1624982768</v>
+        <v>0.1346719903999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09294013898324144</v>
+        <v>0.09348828013420937</v>
       </c>
       <c r="T15">
-        <v>1.088686812545992</v>
+        <v>1.101345961529085</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.05127194020067632</v>
+        <v>0.04760965875777086</v>
       </c>
       <c r="W15">
-        <v>0.2237100765006805</v>
+        <v>0.2245736424649176</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.1831140721452725</v>
+        <v>0.1700344955634674</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1118402308605085</v>
+        <v>0.1137402308605085</v>
       </c>
       <c r="C16">
-        <v>11.32296912565485</v>
+        <v>11.0170547779739</v>
       </c>
       <c r="D16">
-        <v>6.057569125654854</v>
+        <v>5.915554777973906</v>
       </c>
       <c r="E16">
-        <v>2.204600000000001</v>
+        <v>2.3685</v>
       </c>
       <c r="F16">
-        <v>2.2946</v>
+        <v>2.4585</v>
       </c>
       <c r="G16">
         <v>7.56</v>
@@ -2724,37 +2724,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M16">
-        <v>0.5410666800000001</v>
+        <v>0.5797143000000001</v>
       </c>
       <c r="N16">
-        <v>-0.4490666800000001</v>
+        <v>-0.4877143000000001</v>
       </c>
       <c r="O16">
-        <v>-0.1257386704</v>
+        <v>-0.136560004</v>
       </c>
       <c r="P16">
-        <v>-0.3233280096000001</v>
+        <v>-0.351154296</v>
       </c>
       <c r="Q16">
-        <v>0.1346719903999999</v>
+        <v>0.106845704</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09348828013420937</v>
+        <v>0.09404931872402358</v>
       </c>
       <c r="T16">
-        <v>1.101345961529085</v>
+        <v>1.114302972841192</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.04760965875777086</v>
+        <v>0.0444356815072528</v>
       </c>
       <c r="W16">
-        <v>0.2245736424649176</v>
+        <v>0.2253220663005898</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.1700344955634674</v>
+        <v>0.1586988625259028</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2770,22 +2770,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1137402308605085</v>
+        <v>0.1156402308605085</v>
       </c>
       <c r="C17">
-        <v>11.01705477797391</v>
+        <v>10.71764669802336</v>
       </c>
       <c r="D17">
-        <v>5.915554777973908</v>
+        <v>5.78004669802336</v>
       </c>
       <c r="E17">
-        <v>2.3685</v>
+        <v>2.5324</v>
       </c>
       <c r="F17">
-        <v>2.4585</v>
+        <v>2.6224</v>
       </c>
       <c r="G17">
         <v>7.56</v>
@@ -2806,37 +2806,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M17">
-        <v>0.5797143</v>
+        <v>0.6183619200000001</v>
       </c>
       <c r="N17">
-        <v>-0.4877143</v>
+        <v>-0.52636192</v>
       </c>
       <c r="O17">
-        <v>-0.136560004</v>
+        <v>-0.1473813376</v>
       </c>
       <c r="P17">
-        <v>-0.351154296</v>
+        <v>-0.3789805824</v>
       </c>
       <c r="Q17">
-        <v>0.106845704</v>
+        <v>0.07901941760000003</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09404931872402358</v>
+        <v>0.09462371537550006</v>
       </c>
       <c r="T17">
-        <v>1.114302972841192</v>
+        <v>1.127568484422634</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.04443568150725281</v>
+        <v>0.04165845141304951</v>
       </c>
       <c r="W17">
-        <v>0.2253220663005898</v>
+        <v>0.2259769371568029</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.1586988625259029</v>
+        <v>0.148780183618034</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2852,22 +2852,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1156402308605085</v>
+        <v>0.1175402308605085</v>
       </c>
       <c r="C18">
-        <v>10.71764669802336</v>
+        <v>10.4243077798591</v>
       </c>
       <c r="D18">
-        <v>5.78004669802336</v>
+        <v>5.650607779859103</v>
       </c>
       <c r="E18">
-        <v>2.5324</v>
+        <v>2.6963</v>
       </c>
       <c r="F18">
-        <v>2.6224</v>
+        <v>2.7863</v>
       </c>
       <c r="G18">
         <v>7.56</v>
@@ -2888,37 +2888,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M18">
-        <v>0.6183619200000001</v>
+        <v>0.6570095400000001</v>
       </c>
       <c r="N18">
-        <v>-0.52636192</v>
+        <v>-0.5650095400000001</v>
       </c>
       <c r="O18">
-        <v>-0.1473813376</v>
+        <v>-0.1582026712000001</v>
       </c>
       <c r="P18">
-        <v>-0.3789805824</v>
+        <v>-0.4068068688000001</v>
       </c>
       <c r="Q18">
-        <v>0.07901941760000003</v>
+        <v>0.05119313119999996</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09462371537550006</v>
+        <v>0.09521195291014464</v>
       </c>
       <c r="T18">
-        <v>1.127568484422634</v>
+        <v>1.141153646885558</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.04165845141304951</v>
+        <v>0.03920795427110542</v>
       </c>
       <c r="W18">
-        <v>0.2259769371568029</v>
+        <v>0.2265547643828733</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.148780183618034</v>
+        <v>0.1400284081110906</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1175402308605085</v>
+        <v>0.1194402308605085</v>
       </c>
       <c r="C19">
-        <v>10.4243077798591</v>
+        <v>10.13663921428514</v>
       </c>
       <c r="D19">
-        <v>5.650607779859103</v>
+        <v>5.526839214285143</v>
       </c>
       <c r="E19">
-        <v>2.6963</v>
+        <v>2.860200000000001</v>
       </c>
       <c r="F19">
-        <v>2.7863</v>
+        <v>2.950200000000001</v>
       </c>
       <c r="G19">
         <v>7.56</v>
@@ -2970,37 +2970,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M19">
-        <v>0.6570095400000001</v>
+        <v>0.6956571600000002</v>
       </c>
       <c r="N19">
-        <v>-0.5650095400000001</v>
+        <v>-0.6036571600000002</v>
       </c>
       <c r="O19">
-        <v>-0.1582026712000001</v>
+        <v>-0.1690240048000001</v>
       </c>
       <c r="P19">
-        <v>-0.4068068688000001</v>
+        <v>-0.4346331552000002</v>
       </c>
       <c r="Q19">
-        <v>0.05119313119999996</v>
+        <v>0.02336684479999984</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09521195291014464</v>
+        <v>0.09581453770173176</v>
       </c>
       <c r="T19">
-        <v>1.141153646885558</v>
+        <v>1.155070154774406</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.03920795427110542</v>
+        <v>0.03702973458937733</v>
       </c>
       <c r="W19">
-        <v>0.2265547643828733</v>
+        <v>0.2270683885838248</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.1400284081110906</v>
+        <v>0.132249052104919</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1194402308605085</v>
+        <v>0.1213402308605085</v>
       </c>
       <c r="C20">
-        <v>10.13663921428514</v>
+        <v>9.854276384571765</v>
       </c>
       <c r="D20">
-        <v>5.526839214285143</v>
+        <v>5.408376384571767</v>
       </c>
       <c r="E20">
-        <v>2.8602</v>
+        <v>3.0241</v>
       </c>
       <c r="F20">
-        <v>2.9502</v>
+        <v>3.1141</v>
       </c>
       <c r="G20">
         <v>7.56</v>
@@ -3052,37 +3052,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M20">
-        <v>0.6956571600000001</v>
+        <v>0.7343047800000001</v>
       </c>
       <c r="N20">
-        <v>-0.60365716</v>
+        <v>-0.6423047800000001</v>
       </c>
       <c r="O20">
-        <v>-0.1690240048</v>
+        <v>-0.1798453384000001</v>
       </c>
       <c r="P20">
-        <v>-0.4346331552</v>
+        <v>-0.4624594416000001</v>
       </c>
       <c r="Q20">
-        <v>0.02336684480000001</v>
+        <v>-0.004459441600000058</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09581453770173176</v>
+        <v>0.09643200113014821</v>
       </c>
       <c r="T20">
-        <v>1.155070154774406</v>
+        <v>1.169330280141991</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.03702973458937734</v>
+        <v>0.03508080118993642</v>
       </c>
       <c r="W20">
-        <v>0.2270683885838248</v>
+        <v>0.227527947079413</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.1322490521049191</v>
+        <v>0.1252885756783443</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1213402308605085</v>
+        <v>0.1232402308605085</v>
       </c>
       <c r="C21">
-        <v>9.854276384571765</v>
+        <v>9.57688527892712</v>
       </c>
       <c r="D21">
-        <v>5.408376384571767</v>
+        <v>5.29488527892712</v>
       </c>
       <c r="E21">
-        <v>3.0241</v>
+        <v>3.188000000000001</v>
       </c>
       <c r="F21">
-        <v>3.1141</v>
+        <v>3.278</v>
       </c>
       <c r="G21">
         <v>7.56</v>
@@ -3134,37 +3134,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M21">
-        <v>0.7343047800000001</v>
+        <v>0.7729524000000001</v>
       </c>
       <c r="N21">
-        <v>-0.6423047800000001</v>
+        <v>-0.6809524</v>
       </c>
       <c r="O21">
-        <v>-0.1798453384000001</v>
+        <v>-0.190666672</v>
       </c>
       <c r="P21">
-        <v>-0.4624594416000001</v>
+        <v>-0.490285728</v>
       </c>
       <c r="Q21">
-        <v>-0.004459441600000058</v>
+        <v>-0.03228572800000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09643200113014821</v>
+        <v>0.09706490114427507</v>
       </c>
       <c r="T21">
-        <v>1.169330280141991</v>
+        <v>1.183946908643766</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.03508080118993642</v>
+        <v>0.03332676113043961</v>
       </c>
       <c r="W21">
-        <v>0.227527947079413</v>
+        <v>0.2279415497254423</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.1252885756783443</v>
+        <v>0.1190241468944272</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1232402308605085</v>
+        <v>0.1251402308605085</v>
       </c>
       <c r="C22">
-        <v>9.57688527892712</v>
+        <v>9.304159345376251</v>
       </c>
       <c r="D22">
-        <v>5.29488527892712</v>
+        <v>5.186059345376251</v>
       </c>
       <c r="E22">
-        <v>3.188000000000001</v>
+        <v>3.351900000000001</v>
       </c>
       <c r="F22">
-        <v>3.278</v>
+        <v>3.4419</v>
       </c>
       <c r="G22">
         <v>7.56</v>
@@ -3216,37 +3216,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M22">
-        <v>0.7729524000000001</v>
+        <v>0.8116000200000001</v>
       </c>
       <c r="N22">
-        <v>-0.6809524</v>
+        <v>-0.7196000200000001</v>
       </c>
       <c r="O22">
-        <v>-0.190666672</v>
+        <v>-0.2014880056</v>
       </c>
       <c r="P22">
-        <v>-0.490285728</v>
+        <v>-0.5181120144000001</v>
       </c>
       <c r="Q22">
-        <v>-0.03228572800000001</v>
+        <v>-0.06011201440000008</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09706490114427507</v>
+        <v>0.09771382394356969</v>
       </c>
       <c r="T22">
-        <v>1.183946908643766</v>
+        <v>1.198933578373434</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.03332676113043961</v>
+        <v>0.03173977250518058</v>
       </c>
       <c r="W22">
-        <v>0.2279415497254423</v>
+        <v>0.2283157616432784</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.1190241468944272</v>
+        <v>0.1133563303756449</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3262,22 +3262,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1251402308605085</v>
+        <v>0.1270402308605085</v>
       </c>
       <c r="C23">
-        <v>9.304159345376252</v>
+        <v>9.035816726679762</v>
       </c>
       <c r="D23">
-        <v>5.186059345376252</v>
+        <v>5.081616726679763</v>
       </c>
       <c r="E23">
-        <v>3.3519</v>
+        <v>3.5158</v>
       </c>
       <c r="F23">
-        <v>3.4419</v>
+        <v>3.6058</v>
       </c>
       <c r="G23">
         <v>7.56</v>
@@ -3298,37 +3298,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M23">
-        <v>0.81160002</v>
+        <v>0.8502476400000001</v>
       </c>
       <c r="N23">
-        <v>-0.7196000199999999</v>
+        <v>-0.75824764</v>
       </c>
       <c r="O23">
-        <v>-0.2014880056</v>
+        <v>-0.2123093392</v>
       </c>
       <c r="P23">
-        <v>-0.5181120143999999</v>
+        <v>-0.5459383007999999</v>
       </c>
       <c r="Q23">
-        <v>-0.06011201439999986</v>
+        <v>-0.08793830079999992</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09771382394356967</v>
+        <v>0.09837938578900006</v>
       </c>
       <c r="T23">
-        <v>1.198933578373434</v>
+        <v>1.214304521685914</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.03173977250518058</v>
+        <v>0.03029705557312692</v>
       </c>
       <c r="W23">
-        <v>0.2283157616432784</v>
+        <v>0.2286559542958567</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.113356330375645</v>
+        <v>0.1082037699040248</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3344,22 +3344,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1270402308605085</v>
+        <v>0.1289402308605085</v>
       </c>
       <c r="C24">
-        <v>9.035816726679762</v>
+        <v>8.771597822774142</v>
       </c>
       <c r="D24">
-        <v>5.081616726679763</v>
+        <v>4.981297822774143</v>
       </c>
       <c r="E24">
-        <v>3.5158</v>
+        <v>3.6797</v>
       </c>
       <c r="F24">
-        <v>3.6058</v>
+        <v>3.7697</v>
       </c>
       <c r="G24">
         <v>7.56</v>
@@ -3380,37 +3380,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M24">
-        <v>0.8502476400000001</v>
+        <v>0.8888952600000001</v>
       </c>
       <c r="N24">
-        <v>-0.75824764</v>
+        <v>-0.7968952600000001</v>
       </c>
       <c r="O24">
-        <v>-0.2123093392</v>
+        <v>-0.2231306728</v>
       </c>
       <c r="P24">
-        <v>-0.5459383007999999</v>
+        <v>-0.5737645872000001</v>
       </c>
       <c r="Q24">
-        <v>-0.08793830079999992</v>
+        <v>-0.1157645872000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09837938578900006</v>
+        <v>0.09906223495509096</v>
       </c>
       <c r="T24">
-        <v>1.214304521685914</v>
+        <v>1.230074710279237</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.03029705557312692</v>
+        <v>0.02897979228733879</v>
       </c>
       <c r="W24">
-        <v>0.2286559542958567</v>
+        <v>0.2289665649786455</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.1082037699040248</v>
+        <v>0.103499258169067</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1289402308605085</v>
+        <v>0.1308402308605085</v>
       </c>
       <c r="C25">
-        <v>8.771597822774142</v>
+        <v>8.511263136349504</v>
       </c>
       <c r="D25">
-        <v>4.981297822774143</v>
+        <v>4.884863136349504</v>
       </c>
       <c r="E25">
-        <v>3.6797</v>
+        <v>3.843600000000001</v>
       </c>
       <c r="F25">
-        <v>3.7697</v>
+        <v>3.933600000000001</v>
       </c>
       <c r="G25">
         <v>7.56</v>
@@ -3462,37 +3462,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M25">
-        <v>0.8888952600000001</v>
+        <v>0.9275428800000002</v>
       </c>
       <c r="N25">
-        <v>-0.7968952600000001</v>
+        <v>-0.8355428800000002</v>
       </c>
       <c r="O25">
-        <v>-0.2231306728</v>
+        <v>-0.2339520064000001</v>
       </c>
       <c r="P25">
-        <v>-0.5737645872000001</v>
+        <v>-0.6015908736000002</v>
       </c>
       <c r="Q25">
-        <v>-0.1157645872000001</v>
+        <v>-0.1435908736000002</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09906223495509096</v>
+        <v>0.09976305383607902</v>
       </c>
       <c r="T25">
-        <v>1.230074710279237</v>
+        <v>1.246259903835543</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.02897979228733879</v>
+        <v>0.027772300942033</v>
       </c>
       <c r="W25">
-        <v>0.2289665649786455</v>
+        <v>0.2292512914378686</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.103499258169067</v>
+        <v>0.09918678907868927</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3508,22 +3508,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1308402308605085</v>
+        <v>0.1327402308605085</v>
       </c>
       <c r="C26">
-        <v>8.511263136349504</v>
+        <v>8.254591363923968</v>
       </c>
       <c r="D26">
-        <v>4.884863136349504</v>
+        <v>4.792091363923969</v>
       </c>
       <c r="E26">
-        <v>3.8436</v>
+        <v>4.0075</v>
       </c>
       <c r="F26">
-        <v>3.9336</v>
+        <v>4.0975</v>
       </c>
       <c r="G26">
         <v>7.56</v>
@@ -3544,37 +3544,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M26">
-        <v>0.9275428800000001</v>
+        <v>0.9661905000000001</v>
       </c>
       <c r="N26">
-        <v>-0.83554288</v>
+        <v>-0.8741905000000001</v>
       </c>
       <c r="O26">
-        <v>-0.2339520064</v>
+        <v>-0.2447733400000001</v>
       </c>
       <c r="P26">
-        <v>-0.6015908736</v>
+        <v>-0.62941716</v>
       </c>
       <c r="Q26">
-        <v>-0.1435908735999999</v>
+        <v>-0.17141716</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09976305383607902</v>
+        <v>0.1004825612205601</v>
       </c>
       <c r="T26">
-        <v>1.246259903835543</v>
+        <v>1.26287670255335</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.02777230094203301</v>
+        <v>0.02666140890435169</v>
       </c>
       <c r="W26">
-        <v>0.2292512914378686</v>
+        <v>0.2295132397803539</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.09918678907868939</v>
+        <v>0.09521931751554169</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3590,22 +3590,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1327402308605085</v>
+        <v>0.1346402308605085</v>
       </c>
       <c r="C27">
-        <v>8.254591363923968</v>
+        <v>8.00137770038617</v>
       </c>
       <c r="D27">
-        <v>4.792091363923969</v>
+        <v>4.702777700386171</v>
       </c>
       <c r="E27">
-        <v>4.0075</v>
+        <v>4.1714</v>
       </c>
       <c r="F27">
-        <v>4.0975</v>
+        <v>4.2614</v>
       </c>
       <c r="G27">
         <v>7.56</v>
@@ -3626,37 +3626,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M27">
-        <v>0.9661905000000001</v>
+        <v>1.00483812</v>
       </c>
       <c r="N27">
-        <v>-0.8741905000000001</v>
+        <v>-0.91283812</v>
       </c>
       <c r="O27">
-        <v>-0.2447733400000001</v>
+        <v>-0.2555946736</v>
       </c>
       <c r="P27">
-        <v>-0.62941716</v>
+        <v>-0.6572434463999999</v>
       </c>
       <c r="Q27">
-        <v>-0.17141716</v>
+        <v>-0.1992434463999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1004825612205601</v>
+        <v>0.1012215147505676</v>
       </c>
       <c r="T27">
-        <v>1.26287670255335</v>
+        <v>1.279942603939207</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.02666140890435169</v>
+        <v>0.02563597010033816</v>
       </c>
       <c r="W27">
-        <v>0.2295132397803539</v>
+        <v>0.2297550382503403</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.09521931751554169</v>
+        <v>0.09155703607263632</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1346402308605085</v>
+        <v>0.1365402308605085</v>
       </c>
       <c r="C28">
-        <v>8.00137770038617</v>
+        <v>7.751432329665569</v>
       </c>
       <c r="D28">
-        <v>4.702777700386171</v>
+        <v>4.616732329665568</v>
       </c>
       <c r="E28">
-        <v>4.1714</v>
+        <v>4.3353</v>
       </c>
       <c r="F28">
-        <v>4.2614</v>
+        <v>4.4253</v>
       </c>
       <c r="G28">
         <v>7.56</v>
@@ -3708,37 +3708,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M28">
-        <v>1.00483812</v>
+        <v>1.04348574</v>
       </c>
       <c r="N28">
-        <v>-0.91283812</v>
+        <v>-0.9514857399999999</v>
       </c>
       <c r="O28">
-        <v>-0.2555946736</v>
+        <v>-0.2664160072</v>
       </c>
       <c r="P28">
-        <v>-0.6572434463999999</v>
+        <v>-0.6850697327999999</v>
       </c>
       <c r="Q28">
-        <v>-0.1992434463999999</v>
+        <v>-0.2270697327999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1012215147505676</v>
+        <v>0.1019807135827672</v>
       </c>
       <c r="T28">
-        <v>1.279942603939207</v>
+        <v>1.297476064267141</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.02563597010033816</v>
+        <v>0.02468648972625156</v>
       </c>
       <c r="W28">
-        <v>0.2297550382503403</v>
+        <v>0.2299789257225499</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.09155703607263632</v>
+        <v>0.08816603473661278</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1365402308605085</v>
+        <v>0.1384402308605085</v>
       </c>
       <c r="C29">
-        <v>7.751432329665569</v>
+        <v>7.504579078120185</v>
       </c>
       <c r="D29">
-        <v>4.616732329665568</v>
+        <v>4.533779078120186</v>
       </c>
       <c r="E29">
-        <v>4.3353</v>
+        <v>4.499200000000001</v>
       </c>
       <c r="F29">
-        <v>4.4253</v>
+        <v>4.589200000000001</v>
       </c>
       <c r="G29">
         <v>7.56</v>
@@ -3790,37 +3790,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M29">
-        <v>1.04348574</v>
+        <v>1.08213336</v>
       </c>
       <c r="N29">
-        <v>-0.9514857399999999</v>
+        <v>-0.9901333600000002</v>
       </c>
       <c r="O29">
-        <v>-0.2664160072</v>
+        <v>-0.2772373408000001</v>
       </c>
       <c r="P29">
-        <v>-0.6850697327999999</v>
+        <v>-0.7128960192000001</v>
       </c>
       <c r="Q29">
-        <v>-0.2270697327999999</v>
+        <v>-0.2548960192000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1019807135827672</v>
+        <v>0.1027610012714167</v>
       </c>
       <c r="T29">
-        <v>1.297476064267141</v>
+        <v>1.31549656515974</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.02468648972625156</v>
+        <v>0.02380482937888543</v>
       </c>
       <c r="W29">
-        <v>0.2299789257225499</v>
+        <v>0.2301868212324588</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.08816603473661278</v>
+        <v>0.0850172477817337</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3836,22 +3836,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1384402308605085</v>
+        <v>0.1403402308605085</v>
       </c>
       <c r="C30">
-        <v>7.504579078120185</v>
+        <v>7.260654210537107</v>
       </c>
       <c r="D30">
-        <v>4.533779078120186</v>
+        <v>4.45375421053711</v>
       </c>
       <c r="E30">
-        <v>4.499200000000001</v>
+        <v>4.663100000000001</v>
       </c>
       <c r="F30">
-        <v>4.589200000000001</v>
+        <v>4.753100000000001</v>
       </c>
       <c r="G30">
         <v>7.56</v>
@@ -3872,37 +3872,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M30">
-        <v>1.08213336</v>
+        <v>1.12078098</v>
       </c>
       <c r="N30">
-        <v>-0.9901333600000002</v>
+        <v>-1.02878098</v>
       </c>
       <c r="O30">
-        <v>-0.2772373408000001</v>
+        <v>-0.2880586744</v>
       </c>
       <c r="P30">
-        <v>-0.7128960192000001</v>
+        <v>-0.7407223056000001</v>
       </c>
       <c r="Q30">
-        <v>-0.2548960192000001</v>
+        <v>-0.2827223056000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1027610012714167</v>
+        <v>0.1035632688949578</v>
       </c>
       <c r="T30">
-        <v>1.31549656515974</v>
+        <v>1.334024685795793</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.02380482937888543</v>
+        <v>0.02298397319340663</v>
       </c>
       <c r="W30">
-        <v>0.2301868212324588</v>
+        <v>0.2303803791209947</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.0850172477817337</v>
+        <v>0.08208561854788088</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3918,22 +3918,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1403402308605085</v>
+        <v>0.1422402308605085</v>
       </c>
       <c r="C31">
-        <v>7.260654210537108</v>
+        <v>7.019505351430793</v>
       </c>
       <c r="D31">
-        <v>4.45375421053711</v>
+        <v>4.376505351430793</v>
       </c>
       <c r="E31">
-        <v>4.6631</v>
+        <v>4.827</v>
       </c>
       <c r="F31">
-        <v>4.7531</v>
+        <v>4.917</v>
       </c>
       <c r="G31">
         <v>7.56</v>
@@ -3954,37 +3954,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M31">
-        <v>1.12078098</v>
+        <v>1.1594286</v>
       </c>
       <c r="N31">
-        <v>-1.02878098</v>
+        <v>-1.0674286</v>
       </c>
       <c r="O31">
-        <v>-0.2880586744</v>
+        <v>-0.298880008</v>
       </c>
       <c r="P31">
-        <v>-0.7407223055999999</v>
+        <v>-0.7685485919999999</v>
       </c>
       <c r="Q31">
-        <v>-0.2827223055999998</v>
+        <v>-0.3105485919999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1035632688949578</v>
+        <v>0.1043884584506001</v>
       </c>
       <c r="T31">
-        <v>1.334024685795793</v>
+        <v>1.353082181307161</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.02298397319340663</v>
+        <v>0.0222178407536264</v>
       </c>
       <c r="W31">
-        <v>0.2303803791209947</v>
+        <v>0.2305610331502949</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.08208561854788088</v>
+        <v>0.07934943126295146</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4000,22 +4000,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1422402308605085</v>
+        <v>0.1441402308605085</v>
       </c>
       <c r="C32">
-        <v>7.019505351430793</v>
+        <v>6.780990516685751</v>
       </c>
       <c r="D32">
-        <v>4.376505351430793</v>
+        <v>4.301890516685751</v>
       </c>
       <c r="E32">
-        <v>4.827</v>
+        <v>4.9909</v>
       </c>
       <c r="F32">
-        <v>4.917</v>
+        <v>5.0809</v>
       </c>
       <c r="G32">
         <v>7.56</v>
@@ -4036,37 +4036,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M32">
-        <v>1.1594286</v>
+        <v>1.19807622</v>
       </c>
       <c r="N32">
-        <v>-1.0674286</v>
+        <v>-1.10607622</v>
       </c>
       <c r="O32">
-        <v>-0.298880008</v>
+        <v>-0.3097013416</v>
       </c>
       <c r="P32">
-        <v>-0.7685485919999999</v>
+        <v>-0.7963748783999999</v>
       </c>
       <c r="Q32">
-        <v>-0.3105485919999999</v>
+        <v>-0.3383748783999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1043884584506001</v>
+        <v>0.105237566544087</v>
       </c>
       <c r="T32">
-        <v>1.353082181307161</v>
+        <v>1.372692067992772</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.0222178407536264</v>
+        <v>0.02150113621318685</v>
       </c>
       <c r="W32">
-        <v>0.2305610331502949</v>
+        <v>0.2307300320809305</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.07934943126295146</v>
+        <v>0.07678977218995309</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1441402308605085</v>
+        <v>0.1460402308605085</v>
       </c>
       <c r="C33">
-        <v>6.780990516685751</v>
+        <v>6.544977242595629</v>
       </c>
       <c r="D33">
-        <v>4.301890516685751</v>
+        <v>4.229777242595631</v>
       </c>
       <c r="E33">
-        <v>4.9909</v>
+        <v>5.154800000000001</v>
       </c>
       <c r="F33">
-        <v>5.0809</v>
+        <v>5.244800000000001</v>
       </c>
       <c r="G33">
         <v>7.56</v>
@@ -4118,37 +4118,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M33">
-        <v>1.19807622</v>
+        <v>1.23672384</v>
       </c>
       <c r="N33">
-        <v>-1.10607622</v>
+        <v>-1.14472384</v>
       </c>
       <c r="O33">
-        <v>-0.3097013416</v>
+        <v>-0.3205226752000001</v>
       </c>
       <c r="P33">
-        <v>-0.7963748783999999</v>
+        <v>-0.8242011648000001</v>
       </c>
       <c r="Q33">
-        <v>-0.3383748783999999</v>
+        <v>-0.3662011648</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.105237566544087</v>
+        <v>0.1061116484050295</v>
       </c>
       <c r="T33">
-        <v>1.372692067992772</v>
+        <v>1.392878716051489</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.02150113621318685</v>
+        <v>0.02082922570652476</v>
       </c>
       <c r="W33">
-        <v>0.2307300320809305</v>
+        <v>0.2308884685784015</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.07678977218995309</v>
+        <v>0.07439009180901701</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1460402308605085</v>
+        <v>0.1479402308605085</v>
       </c>
       <c r="C34">
-        <v>6.544977242595629</v>
+        <v>6.311341801058357</v>
       </c>
       <c r="D34">
-        <v>4.229777242595631</v>
+        <v>4.160041801058359</v>
       </c>
       <c r="E34">
-        <v>5.154800000000001</v>
+        <v>5.318700000000001</v>
       </c>
       <c r="F34">
-        <v>5.244800000000001</v>
+        <v>5.408700000000001</v>
       </c>
       <c r="G34">
         <v>7.56</v>
@@ -4200,37 +4200,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M34">
-        <v>1.23672384</v>
+        <v>1.27537146</v>
       </c>
       <c r="N34">
-        <v>-1.14472384</v>
+        <v>-1.18337146</v>
       </c>
       <c r="O34">
-        <v>-0.3205226752000001</v>
+        <v>-0.3313440088</v>
       </c>
       <c r="P34">
-        <v>-0.8242011648000001</v>
+        <v>-0.8520274512</v>
       </c>
       <c r="Q34">
-        <v>-0.3662011648</v>
+        <v>-0.3940274512</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1061116484050295</v>
+        <v>0.107011822261821</v>
       </c>
       <c r="T34">
-        <v>1.392878716051489</v>
+        <v>1.413667950619422</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.02082922570652476</v>
+        <v>0.02019803704875128</v>
       </c>
       <c r="W34">
-        <v>0.2308884685784015</v>
+        <v>0.2310373028639045</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.07439009180901701</v>
+        <v>0.07213584660268313</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1479402308605085</v>
+        <v>0.1498402308605085</v>
       </c>
       <c r="C35">
-        <v>6.311341801058357</v>
+        <v>6.079968491145604</v>
       </c>
       <c r="D35">
-        <v>4.160041801058359</v>
+        <v>4.092568491145605</v>
       </c>
       <c r="E35">
-        <v>5.318700000000001</v>
+        <v>5.482600000000001</v>
       </c>
       <c r="F35">
-        <v>5.408700000000001</v>
+        <v>5.5726</v>
       </c>
       <c r="G35">
         <v>7.56</v>
@@ -4282,37 +4282,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M35">
-        <v>1.27537146</v>
+        <v>1.31401908</v>
       </c>
       <c r="N35">
-        <v>-1.18337146</v>
+        <v>-1.22201908</v>
       </c>
       <c r="O35">
-        <v>-0.3313440088</v>
+        <v>-0.3421653424000001</v>
       </c>
       <c r="P35">
-        <v>-0.8520274512</v>
+        <v>-0.8798537376000001</v>
       </c>
       <c r="Q35">
-        <v>-0.3940274512</v>
+        <v>-0.4218537376000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.107011822261821</v>
+        <v>0.1079392741142728</v>
       </c>
       <c r="T35">
-        <v>1.413667950619422</v>
+        <v>1.435087161992444</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.02019803704875128</v>
+        <v>0.01960397713555271</v>
       </c>
       <c r="W35">
-        <v>0.2310373028639045</v>
+        <v>0.2311773821914367</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.07213584660268313</v>
+        <v>0.07001420405554537</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4328,22 +4328,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1498402308605085</v>
+        <v>0.1517402308605085</v>
       </c>
       <c r="C36">
-        <v>6.079968491145604</v>
+        <v>5.850748998513725</v>
       </c>
       <c r="D36">
-        <v>4.092568491145605</v>
+        <v>4.027248998513725</v>
       </c>
       <c r="E36">
-        <v>5.482600000000001</v>
+        <v>5.646500000000001</v>
       </c>
       <c r="F36">
-        <v>5.5726</v>
+        <v>5.7365</v>
       </c>
       <c r="G36">
         <v>7.56</v>
@@ -4364,37 +4364,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M36">
-        <v>1.31401908</v>
+        <v>1.3526667</v>
       </c>
       <c r="N36">
-        <v>-1.22201908</v>
+        <v>-1.2606667</v>
       </c>
       <c r="O36">
-        <v>-0.3421653424000001</v>
+        <v>-0.3529866760000001</v>
       </c>
       <c r="P36">
-        <v>-0.8798537376000001</v>
+        <v>-0.907680024</v>
       </c>
       <c r="Q36">
-        <v>-0.4218537376000001</v>
+        <v>-0.449680024</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1079392741142728</v>
+        <v>0.1088952629468001</v>
       </c>
       <c r="T36">
-        <v>1.435087161992444</v>
+        <v>1.457165426023097</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.01960397713555271</v>
+        <v>0.01904386350310835</v>
       </c>
       <c r="W36">
-        <v>0.2311773821914367</v>
+        <v>0.2313094569859671</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.07001420405554537</v>
+        <v>0.068013798225387</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4410,22 +4410,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1517402308605085</v>
+        <v>0.1536402308605085</v>
       </c>
       <c r="C37">
-        <v>5.850748998513725</v>
+        <v>5.623581815195772</v>
       </c>
       <c r="D37">
-        <v>4.027248998513725</v>
+        <v>3.963981815195773</v>
       </c>
       <c r="E37">
-        <v>5.646500000000001</v>
+        <v>5.810400000000001</v>
       </c>
       <c r="F37">
-        <v>5.7365</v>
+        <v>5.900400000000001</v>
       </c>
       <c r="G37">
         <v>7.56</v>
@@ -4446,37 +4446,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M37">
-        <v>1.3526667</v>
+        <v>1.39131432</v>
       </c>
       <c r="N37">
-        <v>-1.2606667</v>
+        <v>-1.29931432</v>
       </c>
       <c r="O37">
-        <v>-0.3529866760000001</v>
+        <v>-0.3638080096000001</v>
       </c>
       <c r="P37">
-        <v>-0.907680024</v>
+        <v>-0.9355063104000002</v>
       </c>
       <c r="Q37">
-        <v>-0.449680024</v>
+        <v>-0.4775063104000002</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1088952629468001</v>
+        <v>0.1098811264303438</v>
       </c>
       <c r="T37">
-        <v>1.457165426023097</v>
+        <v>1.479933635804708</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.01904386350310835</v>
+        <v>0.01851486729468867</v>
       </c>
       <c r="W37">
-        <v>0.2313094569859671</v>
+        <v>0.2314341942919124</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.068013798225387</v>
+        <v>0.06612452605245955</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1536402308605085</v>
+        <v>0.1555402308605085</v>
       </c>
       <c r="C38">
-        <v>5.623581815195773</v>
+        <v>5.398371713237268</v>
       </c>
       <c r="D38">
-        <v>3.963981815195773</v>
+        <v>3.902671713237269</v>
       </c>
       <c r="E38">
-        <v>5.8104</v>
+        <v>5.9743</v>
       </c>
       <c r="F38">
-        <v>5.9004</v>
+        <v>6.0643</v>
       </c>
       <c r="G38">
         <v>7.56</v>
@@ -4528,37 +4528,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M38">
-        <v>1.39131432</v>
+        <v>1.42996194</v>
       </c>
       <c r="N38">
-        <v>-1.29931432</v>
+        <v>-1.33796194</v>
       </c>
       <c r="O38">
-        <v>-0.3638080096000001</v>
+        <v>-0.3746293432</v>
       </c>
       <c r="P38">
-        <v>-0.9355063104000001</v>
+        <v>-0.9633325967999999</v>
       </c>
       <c r="Q38">
-        <v>-0.4775063104000001</v>
+        <v>-0.5053325968</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1098811264303438</v>
+        <v>0.1108982871673334</v>
       </c>
       <c r="T38">
-        <v>1.479933635804708</v>
+        <v>1.503424645896846</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.01851486729468867</v>
+        <v>0.0180144654759133</v>
       </c>
       <c r="W38">
-        <v>0.2314341942919124</v>
+        <v>0.2315521890407796</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.06612452605245955</v>
+        <v>0.06433737669969042</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4574,22 +4574,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1555402308605085</v>
+        <v>0.1574402308605085</v>
       </c>
       <c r="C39">
-        <v>5.398371713237268</v>
+        <v>5.175029266434971</v>
       </c>
       <c r="D39">
-        <v>3.902671713237269</v>
+        <v>3.843229266434972</v>
       </c>
       <c r="E39">
-        <v>5.9743</v>
+        <v>6.1382</v>
       </c>
       <c r="F39">
-        <v>6.0643</v>
+        <v>6.2282</v>
       </c>
       <c r="G39">
         <v>7.56</v>
@@ -4610,37 +4610,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M39">
-        <v>1.42996194</v>
+        <v>1.46860956</v>
       </c>
       <c r="N39">
-        <v>-1.33796194</v>
+        <v>-1.37660956</v>
       </c>
       <c r="O39">
-        <v>-0.3746293432</v>
+        <v>-0.3854506768000001</v>
       </c>
       <c r="P39">
-        <v>-0.9633325967999999</v>
+        <v>-0.9911588832</v>
       </c>
       <c r="Q39">
-        <v>-0.5053325968</v>
+        <v>-0.5331588832</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1108982871673334</v>
+        <v>0.1119482595410001</v>
       </c>
       <c r="T39">
-        <v>1.503424645896846</v>
+        <v>1.527673430508085</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.0180144654759133</v>
+        <v>0.01754040059496821</v>
       </c>
       <c r="W39">
-        <v>0.2315521890407796</v>
+        <v>0.2316639735397065</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.06433737669969042</v>
+        <v>0.0626442878391722</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1574402308605085</v>
+        <v>0.1593402308605085</v>
       </c>
       <c r="C40">
-        <v>5.175029266434971</v>
+        <v>4.953470415126961</v>
       </c>
       <c r="D40">
-        <v>3.843229266434972</v>
+        <v>3.785570415126961</v>
       </c>
       <c r="E40">
-        <v>6.1382</v>
+        <v>6.3021</v>
       </c>
       <c r="F40">
-        <v>6.2282</v>
+        <v>6.3921</v>
       </c>
       <c r="G40">
         <v>7.56</v>
@@ -4692,37 +4692,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M40">
-        <v>1.46860956</v>
+        <v>1.50725718</v>
       </c>
       <c r="N40">
-        <v>-1.37660956</v>
+        <v>-1.41525718</v>
       </c>
       <c r="O40">
-        <v>-0.3854506768000001</v>
+        <v>-0.3962720104</v>
       </c>
       <c r="P40">
-        <v>-0.9911588832</v>
+        <v>-1.0189851696</v>
       </c>
       <c r="Q40">
-        <v>-0.5331588832</v>
+        <v>-0.5609851696000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1119482595410001</v>
+        <v>0.1130326572383935</v>
       </c>
       <c r="T40">
-        <v>1.527673430508085</v>
+        <v>1.552717257237726</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.01754040059496821</v>
+        <v>0.01709064673355877</v>
       </c>
       <c r="W40">
-        <v>0.2316639735397065</v>
+        <v>0.2317700255002269</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.0626442878391722</v>
+        <v>0.06103802404842418</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4738,22 +4738,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1593402308605085</v>
+        <v>0.1612402308605085</v>
       </c>
       <c r="C41">
-        <v>4.953470415126961</v>
+        <v>4.733616069579591</v>
       </c>
       <c r="D41">
-        <v>3.785570415126961</v>
+        <v>3.729616069579593</v>
       </c>
       <c r="E41">
-        <v>6.3021</v>
+        <v>6.466000000000001</v>
       </c>
       <c r="F41">
-        <v>6.3921</v>
+        <v>6.556000000000001</v>
       </c>
       <c r="G41">
         <v>7.56</v>
@@ -4774,37 +4774,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M41">
-        <v>1.50725718</v>
+        <v>1.5459048</v>
       </c>
       <c r="N41">
-        <v>-1.41525718</v>
+        <v>-1.4539048</v>
       </c>
       <c r="O41">
-        <v>-0.3962720104</v>
+        <v>-0.4070933440000001</v>
       </c>
       <c r="P41">
-        <v>-1.0189851696</v>
+        <v>-1.046811456</v>
       </c>
       <c r="Q41">
-        <v>-0.5609851696000001</v>
+        <v>-0.588811456</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1130326572383935</v>
+        <v>0.1141532015257001</v>
       </c>
       <c r="T41">
-        <v>1.552717257237726</v>
+        <v>1.578595878191688</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.01709064673355877</v>
+        <v>0.0166633805652198</v>
       </c>
       <c r="W41">
-        <v>0.2317700255002269</v>
+        <v>0.2318707748627212</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.06103802404842418</v>
+        <v>0.05951207344721365</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1612402308605085</v>
+        <v>0.1631402308605086</v>
       </c>
       <c r="C42">
-        <v>4.733616069579591</v>
+        <v>4.51539174803607</v>
       </c>
       <c r="D42">
-        <v>3.729616069579593</v>
+        <v>3.675291748036071</v>
       </c>
       <c r="E42">
-        <v>6.466000000000001</v>
+        <v>6.629900000000001</v>
       </c>
       <c r="F42">
-        <v>6.556000000000001</v>
+        <v>6.719900000000001</v>
       </c>
       <c r="G42">
         <v>7.56</v>
@@ -4856,37 +4856,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M42">
-        <v>1.5459048</v>
+        <v>1.58455242</v>
       </c>
       <c r="N42">
-        <v>-1.4539048</v>
+        <v>-1.49255242</v>
       </c>
       <c r="O42">
-        <v>-0.4070933440000001</v>
+        <v>-0.4179146776000001</v>
       </c>
       <c r="P42">
-        <v>-1.046811456</v>
+        <v>-1.0746377424</v>
       </c>
       <c r="Q42">
-        <v>-0.588811456</v>
+        <v>-0.6166377424000002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1141532015257001</v>
+        <v>0.1153117303651187</v>
       </c>
       <c r="T42">
-        <v>1.578595878191688</v>
+        <v>1.60535174053392</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.0166633805652198</v>
+        <v>0.01625695664899493</v>
       </c>
       <c r="W42">
-        <v>0.2318707748627212</v>
+        <v>0.231966609622167</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.05951207344721365</v>
+        <v>0.05806055946069621</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4902,22 +4902,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1631402308605086</v>
+        <v>0.1650402308605085</v>
       </c>
       <c r="C43">
-        <v>4.51539174803607</v>
+        <v>4.29872724594324</v>
       </c>
       <c r="D43">
-        <v>3.675291748036071</v>
+        <v>3.622527245943241</v>
       </c>
       <c r="E43">
-        <v>6.629900000000001</v>
+        <v>6.793800000000001</v>
       </c>
       <c r="F43">
-        <v>6.719900000000001</v>
+        <v>6.883800000000001</v>
       </c>
       <c r="G43">
         <v>7.56</v>
@@ -4938,37 +4938,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M43">
-        <v>1.58455242</v>
+        <v>1.62320004</v>
       </c>
       <c r="N43">
-        <v>-1.49255242</v>
+        <v>-1.53120004</v>
       </c>
       <c r="O43">
-        <v>-0.4179146776000001</v>
+        <v>-0.4287360112</v>
       </c>
       <c r="P43">
-        <v>-1.0746377424</v>
+        <v>-1.1024640288</v>
       </c>
       <c r="Q43">
-        <v>-0.6166377424000002</v>
+        <v>-0.6444640288000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1153117303651187</v>
+        <v>0.1165102084748622</v>
       </c>
       <c r="T43">
-        <v>1.60535174053392</v>
+        <v>1.633030218818988</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.01625695664899493</v>
+        <v>0.01586988625259029</v>
       </c>
       <c r="W43">
-        <v>0.231966609622167</v>
+        <v>0.2320578808216392</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.05806055946069621</v>
+        <v>0.05667816518782254</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1650402308605085</v>
+        <v>0.1669402308605085</v>
       </c>
       <c r="C44">
-        <v>4.298727245943241</v>
+        <v>4.083556333267688</v>
       </c>
       <c r="D44">
-        <v>3.622527245943241</v>
+        <v>3.571256333267688</v>
       </c>
       <c r="E44">
-        <v>6.7938</v>
+        <v>6.9577</v>
       </c>
       <c r="F44">
-        <v>6.8838</v>
+        <v>7.0477</v>
       </c>
       <c r="G44">
         <v>7.56</v>
@@ -5020,37 +5020,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M44">
-        <v>1.62320004</v>
+        <v>1.66184766</v>
       </c>
       <c r="N44">
-        <v>-1.53120004</v>
+        <v>-1.56984766</v>
       </c>
       <c r="O44">
-        <v>-0.4287360112</v>
+        <v>-0.4395573448</v>
       </c>
       <c r="P44">
-        <v>-1.1024640288</v>
+        <v>-1.1302903152</v>
       </c>
       <c r="Q44">
-        <v>-0.6444640287999999</v>
+        <v>-0.6722903151999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1165102084748622</v>
+        <v>0.1177507384481054</v>
       </c>
       <c r="T44">
-        <v>1.633030218818988</v>
+        <v>1.661679871780724</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.01586988625259029</v>
+        <v>0.01550081913043703</v>
       </c>
       <c r="W44">
-        <v>0.2320578808216392</v>
+        <v>0.232144906849043</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.05667816518782254</v>
+        <v>0.05536006832298945</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5066,22 +5066,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1669402308605085</v>
+        <v>0.1688402308605085</v>
       </c>
       <c r="C45">
-        <v>4.083556333267688</v>
+        <v>3.869816477157077</v>
       </c>
       <c r="D45">
-        <v>3.571256333267688</v>
+        <v>3.521416477157078</v>
       </c>
       <c r="E45">
-        <v>6.9577</v>
+        <v>7.121600000000001</v>
       </c>
       <c r="F45">
-        <v>7.0477</v>
+        <v>7.211600000000001</v>
       </c>
       <c r="G45">
         <v>7.56</v>
@@ -5102,37 +5102,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M45">
-        <v>1.66184766</v>
+        <v>1.70049528</v>
       </c>
       <c r="N45">
-        <v>-1.56984766</v>
+        <v>-1.60849528</v>
       </c>
       <c r="O45">
-        <v>-0.4395573448</v>
+        <v>-0.4503786784000001</v>
       </c>
       <c r="P45">
-        <v>-1.1302903152</v>
+        <v>-1.1581166016</v>
       </c>
       <c r="Q45">
-        <v>-0.6722903151999999</v>
+        <v>-0.7001166016</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1177507384481054</v>
+        <v>0.1190355730632501</v>
       </c>
       <c r="T45">
-        <v>1.661679871780724</v>
+        <v>1.691352726633951</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.01550081913043703</v>
+        <v>0.01514852778656346</v>
       </c>
       <c r="W45">
-        <v>0.232144906849043</v>
+        <v>0.2322279771479283</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.05536006832298945</v>
+        <v>0.0541018849520124</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5148,22 +5148,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1688402308605085</v>
+        <v>0.1707402308605085</v>
       </c>
       <c r="C46">
-        <v>3.869816477157077</v>
+        <v>3.657448587504808</v>
       </c>
       <c r="D46">
-        <v>3.521416477157078</v>
+        <v>3.472948587504808</v>
       </c>
       <c r="E46">
-        <v>7.121600000000001</v>
+        <v>7.285500000000001</v>
       </c>
       <c r="F46">
-        <v>7.211600000000001</v>
+        <v>7.375500000000001</v>
       </c>
       <c r="G46">
         <v>7.56</v>
@@ -5184,37 +5184,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M46">
-        <v>1.70049528</v>
+        <v>1.7391429</v>
       </c>
       <c r="N46">
-        <v>-1.60849528</v>
+        <v>-1.6471429</v>
       </c>
       <c r="O46">
-        <v>-0.4503786784000001</v>
+        <v>-0.4612000120000001</v>
       </c>
       <c r="P46">
-        <v>-1.1581166016</v>
+        <v>-1.185942888</v>
       </c>
       <c r="Q46">
-        <v>-0.7001166016</v>
+        <v>-0.7279428880000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1190355730632501</v>
+        <v>0.1203671289371274</v>
       </c>
       <c r="T46">
-        <v>1.691352726633951</v>
+        <v>1.722104594390932</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.01514852778656346</v>
+        <v>0.01481189383575094</v>
       </c>
       <c r="W46">
-        <v>0.2322279771479283</v>
+        <v>0.2323073554335299</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.0541018849520124</v>
+        <v>0.05289962084196764</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1707402308605085</v>
+        <v>0.1726402308605085</v>
       </c>
       <c r="C47">
-        <v>3.657448587504808</v>
+        <v>3.446396783241291</v>
       </c>
       <c r="D47">
-        <v>3.472948587504808</v>
+        <v>3.425796783241291</v>
       </c>
       <c r="E47">
-        <v>7.285500000000001</v>
+        <v>7.449400000000001</v>
       </c>
       <c r="F47">
-        <v>7.375500000000001</v>
+        <v>7.539400000000001</v>
       </c>
       <c r="G47">
         <v>7.56</v>
@@ -5266,37 +5266,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M47">
-        <v>1.7391429</v>
+        <v>1.77779052</v>
       </c>
       <c r="N47">
-        <v>-1.6471429</v>
+        <v>-1.68579052</v>
       </c>
       <c r="O47">
-        <v>-0.4612000120000001</v>
+        <v>-0.4720213456000001</v>
       </c>
       <c r="P47">
-        <v>-1.185942888</v>
+        <v>-1.2137691744</v>
       </c>
       <c r="Q47">
-        <v>-0.7279428880000001</v>
+        <v>-0.7557691743999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1203671289371274</v>
+        <v>0.1217480016952223</v>
       </c>
       <c r="T47">
-        <v>1.722104594390932</v>
+        <v>1.753995420212987</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.01481189383575094</v>
+        <v>0.01448989614366939</v>
       </c>
       <c r="W47">
-        <v>0.2323073554335299</v>
+        <v>0.2323832824893228</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.05289962084196764</v>
+        <v>0.05174962908453362</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5312,22 +5312,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1726402308605085</v>
+        <v>0.1745402308605085</v>
       </c>
       <c r="C48">
-        <v>3.446396783241291</v>
+        <v>3.236608177408423</v>
       </c>
       <c r="D48">
-        <v>3.425796783241291</v>
+        <v>3.379908177408423</v>
       </c>
       <c r="E48">
-        <v>7.449400000000001</v>
+        <v>7.613300000000001</v>
       </c>
       <c r="F48">
-        <v>7.539400000000001</v>
+        <v>7.7033</v>
       </c>
       <c r="G48">
         <v>7.56</v>
@@ -5348,37 +5348,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M48">
-        <v>1.77779052</v>
+        <v>1.81643814</v>
       </c>
       <c r="N48">
-        <v>-1.68579052</v>
+        <v>-1.72443814</v>
       </c>
       <c r="O48">
-        <v>-0.4720213456000001</v>
+        <v>-0.4828426792000001</v>
       </c>
       <c r="P48">
-        <v>-1.2137691744</v>
+        <v>-1.2415954608</v>
       </c>
       <c r="Q48">
-        <v>-0.7557691743999999</v>
+        <v>-0.7835954608000002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1217480016952223</v>
+        <v>0.1231809828592831</v>
       </c>
       <c r="T48">
-        <v>1.753995420212987</v>
+        <v>1.787089673424552</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.01448989614366939</v>
+        <v>0.01418160048103813</v>
       </c>
       <c r="W48">
-        <v>0.2323832824893228</v>
+        <v>0.2324559786065712</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.05174962908453362</v>
+        <v>0.05064857314656479</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5394,22 +5394,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1745402308605085</v>
+        <v>0.1764402308605085</v>
       </c>
       <c r="C49">
-        <v>3.236608177408423</v>
+        <v>3.028032679279327</v>
       </c>
       <c r="D49">
-        <v>3.379908177408423</v>
+        <v>3.335232679279329</v>
       </c>
       <c r="E49">
-        <v>7.613300000000001</v>
+        <v>7.777200000000001</v>
       </c>
       <c r="F49">
-        <v>7.7033</v>
+        <v>7.867200000000001</v>
       </c>
       <c r="G49">
         <v>7.56</v>
@@ -5430,37 +5430,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M49">
-        <v>1.81643814</v>
+        <v>1.85508576</v>
       </c>
       <c r="N49">
-        <v>-1.72443814</v>
+        <v>-1.76308576</v>
       </c>
       <c r="O49">
-        <v>-0.4828426792000001</v>
+        <v>-0.4936640128000001</v>
       </c>
       <c r="P49">
-        <v>-1.2415954608</v>
+        <v>-1.2694217472</v>
       </c>
       <c r="Q49">
-        <v>-0.7835954608000002</v>
+        <v>-0.8114217472000003</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1231809828592831</v>
+        <v>0.1246690786835001</v>
       </c>
       <c r="T49">
-        <v>1.787089673424552</v>
+        <v>1.821456782528871</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.01418160048103813</v>
+        <v>0.0138861504710165</v>
       </c>
       <c r="W49">
-        <v>0.2324559786065712</v>
+        <v>0.2325256457189343</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.05064857314656479</v>
+        <v>0.04959339453934464</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5476,22 +5476,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1764402308605085</v>
+        <v>0.1783402308605085</v>
       </c>
       <c r="C50">
-        <v>3.028032679279328</v>
+        <v>2.820622811966814</v>
       </c>
       <c r="D50">
-        <v>3.335232679279329</v>
+        <v>3.291722811966815</v>
       </c>
       <c r="E50">
-        <v>7.777200000000001</v>
+        <v>7.9411</v>
       </c>
       <c r="F50">
-        <v>7.8672</v>
+        <v>8.0311</v>
       </c>
       <c r="G50">
         <v>7.56</v>
@@ -5512,37 +5512,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M50">
-        <v>1.85508576</v>
+        <v>1.89373338</v>
       </c>
       <c r="N50">
-        <v>-1.76308576</v>
+        <v>-1.80173338</v>
       </c>
       <c r="O50">
-        <v>-0.4936640128000001</v>
+        <v>-0.5044853464000001</v>
       </c>
       <c r="P50">
-        <v>-1.2694217472</v>
+        <v>-1.2972480336</v>
       </c>
       <c r="Q50">
-        <v>-0.8114217472</v>
+        <v>-0.8392480336000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1246690786835001</v>
+        <v>0.126215531206706</v>
       </c>
       <c r="T50">
-        <v>1.821456782528871</v>
+        <v>1.857171621401986</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0138861504710165</v>
+        <v>0.01360275964507739</v>
       </c>
       <c r="W50">
-        <v>0.2325256457189343</v>
+        <v>0.2325924692756908</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.04959339453934464</v>
+        <v>0.04858128444670495</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5558,22 +5558,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1783402308605085</v>
+        <v>0.1802402308605085</v>
       </c>
       <c r="C51">
-        <v>2.820622811966814</v>
+        <v>2.61433354412434</v>
       </c>
       <c r="D51">
-        <v>3.291722811966815</v>
+        <v>3.249333544124342</v>
       </c>
       <c r="E51">
-        <v>7.9411</v>
+        <v>8.105</v>
       </c>
       <c r="F51">
-        <v>8.0311</v>
+        <v>8.195</v>
       </c>
       <c r="G51">
         <v>7.56</v>
@@ -5594,37 +5594,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M51">
-        <v>1.89373338</v>
+        <v>1.932381</v>
       </c>
       <c r="N51">
-        <v>-1.80173338</v>
+        <v>-1.840381</v>
       </c>
       <c r="O51">
-        <v>-0.5044853464000001</v>
+        <v>-0.51530668</v>
       </c>
       <c r="P51">
-        <v>-1.2972480336</v>
+        <v>-1.32507432</v>
       </c>
       <c r="Q51">
-        <v>-0.8392480336000001</v>
+        <v>-0.8670743200000002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.126215531206706</v>
+        <v>0.1278238418308401</v>
       </c>
       <c r="T51">
-        <v>1.857171621401986</v>
+        <v>1.894315053830026</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.01360275964507739</v>
+        <v>0.01333070445217584</v>
       </c>
       <c r="W51">
-        <v>0.2325924692756908</v>
+        <v>0.2326566198901769</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.04858128444670495</v>
+        <v>0.0476096587577709</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1802402308605085</v>
+        <v>0.1821402308605085</v>
       </c>
       <c r="C52">
-        <v>2.61433354412434</v>
+        <v>2.409122134485314</v>
       </c>
       <c r="D52">
-        <v>3.249333544124342</v>
+        <v>3.208022134485315</v>
       </c>
       <c r="E52">
-        <v>8.105</v>
+        <v>8.2689</v>
       </c>
       <c r="F52">
-        <v>8.195</v>
+        <v>8.3589</v>
       </c>
       <c r="G52">
         <v>7.56</v>
@@ -5676,37 +5676,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M52">
-        <v>1.932381</v>
+        <v>1.97102862</v>
       </c>
       <c r="N52">
-        <v>-1.840381</v>
+        <v>-1.87902862</v>
       </c>
       <c r="O52">
-        <v>-0.51530668</v>
+        <v>-0.5261280136000001</v>
       </c>
       <c r="P52">
-        <v>-1.32507432</v>
+        <v>-1.3529006064</v>
       </c>
       <c r="Q52">
-        <v>-0.8670743200000002</v>
+        <v>-0.8949006064</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1278238418308401</v>
+        <v>0.1294977977865715</v>
       </c>
       <c r="T52">
-        <v>1.894315053830026</v>
+        <v>1.932974544724516</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.01333070445217584</v>
+        <v>0.01306931809036847</v>
       </c>
       <c r="W52">
-        <v>0.2326566198901769</v>
+        <v>0.2327182547942911</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.0476096587577709</v>
+        <v>0.04667613603703025</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1821402308605085</v>
+        <v>0.1840402308605085</v>
       </c>
       <c r="C53">
-        <v>2.409122134485314</v>
+        <v>2.204947988112515</v>
       </c>
       <c r="D53">
-        <v>3.208022134485315</v>
+        <v>3.167747988112515</v>
       </c>
       <c r="E53">
-        <v>8.2689</v>
+        <v>8.4328</v>
       </c>
       <c r="F53">
-        <v>8.3589</v>
+        <v>8.5228</v>
       </c>
       <c r="G53">
         <v>7.56</v>
@@ -5758,37 +5758,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M53">
-        <v>1.97102862</v>
+        <v>2.00967624</v>
       </c>
       <c r="N53">
-        <v>-1.87902862</v>
+        <v>-1.91767624</v>
       </c>
       <c r="O53">
-        <v>-0.5261280136000001</v>
+        <v>-0.5369493472000001</v>
       </c>
       <c r="P53">
-        <v>-1.3529006064</v>
+        <v>-1.3807268928</v>
       </c>
       <c r="Q53">
-        <v>-0.8949006064</v>
+        <v>-0.9227268927999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1294977977865715</v>
+        <v>0.1312415019071251</v>
       </c>
       <c r="T53">
-        <v>1.932974544724516</v>
+        <v>1.97324484773961</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.01306931809036847</v>
+        <v>0.01281798505016908</v>
       </c>
       <c r="W53">
-        <v>0.2327182547942911</v>
+        <v>0.2327775191251701</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.04667613603703025</v>
+        <v>0.04577851803631816</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5804,22 +5804,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1840402308605085</v>
+        <v>0.1859402308605085</v>
       </c>
       <c r="C54">
-        <v>2.204947988112515</v>
+        <v>2.001772523341275</v>
       </c>
       <c r="D54">
-        <v>3.167747988112515</v>
+        <v>3.128472523341276</v>
       </c>
       <c r="E54">
-        <v>8.4328</v>
+        <v>8.5967</v>
       </c>
       <c r="F54">
-        <v>8.5228</v>
+        <v>8.6867</v>
       </c>
       <c r="G54">
         <v>7.56</v>
@@ -5840,37 +5840,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M54">
-        <v>2.00967624</v>
+        <v>2.04832386</v>
       </c>
       <c r="N54">
-        <v>-1.91767624</v>
+        <v>-1.95632386</v>
       </c>
       <c r="O54">
-        <v>-0.5369493472000001</v>
+        <v>-0.5477706808</v>
       </c>
       <c r="P54">
-        <v>-1.3807268928</v>
+        <v>-1.4085531792</v>
       </c>
       <c r="Q54">
-        <v>-0.9227268927999999</v>
+        <v>-0.9505531791999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1312415019071251</v>
+        <v>0.1330594062030214</v>
       </c>
       <c r="T54">
-        <v>1.97324484773961</v>
+        <v>2.01522878067024</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.01281798505016908</v>
+        <v>0.01257613627563759</v>
       </c>
       <c r="W54">
-        <v>0.2327775191251701</v>
+        <v>0.2328345470662047</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.04577851803631816</v>
+        <v>0.04491477241299147</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5886,22 +5886,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1859402308605085</v>
+        <v>0.1878402308605085</v>
       </c>
       <c r="C55">
-        <v>2.001772523341275</v>
+        <v>1.79955904849974</v>
       </c>
       <c r="D55">
-        <v>3.128472523341276</v>
+        <v>3.09015904849974</v>
       </c>
       <c r="E55">
-        <v>8.5967</v>
+        <v>8.7606</v>
       </c>
       <c r="F55">
-        <v>8.6867</v>
+        <v>8.8506</v>
       </c>
       <c r="G55">
         <v>7.56</v>
@@ -5922,37 +5922,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M55">
-        <v>2.04832386</v>
+        <v>2.08697148</v>
       </c>
       <c r="N55">
-        <v>-1.95632386</v>
+        <v>-1.99497148</v>
       </c>
       <c r="O55">
-        <v>-0.5477706808</v>
+        <v>-0.5585920143999999</v>
       </c>
       <c r="P55">
-        <v>-1.4085531792</v>
+        <v>-1.4363794656</v>
       </c>
       <c r="Q55">
-        <v>-0.9505531791999999</v>
+        <v>-0.9783794656</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1330594062030214</v>
+        <v>0.1349563498161305</v>
       </c>
       <c r="T55">
-        <v>2.01522878067024</v>
+        <v>2.059038101989158</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.01257613627563759</v>
+        <v>0.01234324486312578</v>
       </c>
       <c r="W55">
-        <v>0.2328345470662047</v>
+        <v>0.232889462861275</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.04491477241299147</v>
+        <v>0.04408301736830644</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5968,22 +5968,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1878402308605085</v>
+        <v>0.1897402308605085</v>
       </c>
       <c r="C56">
-        <v>1.79955904849974</v>
+        <v>1.598272647578115</v>
       </c>
       <c r="D56">
-        <v>3.09015904849974</v>
+        <v>3.052772647578118</v>
       </c>
       <c r="E56">
-        <v>8.7606</v>
+        <v>8.924500000000002</v>
       </c>
       <c r="F56">
-        <v>8.8506</v>
+        <v>9.014500000000002</v>
       </c>
       <c r="G56">
         <v>7.56</v>
@@ -6004,37 +6004,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M56">
-        <v>2.08697148</v>
+        <v>2.125619100000001</v>
       </c>
       <c r="N56">
-        <v>-1.99497148</v>
+        <v>-2.033619100000001</v>
       </c>
       <c r="O56">
-        <v>-0.5585920143999999</v>
+        <v>-0.5694133480000002</v>
       </c>
       <c r="P56">
-        <v>-1.4363794656</v>
+        <v>-1.464205752</v>
       </c>
       <c r="Q56">
-        <v>-0.9783794656</v>
+        <v>-1.006205752</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1349563498161305</v>
+        <v>0.1369376020342668</v>
       </c>
       <c r="T56">
-        <v>2.059038101989158</v>
+        <v>2.104794504255584</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.01234324486312578</v>
+        <v>0.01211882222925076</v>
       </c>
       <c r="W56">
-        <v>0.232889462861275</v>
+        <v>0.2329423817183427</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.04408301736830644</v>
+        <v>0.0432815079616099</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6050,22 +6050,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1897402308605085</v>
+        <v>0.1916402308605085</v>
       </c>
       <c r="C57">
-        <v>1.598272647578115</v>
+        <v>1.397880074098158</v>
       </c>
       <c r="D57">
-        <v>3.052772647578118</v>
+        <v>3.01628007409816</v>
       </c>
       <c r="E57">
-        <v>8.924500000000002</v>
+        <v>9.088400000000002</v>
       </c>
       <c r="F57">
-        <v>9.014500000000002</v>
+        <v>9.178400000000002</v>
       </c>
       <c r="G57">
         <v>7.56</v>
@@ -6086,37 +6086,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M57">
-        <v>2.125619100000001</v>
+        <v>2.164266720000001</v>
       </c>
       <c r="N57">
-        <v>-2.033619100000001</v>
+        <v>-2.07226672</v>
       </c>
       <c r="O57">
-        <v>-0.5694133480000002</v>
+        <v>-0.5802346816000001</v>
       </c>
       <c r="P57">
-        <v>-1.464205752</v>
+        <v>-1.4920320384</v>
       </c>
       <c r="Q57">
-        <v>-1.006205752</v>
+        <v>-1.0340320384</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1369376020342668</v>
+        <v>0.1390089111714092</v>
       </c>
       <c r="T57">
-        <v>2.104794504255584</v>
+        <v>2.152630742988666</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.01211882222925076</v>
+        <v>0.01190241468944271</v>
       </c>
       <c r="W57">
-        <v>0.2329423817183427</v>
+        <v>0.2329934106162294</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.0432815079616099</v>
+        <v>0.04250862389086685</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6132,22 +6132,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1916402308605085</v>
+        <v>0.1935402308605085</v>
       </c>
       <c r="C58">
-        <v>1.397880074098158</v>
+        <v>1.198349652504747</v>
       </c>
       <c r="D58">
-        <v>3.01628007409816</v>
+        <v>2.980649652504749</v>
       </c>
       <c r="E58">
-        <v>9.088400000000002</v>
+        <v>9.252300000000002</v>
       </c>
       <c r="F58">
-        <v>9.178400000000002</v>
+        <v>9.342300000000002</v>
       </c>
       <c r="G58">
         <v>7.56</v>
@@ -6168,37 +6168,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M58">
-        <v>2.164266720000001</v>
+        <v>2.20291434</v>
       </c>
       <c r="N58">
-        <v>-2.07226672</v>
+        <v>-2.11091434</v>
       </c>
       <c r="O58">
-        <v>-0.5802346816000001</v>
+        <v>-0.5910560152000002</v>
       </c>
       <c r="P58">
-        <v>-1.4920320384</v>
+        <v>-1.5198583248</v>
       </c>
       <c r="Q58">
-        <v>-1.0340320384</v>
+        <v>-1.0618583248</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1390089111714092</v>
+        <v>0.1411765602684187</v>
       </c>
       <c r="T58">
-        <v>2.152630742988666</v>
+        <v>2.20269192305817</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.01190241468944271</v>
+        <v>0.01169360039664548</v>
       </c>
       <c r="W58">
-        <v>0.2329934106162294</v>
+        <v>0.233042649026471</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.04250862389086685</v>
+        <v>0.04176285855944817</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6214,22 +6214,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1935402308605085</v>
+        <v>0.1954402308605085</v>
       </c>
       <c r="C59">
-        <v>1.198349652504747</v>
+        <v>0.9996511864648934</v>
       </c>
       <c r="D59">
-        <v>2.980649652504749</v>
+        <v>2.945851186464895</v>
       </c>
       <c r="E59">
-        <v>9.252300000000002</v>
+        <v>9.416200000000002</v>
       </c>
       <c r="F59">
-        <v>9.342300000000002</v>
+        <v>9.506200000000002</v>
       </c>
       <c r="G59">
         <v>7.56</v>
@@ -6250,37 +6250,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M59">
-        <v>2.20291434</v>
+        <v>2.24156196</v>
       </c>
       <c r="N59">
-        <v>-2.11091434</v>
+        <v>-2.14956196</v>
       </c>
       <c r="O59">
-        <v>-0.5910560152000002</v>
+        <v>-0.6018773488000001</v>
       </c>
       <c r="P59">
-        <v>-1.5198583248</v>
+        <v>-1.5476846112</v>
       </c>
       <c r="Q59">
-        <v>-1.0618583248</v>
+        <v>-1.0896846112</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1411765602684187</v>
+        <v>0.1434474307510001</v>
       </c>
       <c r="T59">
-        <v>2.20269192305817</v>
+        <v>2.255136968845269</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01169360039664548</v>
+        <v>0.01149198659670331</v>
       </c>
       <c r="W59">
-        <v>0.233042649026471</v>
+        <v>0.2330901895604973</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.04176285855944817</v>
+        <v>0.04104280927394044</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6296,22 +6296,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1954402308605085</v>
+        <v>0.1973402308605085</v>
       </c>
       <c r="C60">
-        <v>0.9996511864648951</v>
+        <v>0.8017558735161412</v>
       </c>
       <c r="D60">
-        <v>2.945851186464896</v>
+        <v>2.91185587351614</v>
       </c>
       <c r="E60">
-        <v>9.4162</v>
+        <v>9.5801</v>
       </c>
       <c r="F60">
-        <v>9.5062</v>
+        <v>9.6701</v>
       </c>
       <c r="G60">
         <v>7.56</v>
@@ -6332,37 +6332,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M60">
-        <v>2.24156196</v>
+        <v>2.28020958</v>
       </c>
       <c r="N60">
-        <v>-2.14956196</v>
+        <v>-2.18820958</v>
       </c>
       <c r="O60">
-        <v>-0.6018773488</v>
+        <v>-0.6126986824000001</v>
       </c>
       <c r="P60">
-        <v>-1.5476846112</v>
+        <v>-1.5755108976</v>
       </c>
       <c r="Q60">
-        <v>-1.0896846112</v>
+        <v>-1.1175108976</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1434474307510001</v>
+        <v>0.1458290754034635</v>
       </c>
       <c r="T60">
-        <v>2.255136968845269</v>
+        <v>2.310140309548811</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.01149198659670331</v>
+        <v>0.01129720716286088</v>
       </c>
       <c r="W60">
-        <v>0.2330901895604973</v>
+        <v>0.2331361185509974</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.04104280927394044</v>
+        <v>0.04034716843878894</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6378,22 +6378,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1973402308605085</v>
+        <v>0.1992402308605085</v>
       </c>
       <c r="C61">
-        <v>0.8017558735161412</v>
+        <v>0.6046362255573161</v>
       </c>
       <c r="D61">
-        <v>2.91185587351614</v>
+        <v>2.878636225557316</v>
       </c>
       <c r="E61">
-        <v>9.5801</v>
+        <v>9.744</v>
       </c>
       <c r="F61">
-        <v>9.6701</v>
+        <v>9.834</v>
       </c>
       <c r="G61">
         <v>7.56</v>
@@ -6414,37 +6414,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M61">
-        <v>2.28020958</v>
+        <v>2.3188572</v>
       </c>
       <c r="N61">
-        <v>-2.18820958</v>
+        <v>-2.2268572</v>
       </c>
       <c r="O61">
-        <v>-0.6126986824000001</v>
+        <v>-0.6235200160000001</v>
       </c>
       <c r="P61">
-        <v>-1.5755108976</v>
+        <v>-1.603337184</v>
       </c>
       <c r="Q61">
-        <v>-1.1175108976</v>
+        <v>-1.145337184</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1458290754034635</v>
+        <v>0.1483298022885501</v>
       </c>
       <c r="T61">
-        <v>2.310140309548811</v>
+        <v>2.367893817287532</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.01129720716286088</v>
+        <v>0.0111089203768132</v>
       </c>
       <c r="W61">
-        <v>0.2331361185509974</v>
+        <v>0.2331805165751475</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.04034716843878894</v>
+        <v>0.03967471563147573</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6460,22 +6460,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1992402308605085</v>
+        <v>0.2011402308605085</v>
       </c>
       <c r="C62">
-        <v>0.6046362255573161</v>
+        <v>0.4082659947203702</v>
       </c>
       <c r="D62">
-        <v>2.878636225557316</v>
+        <v>2.84616599472037</v>
       </c>
       <c r="E62">
-        <v>9.744</v>
+        <v>9.9079</v>
       </c>
       <c r="F62">
-        <v>9.834</v>
+        <v>9.9979</v>
       </c>
       <c r="G62">
         <v>7.56</v>
@@ -6496,37 +6496,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M62">
-        <v>2.3188572</v>
+        <v>2.35750482</v>
       </c>
       <c r="N62">
-        <v>-2.2268572</v>
+        <v>-2.26550482</v>
       </c>
       <c r="O62">
-        <v>-0.6235200160000001</v>
+        <v>-0.6343413496</v>
       </c>
       <c r="P62">
-        <v>-1.603337184</v>
+        <v>-1.6311634704</v>
       </c>
       <c r="Q62">
-        <v>-1.145337184</v>
+        <v>-1.1731634704</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1483298022885501</v>
+        <v>0.1509587715780001</v>
       </c>
       <c r="T62">
-        <v>2.367893817287532</v>
+        <v>2.428609043371828</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0111089203768132</v>
+        <v>0.01092680692801299</v>
       </c>
       <c r="W62">
-        <v>0.2331805165751475</v>
+        <v>0.2332234589263746</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.03967471563147573</v>
+        <v>0.03902431045718924</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2011402308605085</v>
+        <v>0.2030402308605085</v>
       </c>
       <c r="C63">
-        <v>0.4082659947203702</v>
+        <v>0.21262010420309</v>
       </c>
       <c r="D63">
-        <v>2.84616599472037</v>
+        <v>2.814420104203091</v>
       </c>
       <c r="E63">
-        <v>9.9079</v>
+        <v>10.0718</v>
       </c>
       <c r="F63">
-        <v>9.9979</v>
+        <v>10.1618</v>
       </c>
       <c r="G63">
         <v>7.56</v>
@@ -6578,37 +6578,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M63">
-        <v>2.35750482</v>
+        <v>2.39615244</v>
       </c>
       <c r="N63">
-        <v>-2.26550482</v>
+        <v>-2.30415244</v>
       </c>
       <c r="O63">
-        <v>-0.6343413496</v>
+        <v>-0.6451626832</v>
       </c>
       <c r="P63">
-        <v>-1.6311634704</v>
+        <v>-1.6589897568</v>
       </c>
       <c r="Q63">
-        <v>-1.1731634704</v>
+        <v>-1.2009897568</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1509587715780001</v>
+        <v>0.153726107672158</v>
       </c>
       <c r="T63">
-        <v>2.428609043371828</v>
+        <v>2.492519807671087</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01092680692801299</v>
+        <v>0.01075056810659342</v>
       </c>
       <c r="W63">
-        <v>0.2332234589263746</v>
+        <v>0.2332650160404653</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.03902431045718924</v>
+        <v>0.03839488609497654</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2030402308605085</v>
+        <v>0.2049402308605086</v>
       </c>
       <c r="C64">
-        <v>0.21262010420309</v>
+        <v>0.0176745836796961</v>
       </c>
       <c r="D64">
-        <v>2.814420104203091</v>
+        <v>2.783374583679699</v>
       </c>
       <c r="E64">
-        <v>10.0718</v>
+        <v>10.2357</v>
       </c>
       <c r="F64">
-        <v>10.1618</v>
+        <v>10.3257</v>
       </c>
       <c r="G64">
         <v>7.56</v>
@@ -6660,37 +6660,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M64">
-        <v>2.39615244</v>
+        <v>2.434800060000001</v>
       </c>
       <c r="N64">
-        <v>-2.30415244</v>
+        <v>-2.342800060000001</v>
       </c>
       <c r="O64">
-        <v>-0.6451626832</v>
+        <v>-0.6559840168000002</v>
       </c>
       <c r="P64">
-        <v>-1.6589897568</v>
+        <v>-1.6868160432</v>
       </c>
       <c r="Q64">
-        <v>-1.2009897568</v>
+        <v>-1.2288160432</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.153726107672158</v>
+        <v>0.1566430295011353</v>
       </c>
       <c r="T64">
-        <v>2.492519807671087</v>
+        <v>2.559885207878414</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01075056810659342</v>
+        <v>0.01057992416839352</v>
       </c>
       <c r="W64">
-        <v>0.2332650160404653</v>
+        <v>0.2333052538810928</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.03839488609497654</v>
+        <v>0.03778544345854828</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6706,22 +6706,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2049402308605086</v>
+        <v>0.2068402308605085</v>
       </c>
       <c r="C65">
-        <v>0.0176745836796961</v>
+        <v>-0.1765934910603466</v>
       </c>
       <c r="D65">
-        <v>2.783374583679699</v>
+        <v>2.753006508939655</v>
       </c>
       <c r="E65">
-        <v>10.2357</v>
+        <v>10.3996</v>
       </c>
       <c r="F65">
-        <v>10.3257</v>
+        <v>10.4896</v>
       </c>
       <c r="G65">
         <v>7.56</v>
@@ -6742,37 +6742,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M65">
-        <v>2.434800060000001</v>
+        <v>2.47344768</v>
       </c>
       <c r="N65">
-        <v>-2.342800060000001</v>
+        <v>-2.38144768</v>
       </c>
       <c r="O65">
-        <v>-0.6559840168000002</v>
+        <v>-0.6668053504000002</v>
       </c>
       <c r="P65">
-        <v>-1.6868160432</v>
+        <v>-1.7146423296</v>
       </c>
       <c r="Q65">
-        <v>-1.2288160432</v>
+        <v>-1.2566423296</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1566430295011353</v>
+        <v>0.1597220025428335</v>
       </c>
       <c r="T65">
-        <v>2.559885207878414</v>
+        <v>2.63099313031948</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01057992416839352</v>
+        <v>0.01041461285326238</v>
       </c>
       <c r="W65">
-        <v>0.2333052538810928</v>
+        <v>0.2333442342892007</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.03778544345854828</v>
+        <v>0.03719504590450851</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6788,22 +6788,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2068402308605085</v>
+        <v>0.2087402308605085</v>
       </c>
       <c r="C66">
-        <v>-0.1765934910603466</v>
+        <v>-0.3702060545647345</v>
       </c>
       <c r="D66">
-        <v>2.753006508939655</v>
+        <v>2.723293945435266</v>
       </c>
       <c r="E66">
-        <v>10.3996</v>
+        <v>10.5635</v>
       </c>
       <c r="F66">
-        <v>10.4896</v>
+        <v>10.6535</v>
       </c>
       <c r="G66">
         <v>7.56</v>
@@ -6824,37 +6824,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M66">
-        <v>2.47344768</v>
+        <v>2.5120953</v>
       </c>
       <c r="N66">
-        <v>-2.38144768</v>
+        <v>-2.4200953</v>
       </c>
       <c r="O66">
-        <v>-0.6668053504000002</v>
+        <v>-0.6776266840000001</v>
       </c>
       <c r="P66">
-        <v>-1.7146423296</v>
+        <v>-1.742468616</v>
       </c>
       <c r="Q66">
-        <v>-1.2566423296</v>
+        <v>-1.284468616</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1597220025428335</v>
+        <v>0.1629769169012001</v>
       </c>
       <c r="T66">
-        <v>2.63099313031948</v>
+        <v>2.706164362614323</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01041461285326238</v>
+        <v>0.01025438804013526</v>
       </c>
       <c r="W66">
-        <v>0.2333442342892007</v>
+        <v>0.2333820153001361</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.03719504590450851</v>
+        <v>0.03662281442905457</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6870,22 +6870,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2087402308605085</v>
+        <v>0.2106402308605085</v>
       </c>
       <c r="C67">
-        <v>-0.3702060545647345</v>
+        <v>-0.5631841045540913</v>
       </c>
       <c r="D67">
-        <v>2.723293945435266</v>
+        <v>2.694215895445911</v>
       </c>
       <c r="E67">
-        <v>10.5635</v>
+        <v>10.7274</v>
       </c>
       <c r="F67">
-        <v>10.6535</v>
+        <v>10.8174</v>
       </c>
       <c r="G67">
         <v>7.56</v>
@@ -6906,37 +6906,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M67">
-        <v>2.5120953</v>
+        <v>2.55074292</v>
       </c>
       <c r="N67">
-        <v>-2.4200953</v>
+        <v>-2.45874292</v>
       </c>
       <c r="O67">
-        <v>-0.6776266840000001</v>
+        <v>-0.6884480176000001</v>
       </c>
       <c r="P67">
-        <v>-1.742468616</v>
+        <v>-1.7702949024</v>
       </c>
       <c r="Q67">
-        <v>-1.284468616</v>
+        <v>-1.3122949024</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1629769169012001</v>
+        <v>0.166423296810059</v>
       </c>
       <c r="T67">
-        <v>2.706164362614323</v>
+        <v>2.785757432102979</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01025438804013526</v>
+        <v>0.01009901852437564</v>
       </c>
       <c r="W67">
-        <v>0.2333820153001361</v>
+        <v>0.2334186514319522</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.03662281442905457</v>
+        <v>0.03606792330134156</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6952,22 +6952,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2106402308605085</v>
+        <v>0.2125402308605085</v>
       </c>
       <c r="C68">
-        <v>-0.5631841045540913</v>
+        <v>-0.7555477514085585</v>
       </c>
       <c r="D68">
-        <v>2.694215895445911</v>
+        <v>2.665752248591442</v>
       </c>
       <c r="E68">
-        <v>10.7274</v>
+        <v>10.8913</v>
       </c>
       <c r="F68">
-        <v>10.8174</v>
+        <v>10.9813</v>
       </c>
       <c r="G68">
         <v>7.56</v>
@@ -6988,37 +6988,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M68">
-        <v>2.55074292</v>
+        <v>2.58939054</v>
       </c>
       <c r="N68">
-        <v>-2.45874292</v>
+        <v>-2.49739054</v>
       </c>
       <c r="O68">
-        <v>-0.6884480176000001</v>
+        <v>-0.6992693512000001</v>
       </c>
       <c r="P68">
-        <v>-1.7702949024</v>
+        <v>-1.7981211888</v>
       </c>
       <c r="Q68">
-        <v>-1.3122949024</v>
+        <v>-1.3401211888</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.166423296810059</v>
+        <v>0.1700785482285456</v>
       </c>
       <c r="T68">
-        <v>2.785757432102979</v>
+        <v>2.870174323984888</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01009901852437564</v>
+        <v>0.009948286904608838</v>
       </c>
       <c r="W68">
-        <v>0.2334186514319522</v>
+        <v>0.2334541939478932</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.03606792330134156</v>
+        <v>0.03552959608788875</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7034,22 +7034,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2125402308605085</v>
+        <v>0.2144402308605085</v>
       </c>
       <c r="C69">
-        <v>-0.7555477514085585</v>
+        <v>-0.9473162645503219</v>
       </c>
       <c r="D69">
-        <v>2.665752248591442</v>
+        <v>2.637883735449678</v>
       </c>
       <c r="E69">
-        <v>10.8913</v>
+        <v>11.0552</v>
       </c>
       <c r="F69">
-        <v>10.9813</v>
+        <v>11.1452</v>
       </c>
       <c r="G69">
         <v>7.56</v>
@@ -7070,37 +7070,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M69">
-        <v>2.58939054</v>
+        <v>2.62803816</v>
       </c>
       <c r="N69">
-        <v>-2.49739054</v>
+        <v>-2.53603816</v>
       </c>
       <c r="O69">
-        <v>-0.6992693512000001</v>
+        <v>-0.7100906848000001</v>
       </c>
       <c r="P69">
-        <v>-1.7981211888</v>
+        <v>-1.8259474752</v>
       </c>
       <c r="Q69">
-        <v>-1.3401211888</v>
+        <v>-1.3679474752</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1700785482285456</v>
+        <v>0.1739622528606877</v>
       </c>
       <c r="T69">
-        <v>2.870174323984888</v>
+        <v>2.959867271609416</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.009948286904608838</v>
+        <v>0.009801988567776355</v>
       </c>
       <c r="W69">
-        <v>0.2334541939478932</v>
+        <v>0.2334886910957183</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.03552959608788875</v>
+        <v>0.03500710202777269</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7116,22 +7116,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2144402308605085</v>
+        <v>0.2163402308605085</v>
       </c>
       <c r="C70">
-        <v>-0.9473162645503219</v>
+        <v>-1.138508115946852</v>
       </c>
       <c r="D70">
-        <v>2.637883735449678</v>
+        <v>2.61059188405315</v>
       </c>
       <c r="E70">
-        <v>11.0552</v>
+        <v>11.2191</v>
       </c>
       <c r="F70">
-        <v>11.1452</v>
+        <v>11.3091</v>
       </c>
       <c r="G70">
         <v>7.56</v>
@@ -7152,37 +7152,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M70">
-        <v>2.62803816</v>
+        <v>2.66668578</v>
       </c>
       <c r="N70">
-        <v>-2.53603816</v>
+        <v>-2.57468578</v>
       </c>
       <c r="O70">
-        <v>-0.7100906848000001</v>
+        <v>-0.7209120184000002</v>
       </c>
       <c r="P70">
-        <v>-1.8259474752</v>
+        <v>-1.8537737616</v>
       </c>
       <c r="Q70">
-        <v>-1.3679474752</v>
+        <v>-1.3957737616</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1739622528606877</v>
+        <v>0.1780965190820002</v>
       </c>
       <c r="T70">
-        <v>2.959867271609416</v>
+        <v>3.055346861016171</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.009801988567776355</v>
+        <v>0.009659930762446263</v>
       </c>
       <c r="W70">
-        <v>0.2334886910957183</v>
+        <v>0.2335221883262152</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.03500710202777269</v>
+        <v>0.03449975272302241</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7198,22 +7198,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2163402308605085</v>
+        <v>0.2182402308605085</v>
       </c>
       <c r="C71">
-        <v>-1.138508115946852</v>
+        <v>-1.329141020941254</v>
       </c>
       <c r="D71">
-        <v>2.61059188405315</v>
+        <v>2.583858979058747</v>
       </c>
       <c r="E71">
-        <v>11.2191</v>
+        <v>11.383</v>
       </c>
       <c r="F71">
-        <v>11.3091</v>
+        <v>11.473</v>
       </c>
       <c r="G71">
         <v>7.56</v>
@@ -7234,37 +7234,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M71">
-        <v>2.66668578</v>
+        <v>2.7053334</v>
       </c>
       <c r="N71">
-        <v>-2.57468578</v>
+        <v>-2.6133334</v>
       </c>
       <c r="O71">
-        <v>-0.7209120184000002</v>
+        <v>-0.7317333520000001</v>
       </c>
       <c r="P71">
-        <v>-1.8537737616</v>
+        <v>-1.881600048</v>
       </c>
       <c r="Q71">
-        <v>-1.3957737616</v>
+        <v>-1.423600048</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1780965190820002</v>
+        <v>0.1825064030514002</v>
       </c>
       <c r="T71">
-        <v>3.055346861016171</v>
+        <v>3.157191756383377</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.009659930762446263</v>
+        <v>0.009521931751554174</v>
       </c>
       <c r="W71">
-        <v>0.2335221883262152</v>
+        <v>0.2335547284929835</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.03449975272302241</v>
+        <v>0.0340068991126935</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7280,22 +7280,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2182402308605085</v>
+        <v>0.2201402308605085</v>
       </c>
       <c r="C72">
-        <v>-1.329141020941254</v>
+        <v>-1.519231976599416</v>
       </c>
       <c r="D72">
-        <v>2.583858979058747</v>
+        <v>2.557668023400587</v>
       </c>
       <c r="E72">
-        <v>11.383</v>
+        <v>11.5469</v>
       </c>
       <c r="F72">
-        <v>11.473</v>
+        <v>11.6369</v>
       </c>
       <c r="G72">
         <v>7.56</v>
@@ -7316,37 +7316,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M72">
-        <v>2.7053334</v>
+        <v>2.743981020000001</v>
       </c>
       <c r="N72">
-        <v>-2.6133334</v>
+        <v>-2.65198102</v>
       </c>
       <c r="O72">
-        <v>-0.7317333520000001</v>
+        <v>-0.7425546856000002</v>
       </c>
       <c r="P72">
-        <v>-1.881600048</v>
+        <v>-1.9094263344</v>
       </c>
       <c r="Q72">
-        <v>-1.423600048</v>
+        <v>-1.4514263344</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1825064030514002</v>
+        <v>0.1872204169497244</v>
       </c>
       <c r="T72">
-        <v>3.157191756383377</v>
+        <v>3.266060437637976</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.009521931751554174</v>
+        <v>0.009387820036743551</v>
       </c>
       <c r="W72">
-        <v>0.2335547284929835</v>
+        <v>0.2335863520353359</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.0340068991126935</v>
+        <v>0.03352792870265553</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7362,22 +7362,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2201402308605085</v>
+        <v>0.2220402308605085</v>
       </c>
       <c r="C73">
-        <v>-1.519231976599414</v>
+        <v>-1.708797297748317</v>
       </c>
       <c r="D73">
-        <v>2.557668023400587</v>
+        <v>2.532002702251684</v>
       </c>
       <c r="E73">
-        <v>11.5469</v>
+        <v>11.7108</v>
       </c>
       <c r="F73">
-        <v>11.6369</v>
+        <v>11.8008</v>
       </c>
       <c r="G73">
         <v>7.56</v>
@@ -7398,37 +7398,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M73">
-        <v>2.74398102</v>
+        <v>2.78262864</v>
       </c>
       <c r="N73">
-        <v>-2.65198102</v>
+        <v>-2.69062864</v>
       </c>
       <c r="O73">
-        <v>-0.7425546856</v>
+        <v>-0.7533760192000002</v>
       </c>
       <c r="P73">
-        <v>-1.9094263344</v>
+        <v>-1.9372526208</v>
       </c>
       <c r="Q73">
-        <v>-1.4514263344</v>
+        <v>-1.4792526208</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1872204169497243</v>
+        <v>0.1922711461265002</v>
       </c>
       <c r="T73">
-        <v>3.266060437637975</v>
+        <v>3.382705453267903</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.009387820036743551</v>
+        <v>0.009257433647344335</v>
       </c>
       <c r="W73">
-        <v>0.2335863520353359</v>
+        <v>0.2336170971459562</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.03352792870265553</v>
+        <v>0.03306226302622983</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7444,22 +7444,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2220402308605085</v>
+        <v>0.2239402308605085</v>
       </c>
       <c r="C74">
-        <v>-1.708797297748317</v>
+        <v>-1.897852650866135</v>
       </c>
       <c r="D74">
-        <v>2.532002702251684</v>
+        <v>2.506847349133867</v>
       </c>
       <c r="E74">
-        <v>11.7108</v>
+        <v>11.8747</v>
       </c>
       <c r="F74">
-        <v>11.8008</v>
+        <v>11.9647</v>
       </c>
       <c r="G74">
         <v>7.56</v>
@@ -7480,37 +7480,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M74">
-        <v>2.78262864</v>
+        <v>2.82127626</v>
       </c>
       <c r="N74">
-        <v>-2.69062864</v>
+        <v>-2.72927626</v>
       </c>
       <c r="O74">
-        <v>-0.7533760192000002</v>
+        <v>-0.7641973528000001</v>
       </c>
       <c r="P74">
-        <v>-1.9372526208</v>
+        <v>-1.9650789072</v>
       </c>
       <c r="Q74">
-        <v>-1.4792526208</v>
+        <v>-1.5070789072</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1922711461265002</v>
+        <v>0.1976960033904446</v>
       </c>
       <c r="T74">
-        <v>3.382705453267903</v>
+        <v>3.507990840425973</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.009257433647344335</v>
+        <v>0.009130619487791673</v>
       </c>
       <c r="W74">
-        <v>0.2336170971459562</v>
+        <v>0.2336469999247787</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.03306226302622983</v>
+        <v>0.0326093553135417</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7526,22 +7526,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2239402308605085</v>
+        <v>0.2258402308605085</v>
       </c>
       <c r="C75">
-        <v>-1.897852650866135</v>
+        <v>-2.086413085972017</v>
       </c>
       <c r="D75">
-        <v>2.506847349133867</v>
+        <v>2.482186914027983</v>
       </c>
       <c r="E75">
-        <v>11.8747</v>
+        <v>12.0386</v>
       </c>
       <c r="F75">
-        <v>11.9647</v>
+        <v>12.1286</v>
       </c>
       <c r="G75">
         <v>7.56</v>
@@ -7562,37 +7562,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M75">
-        <v>2.82127626</v>
+        <v>2.85992388</v>
       </c>
       <c r="N75">
-        <v>-2.72927626</v>
+        <v>-2.76792388</v>
       </c>
       <c r="O75">
-        <v>-0.7641973528000001</v>
+        <v>-0.7750186864000002</v>
       </c>
       <c r="P75">
-        <v>-1.9650789072</v>
+        <v>-1.9929051936</v>
       </c>
       <c r="Q75">
-        <v>-1.5070789072</v>
+        <v>-1.5349051936</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1976960033904446</v>
+        <v>0.2035381573670002</v>
       </c>
       <c r="T75">
-        <v>3.507990840425973</v>
+        <v>3.642913565057742</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.009130619487791673</v>
+        <v>0.009007232737956651</v>
       </c>
       <c r="W75">
-        <v>0.2336469999247787</v>
+        <v>0.2336760945203898</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.0326093553135417</v>
+        <v>0.03216868834984521</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7608,22 +7608,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2258402308605085</v>
+        <v>0.2277402308605085</v>
       </c>
       <c r="C76">
-        <v>-2.086413085972017</v>
+        <v>-2.274493066651969</v>
       </c>
       <c r="D76">
-        <v>2.482186914027983</v>
+        <v>2.458006933348032</v>
       </c>
       <c r="E76">
-        <v>12.0386</v>
+        <v>12.2025</v>
       </c>
       <c r="F76">
-        <v>12.1286</v>
+        <v>12.2925</v>
       </c>
       <c r="G76">
         <v>7.56</v>
@@ -7644,37 +7644,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M76">
-        <v>2.85992388</v>
+        <v>2.8985715</v>
       </c>
       <c r="N76">
-        <v>-2.76792388</v>
+        <v>-2.8065715</v>
       </c>
       <c r="O76">
-        <v>-0.7750186864000002</v>
+        <v>-0.7858400200000001</v>
       </c>
       <c r="P76">
-        <v>-1.9929051936</v>
+        <v>-2.02073148</v>
       </c>
       <c r="Q76">
-        <v>-1.5349051936</v>
+        <v>-1.56273148</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2035381573670002</v>
+        <v>0.2098476836616802</v>
       </c>
       <c r="T76">
-        <v>3.642913565057742</v>
+        <v>3.788630107660051</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.009007232737956651</v>
+        <v>0.008887136301450563</v>
       </c>
       <c r="W76">
-        <v>0.2336760945203898</v>
+        <v>0.233704413260118</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.03216868834984521</v>
+        <v>0.03173977250518056</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7690,22 +7690,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2277402308605085</v>
+        <v>0.2296402308605085</v>
       </c>
       <c r="C77">
-        <v>-2.274493066651969</v>
+        <v>-2.46210649834668</v>
       </c>
       <c r="D77">
-        <v>2.458006933348032</v>
+        <v>2.43429350165332</v>
       </c>
       <c r="E77">
-        <v>12.2025</v>
+        <v>12.3664</v>
       </c>
       <c r="F77">
-        <v>12.2925</v>
+        <v>12.4564</v>
       </c>
       <c r="G77">
         <v>7.56</v>
@@ -7726,37 +7726,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M77">
-        <v>2.8985715</v>
+        <v>2.93721912</v>
       </c>
       <c r="N77">
-        <v>-2.8065715</v>
+        <v>-2.84521912</v>
       </c>
       <c r="O77">
-        <v>-0.7858400200000001</v>
+        <v>-0.7966613536000001</v>
       </c>
       <c r="P77">
-        <v>-2.02073148</v>
+        <v>-2.0485577664</v>
       </c>
       <c r="Q77">
-        <v>-1.56273148</v>
+        <v>-1.5905577664</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2098476836616802</v>
+        <v>0.2166830038142502</v>
       </c>
       <c r="T77">
-        <v>3.788630107660051</v>
+        <v>3.94648969547922</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.008887136301450563</v>
+        <v>0.008770200297484106</v>
       </c>
       <c r="W77">
-        <v>0.233704413260118</v>
+        <v>0.2337319867698533</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.03173977250518056</v>
+        <v>0.0313221439195861</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7772,22 +7772,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2296402308605085</v>
+        <v>0.2315402308605085</v>
       </c>
       <c r="C78">
-        <v>-2.46210649834668</v>
+        <v>-2.649266755017596</v>
       </c>
       <c r="D78">
-        <v>2.43429350165332</v>
+        <v>2.411033244982405</v>
       </c>
       <c r="E78">
-        <v>12.3664</v>
+        <v>12.5303</v>
       </c>
       <c r="F78">
-        <v>12.4564</v>
+        <v>12.6203</v>
       </c>
       <c r="G78">
         <v>7.56</v>
@@ -7808,37 +7808,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M78">
-        <v>2.93721912</v>
+        <v>2.97586674</v>
       </c>
       <c r="N78">
-        <v>-2.84521912</v>
+        <v>-2.88386674</v>
       </c>
       <c r="O78">
-        <v>-0.7966613536000001</v>
+        <v>-0.8074826872000002</v>
       </c>
       <c r="P78">
-        <v>-2.0485577664</v>
+        <v>-2.0763840528</v>
       </c>
       <c r="Q78">
-        <v>-1.5905577664</v>
+        <v>-1.6183840528</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2166830038142502</v>
+        <v>0.2241126996322611</v>
       </c>
       <c r="T78">
-        <v>3.94648969547922</v>
+        <v>4.118076203978316</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.008770200297484106</v>
+        <v>0.008656301592321976</v>
       </c>
       <c r="W78">
-        <v>0.2337319867698533</v>
+        <v>0.2337588440845305</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.0313221439195861</v>
+        <v>0.0309153628297214</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7854,22 +7854,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2315402308605085</v>
+        <v>0.2334402308605085</v>
       </c>
       <c r="C79">
-        <v>-2.649266755017596</v>
+        <v>-2.835986704298643</v>
       </c>
       <c r="D79">
-        <v>2.411033244982405</v>
+        <v>2.388213295701358</v>
       </c>
       <c r="E79">
-        <v>12.5303</v>
+        <v>12.6942</v>
       </c>
       <c r="F79">
-        <v>12.6203</v>
+        <v>12.7842</v>
       </c>
       <c r="G79">
         <v>7.56</v>
@@ -7890,37 +7890,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M79">
-        <v>2.97586674</v>
+        <v>3.01451436</v>
       </c>
       <c r="N79">
-        <v>-2.88386674</v>
+        <v>-2.92251436</v>
       </c>
       <c r="O79">
-        <v>-0.8074826872000002</v>
+        <v>-0.8183040208000001</v>
       </c>
       <c r="P79">
-        <v>-2.0763840528</v>
+        <v>-2.1042103392</v>
       </c>
       <c r="Q79">
-        <v>-1.6183840528</v>
+        <v>-1.6462103392</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2241126996322611</v>
+        <v>0.2322178223428184</v>
       </c>
       <c r="T79">
-        <v>4.118076203978316</v>
+        <v>4.305261485977332</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.008656301592321976</v>
+        <v>0.008545323366779387</v>
       </c>
       <c r="W79">
-        <v>0.2337588440845305</v>
+        <v>0.2337850127501134</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.0309153628297214</v>
+        <v>0.03051901202421214</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7936,22 +7936,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2334402308605085</v>
+        <v>0.2353402308605085</v>
       </c>
       <c r="C80">
-        <v>-2.835986704298643</v>
+        <v>-3.022278731233001</v>
       </c>
       <c r="D80">
-        <v>2.388213295701358</v>
+        <v>2.365821268767</v>
       </c>
       <c r="E80">
-        <v>12.6942</v>
+        <v>12.8581</v>
       </c>
       <c r="F80">
-        <v>12.7842</v>
+        <v>12.9481</v>
       </c>
       <c r="G80">
         <v>7.56</v>
@@ -7972,37 +7972,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M80">
-        <v>3.01451436</v>
+        <v>3.05316198</v>
       </c>
       <c r="N80">
-        <v>-2.92251436</v>
+        <v>-2.96116198</v>
       </c>
       <c r="O80">
-        <v>-0.8183040208000001</v>
+        <v>-0.8291253544000001</v>
       </c>
       <c r="P80">
-        <v>-2.1042103392</v>
+        <v>-2.1320366256</v>
       </c>
       <c r="Q80">
-        <v>-1.6462103392</v>
+        <v>-1.6740366256</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2322178223428184</v>
+        <v>0.2410948615020003</v>
       </c>
       <c r="T80">
-        <v>4.305261485977332</v>
+        <v>4.510273937690538</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.008545323366779387</v>
+        <v>0.00843715471656699</v>
       </c>
       <c r="W80">
-        <v>0.2337850127501134</v>
+        <v>0.2338105189178335</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.03051901202421214</v>
+        <v>0.0301326954163107</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2353402308605085</v>
+        <v>0.2372402308605085</v>
       </c>
       <c r="C81">
-        <v>-3.022278731233001</v>
+        <v>-3.208154760686963</v>
       </c>
       <c r="D81">
-        <v>2.365821268767</v>
+        <v>2.34384523931304</v>
       </c>
       <c r="E81">
-        <v>12.8581</v>
+        <v>13.022</v>
       </c>
       <c r="F81">
-        <v>12.9481</v>
+        <v>13.112</v>
       </c>
       <c r="G81">
         <v>7.56</v>
@@ -8054,37 +8054,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M81">
-        <v>3.05316198</v>
+        <v>3.0918096</v>
       </c>
       <c r="N81">
-        <v>-2.96116198</v>
+        <v>-2.9998096</v>
       </c>
       <c r="O81">
-        <v>-0.8291253544000001</v>
+        <v>-0.8399466880000002</v>
       </c>
       <c r="P81">
-        <v>-2.1320366256</v>
+        <v>-2.159862912</v>
       </c>
       <c r="Q81">
-        <v>-1.6740366256</v>
+        <v>-1.701862912</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2410948615020003</v>
+        <v>0.2508596045771003</v>
       </c>
       <c r="T81">
-        <v>4.510273937690538</v>
+        <v>4.735787634575065</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.00843715471656699</v>
+        <v>0.008331690282609902</v>
       </c>
       <c r="W81">
-        <v>0.2338105189178335</v>
+        <v>0.2338353874313606</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.0301326954163107</v>
+        <v>0.02975603672360683</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8100,22 +8100,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2372402308605085</v>
+        <v>0.2391402308605085</v>
       </c>
       <c r="C82">
-        <v>-3.208154760686963</v>
+        <v>-3.393626278526034</v>
       </c>
       <c r="D82">
-        <v>2.34384523931304</v>
+        <v>2.322273721473968</v>
       </c>
       <c r="E82">
-        <v>13.022</v>
+        <v>13.1859</v>
       </c>
       <c r="F82">
-        <v>13.112</v>
+        <v>13.2759</v>
       </c>
       <c r="G82">
         <v>7.56</v>
@@ -8136,37 +8136,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M82">
-        <v>3.0918096</v>
+        <v>3.130457220000001</v>
       </c>
       <c r="N82">
-        <v>-2.9998096</v>
+        <v>-3.038457220000001</v>
       </c>
       <c r="O82">
-        <v>-0.8399466880000002</v>
+        <v>-0.8507680216000002</v>
       </c>
       <c r="P82">
-        <v>-2.159862912</v>
+        <v>-2.1876891984</v>
       </c>
       <c r="Q82">
-        <v>-1.701862912</v>
+        <v>-1.7296891984</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2508596045771003</v>
+        <v>0.2616522153443161</v>
       </c>
       <c r="T82">
-        <v>4.735787634575065</v>
+        <v>4.985039615342174</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.008331690282609902</v>
+        <v>0.008228829908750519</v>
       </c>
       <c r="W82">
-        <v>0.2338353874313606</v>
+        <v>0.2338596419075167</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.02975603672360683</v>
+        <v>0.02938867824553759</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8182,22 +8182,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2391402308605085</v>
+        <v>0.2410402308605085</v>
       </c>
       <c r="C83">
-        <v>-3.393626278526034</v>
+        <v>-3.5787043516324</v>
       </c>
       <c r="D83">
-        <v>2.322273721473968</v>
+        <v>2.301095648367603</v>
       </c>
       <c r="E83">
-        <v>13.1859</v>
+        <v>13.3498</v>
       </c>
       <c r="F83">
-        <v>13.2759</v>
+        <v>13.4398</v>
       </c>
       <c r="G83">
         <v>7.56</v>
@@ -8218,37 +8218,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M83">
-        <v>3.130457220000001</v>
+        <v>3.169104840000001</v>
       </c>
       <c r="N83">
-        <v>-3.038457220000001</v>
+        <v>-3.077104840000001</v>
       </c>
       <c r="O83">
-        <v>-0.8507680216000002</v>
+        <v>-0.8615893552000002</v>
       </c>
       <c r="P83">
-        <v>-2.1876891984</v>
+        <v>-2.2155154848</v>
       </c>
       <c r="Q83">
-        <v>-1.7296891984</v>
+        <v>-1.7575154848</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2616522153443161</v>
+        <v>0.273644005085667</v>
       </c>
       <c r="T83">
-        <v>4.985039615342174</v>
+        <v>5.261986260638961</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.008228829908750519</v>
+        <v>0.008128478324497463</v>
       </c>
       <c r="W83">
-        <v>0.2338596419075167</v>
+        <v>0.2338833048110835</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.02938867824553759</v>
+        <v>0.02903027973034811</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2410402308605085</v>
+        <v>0.2429402308605086</v>
       </c>
       <c r="C84">
-        <v>-3.5787043516324</v>
+        <v>-3.763399646836922</v>
       </c>
       <c r="D84">
-        <v>2.301095648367603</v>
+        <v>2.280300353163081</v>
       </c>
       <c r="E84">
-        <v>13.3498</v>
+        <v>13.5137</v>
       </c>
       <c r="F84">
-        <v>13.4398</v>
+        <v>13.6037</v>
       </c>
       <c r="G84">
         <v>7.56</v>
@@ -8300,37 +8300,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M84">
-        <v>3.169104840000001</v>
+        <v>3.20775246</v>
       </c>
       <c r="N84">
-        <v>-3.077104840000001</v>
+        <v>-3.11575246</v>
       </c>
       <c r="O84">
-        <v>-0.8615893552000002</v>
+        <v>-0.8724106888000002</v>
       </c>
       <c r="P84">
-        <v>-2.2155154848</v>
+        <v>-2.2433417712</v>
       </c>
       <c r="Q84">
-        <v>-1.7575154848</v>
+        <v>-1.7853417712</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.273644005085667</v>
+        <v>0.287046593620118</v>
       </c>
       <c r="T84">
-        <v>5.261986260638961</v>
+        <v>5.571514864205961</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.008128478324497463</v>
+        <v>0.008030544850708338</v>
       </c>
       <c r="W84">
-        <v>0.2338833048110835</v>
+        <v>0.233906397524203</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.02903027973034811</v>
+        <v>0.02868051732395838</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2429402308605086</v>
+        <v>0.2448402308605085</v>
       </c>
       <c r="C85">
-        <v>-3.763399646836922</v>
+        <v>-3.947722448833835</v>
       </c>
       <c r="D85">
-        <v>2.280300353163081</v>
+        <v>2.259877551166167</v>
       </c>
       <c r="E85">
-        <v>13.5137</v>
+        <v>13.6776</v>
       </c>
       <c r="F85">
-        <v>13.6037</v>
+        <v>13.7676</v>
       </c>
       <c r="G85">
         <v>7.56</v>
@@ -8382,37 +8382,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M85">
-        <v>3.20775246</v>
+        <v>3.24640008</v>
       </c>
       <c r="N85">
-        <v>-3.11575246</v>
+        <v>-3.15440008</v>
       </c>
       <c r="O85">
-        <v>-0.8724106888000002</v>
+        <v>-0.8832320224000002</v>
       </c>
       <c r="P85">
-        <v>-2.2433417712</v>
+        <v>-2.2711680576</v>
       </c>
       <c r="Q85">
-        <v>-1.7853417712</v>
+        <v>-1.8131680576</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.287046593620118</v>
+        <v>0.3021245057213754</v>
       </c>
       <c r="T85">
-        <v>5.571514864205961</v>
+        <v>5.919734543218834</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.008030544850708338</v>
+        <v>0.007934943126295144</v>
       </c>
       <c r="W85">
-        <v>0.233906397524203</v>
+        <v>0.2339289404108196</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.02868051732395838</v>
+        <v>0.02833908259391127</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8428,22 +8428,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2448402308605085</v>
+        <v>0.2467402308605085</v>
       </c>
       <c r="C86">
-        <v>-3.947722448833833</v>
+        <v>-4.13168267714128</v>
       </c>
       <c r="D86">
-        <v>2.259877551166167</v>
+        <v>2.239817322858721</v>
       </c>
       <c r="E86">
-        <v>13.6776</v>
+        <v>13.8415</v>
       </c>
       <c r="F86">
-        <v>13.7676</v>
+        <v>13.9315</v>
       </c>
       <c r="G86">
         <v>7.56</v>
@@ -8464,37 +8464,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M86">
-        <v>3.24640008</v>
+        <v>3.2850477</v>
       </c>
       <c r="N86">
-        <v>-3.15440008</v>
+        <v>-3.1930477</v>
       </c>
       <c r="O86">
-        <v>-0.8832320224</v>
+        <v>-0.8940533560000001</v>
       </c>
       <c r="P86">
-        <v>-2.2711680576</v>
+        <v>-2.298994344</v>
       </c>
       <c r="Q86">
-        <v>-1.8131680576</v>
+        <v>-1.840994344</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3021245057213753</v>
+        <v>0.3192128061028003</v>
       </c>
       <c r="T86">
-        <v>5.919734543218829</v>
+        <v>6.314383512766752</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.007934943126295146</v>
+        <v>0.007841590854221085</v>
       </c>
       <c r="W86">
-        <v>0.2339289404108196</v>
+        <v>0.2339509528765747</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.02833908259391127</v>
+        <v>0.02800568162221817</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8510,22 +8510,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2467402308605085</v>
+        <v>0.2486402308605085</v>
       </c>
       <c r="C87">
-        <v>-4.13168267714128</v>
+        <v>-4.315289902166471</v>
       </c>
       <c r="D87">
-        <v>2.239817322858721</v>
+        <v>2.220110097833529</v>
       </c>
       <c r="E87">
-        <v>13.8415</v>
+        <v>14.0054</v>
       </c>
       <c r="F87">
-        <v>13.9315</v>
+        <v>14.0954</v>
       </c>
       <c r="G87">
         <v>7.56</v>
@@ -8546,37 +8546,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M87">
-        <v>3.2850477</v>
+        <v>3.32369532</v>
       </c>
       <c r="N87">
-        <v>-3.1930477</v>
+        <v>-3.23169532</v>
       </c>
       <c r="O87">
-        <v>-0.8940533560000001</v>
+        <v>-0.9048746896000001</v>
       </c>
       <c r="P87">
-        <v>-2.298994344</v>
+        <v>-2.3268206304</v>
       </c>
       <c r="Q87">
-        <v>-1.840994344</v>
+        <v>-1.8688206304</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3192128061028003</v>
+        <v>0.3387422922530003</v>
       </c>
       <c r="T87">
-        <v>6.314383512766752</v>
+        <v>6.765410906535805</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.007841590854221085</v>
+        <v>0.007750409565218513</v>
       </c>
       <c r="W87">
-        <v>0.2339509528765747</v>
+        <v>0.2339724534245215</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.02800568162221817</v>
+        <v>0.02768003416149467</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2486402308605085</v>
+        <v>0.2505402308605085</v>
       </c>
       <c r="C88">
-        <v>-4.315289902166471</v>
+        <v>-4.498553360430147</v>
       </c>
       <c r="D88">
-        <v>2.220110097833529</v>
+        <v>2.200746639569853</v>
       </c>
       <c r="E88">
-        <v>14.0054</v>
+        <v>14.1693</v>
       </c>
       <c r="F88">
-        <v>14.0954</v>
+        <v>14.2593</v>
       </c>
       <c r="G88">
         <v>7.56</v>
@@ -8628,37 +8628,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M88">
-        <v>3.32369532</v>
+        <v>3.36234294</v>
       </c>
       <c r="N88">
-        <v>-3.23169532</v>
+        <v>-3.27034294</v>
       </c>
       <c r="O88">
-        <v>-0.9048746896000001</v>
+        <v>-0.9156960232000001</v>
       </c>
       <c r="P88">
-        <v>-2.3268206304</v>
+        <v>-2.3546469168</v>
       </c>
       <c r="Q88">
-        <v>-1.8688206304</v>
+        <v>-1.8966469168</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3387422922530003</v>
+        <v>0.3612763147340003</v>
       </c>
       <c r="T88">
-        <v>6.765410906535805</v>
+        <v>7.285827130115483</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.007750409565218513</v>
+        <v>0.007661324397802209</v>
       </c>
       <c r="W88">
-        <v>0.2339724534245215</v>
+        <v>0.2339934597069983</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.02768003416149467</v>
+        <v>0.02736187284929359</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8674,22 +8674,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2505402308605085</v>
+        <v>0.2524402308605085</v>
       </c>
       <c r="C89">
-        <v>-4.498553360430147</v>
+        <v>-4.681481969001219</v>
       </c>
       <c r="D89">
-        <v>2.200746639569853</v>
+        <v>2.181718030998783</v>
       </c>
       <c r="E89">
-        <v>14.1693</v>
+        <v>14.3332</v>
       </c>
       <c r="F89">
-        <v>14.2593</v>
+        <v>14.4232</v>
       </c>
       <c r="G89">
         <v>7.56</v>
@@ -8710,37 +8710,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M89">
-        <v>3.36234294</v>
+        <v>3.40099056</v>
       </c>
       <c r="N89">
-        <v>-3.27034294</v>
+        <v>-3.30899056</v>
       </c>
       <c r="O89">
-        <v>-0.9156960232000001</v>
+        <v>-0.9265173568000001</v>
       </c>
       <c r="P89">
-        <v>-2.3546469168</v>
+        <v>-2.3824732032</v>
       </c>
       <c r="Q89">
-        <v>-1.8966469168</v>
+        <v>-1.9244732032</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3612763147340003</v>
+        <v>0.3875660076285004</v>
       </c>
       <c r="T89">
-        <v>7.285827130115483</v>
+        <v>7.892979390958439</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.007661324397802209</v>
+        <v>0.007574263893281729</v>
       </c>
       <c r="W89">
-        <v>0.2339934597069983</v>
+        <v>0.2340139885739642</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.02736187284929359</v>
+        <v>0.02705094247600615</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2524402308605085</v>
+        <v>0.2543402308605085</v>
       </c>
       <c r="C90">
-        <v>-4.681481969001219</v>
+        <v>-4.864084339188963</v>
       </c>
       <c r="D90">
-        <v>2.181718030998783</v>
+        <v>2.163015660811038</v>
       </c>
       <c r="E90">
-        <v>14.3332</v>
+        <v>14.4971</v>
       </c>
       <c r="F90">
-        <v>14.4232</v>
+        <v>14.5871</v>
       </c>
       <c r="G90">
         <v>7.56</v>
@@ -8792,37 +8792,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M90">
-        <v>3.40099056</v>
+        <v>3.439638180000001</v>
       </c>
       <c r="N90">
-        <v>-3.30899056</v>
+        <v>-3.347638180000001</v>
       </c>
       <c r="O90">
-        <v>-0.9265173568000001</v>
+        <v>-0.9373386904000003</v>
       </c>
       <c r="P90">
-        <v>-2.3824732032</v>
+        <v>-2.4102994896</v>
       </c>
       <c r="Q90">
-        <v>-1.9244732032</v>
+        <v>-1.9522994896</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3875660076285004</v>
+        <v>0.4186356446856368</v>
       </c>
       <c r="T90">
-        <v>7.892979390958439</v>
+        <v>8.610522971954662</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.007574263893281729</v>
+        <v>0.007489159804593169</v>
       </c>
       <c r="W90">
-        <v>0.2340139885739642</v>
+        <v>0.2340340561180769</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.02705094247600615</v>
+        <v>0.02674699930211843</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8838,22 +8838,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2543402308605085</v>
+        <v>0.2562402308605085</v>
       </c>
       <c r="C91">
-        <v>-4.864084339188963</v>
+        <v>-5.046368789536981</v>
       </c>
       <c r="D91">
-        <v>2.163015660811038</v>
+        <v>2.144631210463021</v>
       </c>
       <c r="E91">
-        <v>14.4971</v>
+        <v>14.661</v>
       </c>
       <c r="F91">
-        <v>14.5871</v>
+        <v>14.751</v>
       </c>
       <c r="G91">
         <v>7.56</v>
@@ -8874,37 +8874,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M91">
-        <v>3.439638180000001</v>
+        <v>3.478285800000001</v>
       </c>
       <c r="N91">
-        <v>-3.347638180000001</v>
+        <v>-3.3862858</v>
       </c>
       <c r="O91">
-        <v>-0.9373386904000003</v>
+        <v>-0.9481600240000002</v>
       </c>
       <c r="P91">
-        <v>-2.4102994896</v>
+        <v>-2.438125776</v>
       </c>
       <c r="Q91">
-        <v>-1.9522994896</v>
+        <v>-1.980125776</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4186356446856368</v>
+        <v>0.4559192091542006</v>
       </c>
       <c r="T91">
-        <v>8.610522971954662</v>
+        <v>9.471575269150131</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.007489159804593169</v>
+        <v>0.007405946917875468</v>
       </c>
       <c r="W91">
-        <v>0.2340340561180769</v>
+        <v>0.234053677716765</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.02674699930211843</v>
+        <v>0.02644981042098382</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2562402308605085</v>
+        <v>0.2581402308605085</v>
       </c>
       <c r="C92">
-        <v>-5.046368789536981</v>
+        <v>-5.228343358160073</v>
       </c>
       <c r="D92">
-        <v>2.144631210463021</v>
+        <v>2.12655664183993</v>
       </c>
       <c r="E92">
-        <v>14.661</v>
+        <v>14.8249</v>
       </c>
       <c r="F92">
-        <v>14.751</v>
+        <v>14.9149</v>
       </c>
       <c r="G92">
         <v>7.56</v>
@@ -8956,37 +8956,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M92">
-        <v>3.478285800000001</v>
+        <v>3.51693342</v>
       </c>
       <c r="N92">
-        <v>-3.3862858</v>
+        <v>-3.42493342</v>
       </c>
       <c r="O92">
-        <v>-0.9481600240000002</v>
+        <v>-0.9589813576000001</v>
       </c>
       <c r="P92">
-        <v>-2.438125776</v>
+        <v>-2.4659520624</v>
       </c>
       <c r="Q92">
-        <v>-1.980125776</v>
+        <v>-2.0079520624</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4559192091542006</v>
+        <v>0.5014880101713339</v>
       </c>
       <c r="T92">
-        <v>9.471575269150131</v>
+        <v>10.52397252127792</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.007405946917875468</v>
+        <v>0.007324562885810902</v>
       </c>
       <c r="W92">
-        <v>0.234053677716765</v>
+        <v>0.2340728680715258</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.02644981042098382</v>
+        <v>0.02615915316361039</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9002,22 +9002,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2581402308605085</v>
+        <v>0.2600402308605085</v>
       </c>
       <c r="C93">
-        <v>-5.228343358160073</v>
+        <v>-5.410015814462504</v>
       </c>
       <c r="D93">
-        <v>2.12655664183993</v>
+        <v>2.108784185537496</v>
       </c>
       <c r="E93">
-        <v>14.8249</v>
+        <v>14.9888</v>
       </c>
       <c r="F93">
-        <v>14.9149</v>
+        <v>15.0788</v>
       </c>
       <c r="G93">
         <v>7.56</v>
@@ -9038,37 +9038,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M93">
-        <v>3.51693342</v>
+        <v>3.55558104</v>
       </c>
       <c r="N93">
-        <v>-3.42493342</v>
+        <v>-3.46358104</v>
       </c>
       <c r="O93">
-        <v>-0.9589813576000001</v>
+        <v>-0.9698026912000002</v>
       </c>
       <c r="P93">
-        <v>-2.4659520624</v>
+        <v>-2.4937783488</v>
       </c>
       <c r="Q93">
-        <v>-2.0079520624</v>
+        <v>-2.0357783488</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5014880101713339</v>
+        <v>0.5584490114427508</v>
       </c>
       <c r="T93">
-        <v>10.52397252127792</v>
+        <v>11.83946908643767</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.007324562885810902</v>
+        <v>0.007244948071834697</v>
       </c>
       <c r="W93">
-        <v>0.2340728680715258</v>
+        <v>0.2340916412446614</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.02615915316361039</v>
+        <v>0.02587481454226681</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2600402308605085</v>
+        <v>0.2619402308605085</v>
       </c>
       <c r="C94">
-        <v>-5.410015814462504</v>
+        <v>-5.591393670273535</v>
       </c>
       <c r="D94">
-        <v>2.108784185537496</v>
+        <v>2.091306329726468</v>
       </c>
       <c r="E94">
-        <v>14.9888</v>
+        <v>15.1527</v>
       </c>
       <c r="F94">
-        <v>15.0788</v>
+        <v>15.2427</v>
       </c>
       <c r="G94">
         <v>7.56</v>
@@ -9120,37 +9120,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M94">
-        <v>3.55558104</v>
+        <v>3.59422866</v>
       </c>
       <c r="N94">
-        <v>-3.46358104</v>
+        <v>-3.50222866</v>
       </c>
       <c r="O94">
-        <v>-0.9698026912000002</v>
+        <v>-0.9806240248000001</v>
       </c>
       <c r="P94">
-        <v>-2.4937783488</v>
+        <v>-2.5216046352</v>
       </c>
       <c r="Q94">
-        <v>-2.0357783488</v>
+        <v>-2.0636046352</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5584490114427508</v>
+        <v>0.6316845845060011</v>
       </c>
       <c r="T94">
-        <v>11.83946908643767</v>
+        <v>13.53082181307162</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.007244948071834697</v>
+        <v>0.007167045404395615</v>
       </c>
       <c r="W94">
-        <v>0.2340916412446614</v>
+        <v>0.2341100106936435</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.02587481454226681</v>
+        <v>0.02559659072998433</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9166,22 +9166,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2619402308605085</v>
+        <v>0.2638402308605085</v>
       </c>
       <c r="C95">
-        <v>-5.591393670273535</v>
+        <v>-5.772484190433726</v>
       </c>
       <c r="D95">
-        <v>2.091306329726468</v>
+        <v>2.074115809566276</v>
       </c>
       <c r="E95">
-        <v>15.1527</v>
+        <v>15.3166</v>
       </c>
       <c r="F95">
-        <v>15.2427</v>
+        <v>15.4066</v>
       </c>
       <c r="G95">
         <v>7.56</v>
@@ -9202,37 +9202,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M95">
-        <v>3.59422866</v>
+        <v>3.632876280000001</v>
       </c>
       <c r="N95">
-        <v>-3.50222866</v>
+        <v>-3.54087628</v>
       </c>
       <c r="O95">
-        <v>-0.9806240248000001</v>
+        <v>-0.9914453584000003</v>
       </c>
       <c r="P95">
-        <v>-2.5216046352</v>
+        <v>-2.5494309216</v>
       </c>
       <c r="Q95">
-        <v>-2.0636046352</v>
+        <v>-2.0914309216</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6316845845060011</v>
+        <v>0.7293320152570013</v>
       </c>
       <c r="T95">
-        <v>13.53082181307162</v>
+        <v>15.78595878191689</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.007167045404395615</v>
+        <v>0.007090800240519064</v>
       </c>
       <c r="W95">
-        <v>0.2341100106936435</v>
+        <v>0.2341279893032856</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.02559659072998433</v>
+        <v>0.02532428657328234</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9248,22 +9248,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2638402308605085</v>
+        <v>0.2657402308605086</v>
       </c>
       <c r="C96">
-        <v>-5.772484190433726</v>
+        <v>-5.953294402863419</v>
       </c>
       <c r="D96">
-        <v>2.074115809566276</v>
+        <v>2.057205597136583</v>
       </c>
       <c r="E96">
-        <v>15.3166</v>
+        <v>15.4805</v>
       </c>
       <c r="F96">
-        <v>15.4066</v>
+        <v>15.5705</v>
       </c>
       <c r="G96">
         <v>7.56</v>
@@ -9284,37 +9284,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M96">
-        <v>3.632876280000001</v>
+        <v>3.6715239</v>
       </c>
       <c r="N96">
-        <v>-3.54087628</v>
+        <v>-3.5795239</v>
       </c>
       <c r="O96">
-        <v>-0.9914453584000003</v>
+        <v>-1.002266692</v>
       </c>
       <c r="P96">
-        <v>-2.5494309216</v>
+        <v>-2.577257208</v>
       </c>
       <c r="Q96">
-        <v>-2.0914309216</v>
+        <v>-2.119257208</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7293320152570013</v>
+        <v>0.8660384183084021</v>
       </c>
       <c r="T96">
-        <v>15.78595878191689</v>
+        <v>18.94315053830028</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.007090800240519064</v>
+        <v>0.007016160237987285</v>
       </c>
       <c r="W96">
-        <v>0.2341279893032856</v>
+        <v>0.2341455894158826</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.02532428657328234</v>
+        <v>0.0250577151356689</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9330,22 +9330,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2657402308605086</v>
+        <v>0.2676402308605085</v>
       </c>
       <c r="C97">
-        <v>-5.953294402863419</v>
+        <v>-6.133831108142642</v>
       </c>
       <c r="D97">
-        <v>2.057205597136583</v>
+        <v>2.04056889185736</v>
       </c>
       <c r="E97">
-        <v>15.4805</v>
+        <v>15.6444</v>
       </c>
       <c r="F97">
-        <v>15.5705</v>
+        <v>15.7344</v>
       </c>
       <c r="G97">
         <v>7.56</v>
@@ -9366,37 +9366,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M97">
-        <v>3.6715239</v>
+        <v>3.710171520000001</v>
       </c>
       <c r="N97">
-        <v>-3.5795239</v>
+        <v>-3.618171520000001</v>
       </c>
       <c r="O97">
-        <v>-1.002266692</v>
+        <v>-1.0130880256</v>
       </c>
       <c r="P97">
-        <v>-2.577257208</v>
+        <v>-2.605083494400001</v>
       </c>
       <c r="Q97">
-        <v>-2.119257208</v>
+        <v>-2.1470834944</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8660384183084021</v>
+        <v>1.071098022885503</v>
       </c>
       <c r="T97">
-        <v>18.94315053830028</v>
+        <v>23.67893817287536</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.007016160237987285</v>
+        <v>0.006943075235508251</v>
       </c>
       <c r="W97">
-        <v>0.2341455894158826</v>
+        <v>0.2341628228594672</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.0250577151356689</v>
+        <v>0.02479669726967237</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9412,22 +9412,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2676402308605085</v>
+        <v>0.2695402308605085</v>
       </c>
       <c r="C98">
-        <v>-6.13383110814264</v>
+        <v>-6.31410088862992</v>
       </c>
       <c r="D98">
-        <v>2.040568891857361</v>
+        <v>2.024199111370081</v>
       </c>
       <c r="E98">
-        <v>15.6444</v>
+        <v>15.8083</v>
       </c>
       <c r="F98">
-        <v>15.7344</v>
+        <v>15.8983</v>
       </c>
       <c r="G98">
         <v>7.56</v>
@@ -9448,37 +9448,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M98">
-        <v>3.71017152</v>
+        <v>3.74881914</v>
       </c>
       <c r="N98">
-        <v>-3.61817152</v>
+        <v>-3.65681914</v>
       </c>
       <c r="O98">
-        <v>-1.0130880256</v>
+        <v>-1.0239093592</v>
       </c>
       <c r="P98">
-        <v>-2.6050834944</v>
+        <v>-2.6329097808</v>
       </c>
       <c r="Q98">
-        <v>-2.1470834944</v>
+        <v>-2.1749097808</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.0710980228855</v>
+        <v>1.412864030514001</v>
       </c>
       <c r="T98">
-        <v>23.6789381728753</v>
+        <v>31.57191756383374</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.006943075235508252</v>
+        <v>0.006871497140296826</v>
       </c>
       <c r="W98">
-        <v>0.2341628228594672</v>
+        <v>0.234179700974318</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.02479669726967237</v>
+        <v>0.02454106121534583</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9494,22 +9494,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2695402308605085</v>
+        <v>0.2714402308605085</v>
       </c>
       <c r="C99">
-        <v>-6.31410088862992</v>
+        <v>-6.494110117145667</v>
       </c>
       <c r="D99">
-        <v>2.024199111370081</v>
+        <v>2.008089882854335</v>
       </c>
       <c r="E99">
-        <v>15.8083</v>
+        <v>15.9722</v>
       </c>
       <c r="F99">
-        <v>15.8983</v>
+        <v>16.0622</v>
       </c>
       <c r="G99">
         <v>7.56</v>
@@ -9530,37 +9530,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M99">
-        <v>3.74881914</v>
+        <v>3.78746676</v>
       </c>
       <c r="N99">
-        <v>-3.65681914</v>
+        <v>-3.69546676</v>
       </c>
       <c r="O99">
-        <v>-1.0239093592</v>
+        <v>-1.0347306928</v>
       </c>
       <c r="P99">
-        <v>-2.6329097808</v>
+        <v>-2.6607360672</v>
       </c>
       <c r="Q99">
-        <v>-2.1749097808</v>
+        <v>-2.2027360672</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.412864030514001</v>
+        <v>2.096396045771001</v>
       </c>
       <c r="T99">
-        <v>31.57191756383374</v>
+        <v>47.3578763457506</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.006871497140296826</v>
+        <v>0.006801379822538695</v>
       </c>
       <c r="W99">
-        <v>0.234179700974318</v>
+        <v>0.2341962346378454</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.02454106121534583</v>
+        <v>0.02429064222335253</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9576,22 +9576,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2714402308605085</v>
+        <v>0.2733402308605086</v>
       </c>
       <c r="C100">
-        <v>-6.494110117145667</v>
+        <v>-6.673864965244196</v>
       </c>
       <c r="D100">
-        <v>2.008089882854335</v>
+        <v>1.992235034755803</v>
       </c>
       <c r="E100">
-        <v>15.9722</v>
+        <v>16.1361</v>
       </c>
       <c r="F100">
-        <v>16.0622</v>
+        <v>16.2261</v>
       </c>
       <c r="G100">
         <v>7.56</v>
@@ -9612,37 +9612,37 @@
         <v>0.09200000000000003</v>
       </c>
       <c r="M100">
-        <v>3.78746676</v>
+        <v>3.82611438</v>
       </c>
       <c r="N100">
-        <v>-3.69546676</v>
+        <v>-3.73411438</v>
       </c>
       <c r="O100">
-        <v>-1.0347306928</v>
+        <v>-1.0455520264</v>
       </c>
       <c r="P100">
-        <v>-2.6607360672</v>
+        <v>-2.6885623536</v>
       </c>
       <c r="Q100">
-        <v>-2.2027360672</v>
+        <v>-2.2305623536</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.096396045771001</v>
+        <v>4.146992091542002</v>
       </c>
       <c r="T100">
-        <v>47.3578763457506</v>
+        <v>94.71575269150121</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.006801379822538695</v>
+        <v>0.006732679016250426</v>
       </c>
       <c r="W100">
-        <v>0.2341962346378454</v>
+        <v>0.2342124342879682</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9650,91 +9650,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.02429064222335253</v>
+        <v>0.02404528220089441</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2733402308605086</v>
-      </c>
-      <c r="C101">
-        <v>-6.673864965244196</v>
-      </c>
-      <c r="D101">
-        <v>1.992235034755803</v>
-      </c>
-      <c r="E101">
-        <v>16.1361</v>
-      </c>
-      <c r="F101">
-        <v>16.2261</v>
-      </c>
-      <c r="G101">
-        <v>7.56</v>
-      </c>
-      <c r="H101">
-        <v>16.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.55</v>
-      </c>
-      <c r="K101">
-        <v>0.458</v>
-      </c>
-      <c r="L101">
-        <v>0.09200000000000003</v>
-      </c>
-      <c r="M101">
-        <v>3.82611438</v>
-      </c>
-      <c r="N101">
-        <v>-3.73411438</v>
-      </c>
-      <c r="O101">
-        <v>-1.0455520264</v>
-      </c>
-      <c r="P101">
-        <v>-2.6885623536</v>
-      </c>
-      <c r="Q101">
-        <v>-2.2305623536</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.146992091542002</v>
-      </c>
-      <c r="T101">
-        <v>94.71575269150121</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.006732679016250426</v>
-      </c>
-      <c r="W101">
-        <v>0.2342124342879682</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.02404528220089441</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
